--- a/reports/Month to Date (Actual)_Payroll.xlsx
+++ b/reports/Month to Date (Actual)_Payroll.xlsx
@@ -40,22 +40,61 @@
     <t>DepartmentTitle</t>
   </si>
   <si>
+    <t>A3K1</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>OD</t>
+  </si>
+  <si>
+    <t>D1010</t>
+  </si>
+  <si>
+    <t>Lift Operations</t>
+  </si>
+  <si>
+    <t>G125</t>
+  </si>
+  <si>
+    <t>A2JJ</t>
+  </si>
+  <si>
+    <t>HR</t>
+  </si>
+  <si>
     <t>A0HA</t>
   </si>
   <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>OD</t>
-  </si>
-  <si>
-    <t>D1010</t>
-  </si>
-  <si>
-    <t>Lift Operations</t>
-  </si>
-  <si>
-    <t>A3K1</t>
+    <t>A0P4</t>
+  </si>
+  <si>
+    <t>B197</t>
+  </si>
+  <si>
+    <t>A2D1</t>
+  </si>
+  <si>
+    <t>A3JX</t>
+  </si>
+  <si>
+    <t>A3LM</t>
+  </si>
+  <si>
+    <t>J520</t>
+  </si>
+  <si>
+    <t>A29S</t>
+  </si>
+  <si>
+    <t>A1PN</t>
+  </si>
+  <si>
+    <t>IL</t>
+  </si>
+  <si>
+    <t>A3JZ</t>
   </si>
   <si>
     <t>A1ZJ</t>
@@ -64,150 +103,111 @@
     <t>A3GJ</t>
   </si>
   <si>
-    <t>A1PN</t>
-  </si>
-  <si>
-    <t>IL</t>
-  </si>
-  <si>
-    <t>A29S</t>
-  </si>
-  <si>
-    <t>G125</t>
-  </si>
-  <si>
-    <t>A3JX</t>
-  </si>
-  <si>
-    <t>A2D1</t>
-  </si>
-  <si>
-    <t>J520</t>
-  </si>
-  <si>
-    <t>A2JJ</t>
-  </si>
-  <si>
-    <t>HR</t>
-  </si>
-  <si>
-    <t>B197</t>
-  </si>
-  <si>
-    <t>A0P4</t>
-  </si>
-  <si>
-    <t>A3JZ</t>
-  </si>
-  <si>
-    <t>A3LM</t>
+    <t>B903</t>
+  </si>
+  <si>
+    <t>D1020</t>
+  </si>
+  <si>
+    <t>Lift Maintenance</t>
+  </si>
+  <si>
+    <t>F406</t>
+  </si>
+  <si>
+    <t>A1JS</t>
+  </si>
+  <si>
+    <t>E302</t>
+  </si>
+  <si>
+    <t>D519</t>
   </si>
   <si>
     <t>E270</t>
   </si>
   <si>
-    <t>D1020</t>
-  </si>
-  <si>
-    <t>Lift Maintenance</t>
-  </si>
-  <si>
-    <t>D519</t>
-  </si>
-  <si>
-    <t>B903</t>
-  </si>
-  <si>
-    <t>E302</t>
-  </si>
-  <si>
-    <t>F406</t>
-  </si>
-  <si>
-    <t>A1JS</t>
+    <t>J169</t>
+  </si>
+  <si>
+    <t>D1030</t>
+  </si>
+  <si>
+    <t>Snowmaking</t>
+  </si>
+  <si>
+    <t>H716</t>
   </si>
   <si>
     <t>G397</t>
   </si>
   <si>
-    <t>D1030</t>
-  </si>
-  <si>
-    <t>Snowmaking</t>
-  </si>
-  <si>
-    <t>H716</t>
-  </si>
-  <si>
-    <t>J169</t>
+    <t>D941</t>
+  </si>
+  <si>
+    <t>A3SK</t>
   </si>
   <si>
     <t>A3IL</t>
   </si>
   <si>
-    <t>A3SK</t>
-  </si>
-  <si>
-    <t>D941</t>
-  </si>
-  <si>
     <t>A3SJ</t>
   </si>
   <si>
+    <t>J056</t>
+  </si>
+  <si>
+    <t>D1060</t>
+  </si>
+  <si>
+    <t>Terrain Park</t>
+  </si>
+  <si>
+    <t>I540</t>
+  </si>
+  <si>
+    <t>H101</t>
+  </si>
+  <si>
+    <t>A3DS</t>
+  </si>
+  <si>
     <t>I238</t>
   </si>
   <si>
-    <t>D1060</t>
-  </si>
-  <si>
-    <t>Terrain Park</t>
-  </si>
-  <si>
-    <t>A3DS</t>
-  </si>
-  <si>
-    <t>J056</t>
-  </si>
-  <si>
-    <t>I540</t>
-  </si>
-  <si>
     <t>H125</t>
   </si>
   <si>
-    <t>H101</t>
+    <t>D826</t>
+  </si>
+  <si>
+    <t>D1070</t>
+  </si>
+  <si>
+    <t>Trail Maintenance</t>
+  </si>
+  <si>
+    <t>A2UN</t>
+  </si>
+  <si>
+    <t>E436</t>
+  </si>
+  <si>
+    <t>B797</t>
   </si>
   <si>
     <t>B250</t>
   </si>
   <si>
-    <t>D1070</t>
-  </si>
-  <si>
-    <t>Trail Maintenance</t>
-  </si>
-  <si>
     <t>A1ZX</t>
   </si>
   <si>
-    <t>E436</t>
-  </si>
-  <si>
-    <t>B797</t>
+    <t>A23C</t>
   </si>
   <si>
     <t>E877</t>
   </si>
   <si>
-    <t>A23C</t>
-  </si>
-  <si>
-    <t>A2UN</t>
-  </si>
-  <si>
-    <t>D826</t>
-  </si>
-  <si>
     <t>J185</t>
   </si>
   <si>
@@ -220,150 +220,150 @@
     <t>A1T8</t>
   </si>
   <si>
+    <t>A889</t>
+  </si>
+  <si>
+    <t>D1200</t>
+  </si>
+  <si>
+    <t>Ski Patrol</t>
+  </si>
+  <si>
+    <t>J471</t>
+  </si>
+  <si>
     <t>E950</t>
   </si>
   <si>
-    <t>D1200</t>
-  </si>
-  <si>
-    <t>Ski Patrol</t>
+    <t>D855</t>
+  </si>
+  <si>
+    <t>A3L3</t>
+  </si>
+  <si>
+    <t>H620</t>
+  </si>
+  <si>
+    <t>B162</t>
+  </si>
+  <si>
+    <t>G076</t>
+  </si>
+  <si>
+    <t>B878</t>
+  </si>
+  <si>
+    <t>B924</t>
+  </si>
+  <si>
+    <t>E584</t>
+  </si>
+  <si>
+    <t>J024</t>
+  </si>
+  <si>
+    <t>E471</t>
+  </si>
+  <si>
+    <t>B898</t>
   </si>
   <si>
     <t>A0JG</t>
   </si>
   <si>
-    <t>B898</t>
-  </si>
-  <si>
     <t>A3LN</t>
   </si>
   <si>
-    <t>B924</t>
-  </si>
-  <si>
-    <t>G076</t>
-  </si>
-  <si>
     <t>I762</t>
   </si>
   <si>
-    <t>D855</t>
-  </si>
-  <si>
-    <t>B878</t>
-  </si>
-  <si>
-    <t>E584</t>
-  </si>
-  <si>
-    <t>A889</t>
-  </si>
-  <si>
-    <t>J024</t>
-  </si>
-  <si>
-    <t>A3L3</t>
-  </si>
-  <si>
-    <t>B162</t>
-  </si>
-  <si>
-    <t>H620</t>
-  </si>
-  <si>
-    <t>J471</t>
-  </si>
-  <si>
-    <t>E471</t>
+    <t>A3PB</t>
+  </si>
+  <si>
+    <t>D1500</t>
+  </si>
+  <si>
+    <t>Tickets</t>
+  </si>
+  <si>
+    <t>D126</t>
+  </si>
+  <si>
+    <t>OL</t>
+  </si>
+  <si>
+    <t>A3NY</t>
+  </si>
+  <si>
+    <t>A3S9</t>
+  </si>
+  <si>
+    <t>B341</t>
+  </si>
+  <si>
+    <t>A37H</t>
+  </si>
+  <si>
+    <t>A3PT</t>
+  </si>
+  <si>
+    <t>A3M3</t>
+  </si>
+  <si>
+    <t>A2KR</t>
+  </si>
+  <si>
+    <t>A34H</t>
+  </si>
+  <si>
+    <t>I552</t>
+  </si>
+  <si>
+    <t>D071</t>
+  </si>
+  <si>
+    <t>C173</t>
+  </si>
+  <si>
+    <t>A3NW</t>
+  </si>
+  <si>
+    <t>E547</t>
+  </si>
+  <si>
+    <t>A2TY</t>
+  </si>
+  <si>
+    <t>J071</t>
+  </si>
+  <si>
+    <t>I565</t>
+  </si>
+  <si>
+    <t>A1FE</t>
   </si>
   <si>
     <t>D441</t>
   </si>
   <si>
-    <t>D1500</t>
-  </si>
-  <si>
-    <t>Tickets</t>
-  </si>
-  <si>
-    <t>A3S9</t>
-  </si>
-  <si>
-    <t>OL</t>
-  </si>
-  <si>
-    <t>D071</t>
-  </si>
-  <si>
-    <t>C173</t>
-  </si>
-  <si>
     <t>A3AD</t>
   </si>
   <si>
-    <t>A34H</t>
+    <t>I563</t>
+  </si>
+  <si>
+    <t>A2O6</t>
+  </si>
+  <si>
+    <t>A3M1</t>
+  </si>
+  <si>
+    <t>A3NV</t>
   </si>
   <si>
     <t>A3SA</t>
   </si>
   <si>
-    <t>D126</t>
-  </si>
-  <si>
-    <t>A3PB</t>
-  </si>
-  <si>
-    <t>A3NY</t>
-  </si>
-  <si>
-    <t>I563</t>
-  </si>
-  <si>
-    <t>A1FE</t>
-  </si>
-  <si>
-    <t>A2O6</t>
-  </si>
-  <si>
-    <t>A3NV</t>
-  </si>
-  <si>
-    <t>I552</t>
-  </si>
-  <si>
-    <t>A3M1</t>
-  </si>
-  <si>
-    <t>J071</t>
-  </si>
-  <si>
-    <t>A2KR</t>
-  </si>
-  <si>
-    <t>A37H</t>
-  </si>
-  <si>
-    <t>A2TY</t>
-  </si>
-  <si>
-    <t>E547</t>
-  </si>
-  <si>
-    <t>B341</t>
-  </si>
-  <si>
-    <t>A3PT</t>
-  </si>
-  <si>
-    <t>I565</t>
-  </si>
-  <si>
-    <t>A3M3</t>
-  </si>
-  <si>
-    <t>A3NW</t>
-  </si>
-  <si>
     <t>G327</t>
   </si>
   <si>
@@ -376,15 +376,15 @@
     <t>A29N</t>
   </si>
   <si>
+    <t>A2AA</t>
+  </si>
+  <si>
     <t>D3000</t>
   </si>
   <si>
     <t>Rentals</t>
   </si>
   <si>
-    <t>A2AA</t>
-  </si>
-  <si>
     <t>D4054</t>
   </si>
   <si>
@@ -400,24 +400,24 @@
     <t>Purg Sports Main Ave</t>
   </si>
   <si>
+    <t>E181</t>
+  </si>
+  <si>
+    <t>D5201</t>
+  </si>
+  <si>
+    <t>Powderhouse</t>
+  </si>
+  <si>
+    <t>A2LP</t>
+  </si>
+  <si>
+    <t>I216</t>
+  </si>
+  <si>
     <t>E655</t>
   </si>
   <si>
-    <t>D5201</t>
-  </si>
-  <si>
-    <t>Powderhouse</t>
-  </si>
-  <si>
-    <t>E181</t>
-  </si>
-  <si>
-    <t>I216</t>
-  </si>
-  <si>
-    <t>A2LP</t>
-  </si>
-  <si>
     <t>A3V5</t>
   </si>
   <si>
@@ -439,121 +439,127 @@
     <t>Waffle Cabin</t>
   </si>
   <si>
+    <t>A36T</t>
+  </si>
+  <si>
+    <t>D5206</t>
+  </si>
+  <si>
+    <t>Hoody's</t>
+  </si>
+  <si>
+    <t>G724</t>
+  </si>
+  <si>
+    <t>I704</t>
+  </si>
+  <si>
+    <t>A3FO</t>
+  </si>
+  <si>
     <t>A3PX</t>
   </si>
   <si>
-    <t>D5206</t>
-  </si>
-  <si>
-    <t>Hoody's</t>
-  </si>
-  <si>
-    <t>G724</t>
-  </si>
-  <si>
-    <t>I704</t>
-  </si>
-  <si>
-    <t>A3FO</t>
-  </si>
-  <si>
     <t>A3ZI</t>
   </si>
   <si>
-    <t>A36T</t>
+    <t>I517</t>
+  </si>
+  <si>
+    <t>D5207</t>
+  </si>
+  <si>
+    <t>Paradise</t>
+  </si>
+  <si>
+    <t>J434</t>
+  </si>
+  <si>
+    <t>A1MU</t>
   </si>
   <si>
     <t>J335</t>
   </si>
   <si>
-    <t>D5207</t>
-  </si>
-  <si>
-    <t>Paradise</t>
-  </si>
-  <si>
     <t>I518</t>
   </si>
   <si>
-    <t>I517</t>
-  </si>
-  <si>
-    <t>J434</t>
-  </si>
-  <si>
-    <t>A1MU</t>
+    <t>A3VO</t>
+  </si>
+  <si>
+    <t>D5208</t>
+  </si>
+  <si>
+    <t>Purgy's</t>
+  </si>
+  <si>
+    <t>D274</t>
+  </si>
+  <si>
+    <t>I666</t>
+  </si>
+  <si>
+    <t>A3UA</t>
+  </si>
+  <si>
+    <t>B101</t>
+  </si>
+  <si>
+    <t>D499</t>
+  </si>
+  <si>
+    <t>A15N</t>
   </si>
   <si>
     <t>A43Z</t>
   </si>
   <si>
-    <t>D5208</t>
-  </si>
-  <si>
-    <t>Purgy's</t>
-  </si>
-  <si>
-    <t>A3VO</t>
-  </si>
-  <si>
     <t>A739</t>
   </si>
   <si>
+    <t>A38R</t>
+  </si>
+  <si>
+    <t>A2RM</t>
+  </si>
+  <si>
     <t>A2HN</t>
   </si>
   <si>
     <t>A3GE</t>
   </si>
   <si>
-    <t>A3UA</t>
-  </si>
-  <si>
-    <t>D274</t>
-  </si>
-  <si>
-    <t>D499</t>
-  </si>
-  <si>
-    <t>B101</t>
-  </si>
-  <si>
-    <t>I666</t>
-  </si>
-  <si>
-    <t>A2RM</t>
-  </si>
-  <si>
-    <t>A38R</t>
-  </si>
-  <si>
     <t>A2SG</t>
   </si>
   <si>
-    <t>A15N</t>
-  </si>
-  <si>
     <t>D5209</t>
   </si>
   <si>
     <t>Village Market Deli</t>
   </si>
   <si>
+    <t>F313</t>
+  </si>
+  <si>
+    <t>D6212</t>
+  </si>
+  <si>
+    <t>Purgatory</t>
+  </si>
+  <si>
+    <t>A42C</t>
+  </si>
+  <si>
     <t>D283</t>
   </si>
   <si>
-    <t>D6212</t>
-  </si>
-  <si>
-    <t>Purgatory</t>
-  </si>
-  <si>
-    <t>F313</t>
-  </si>
-  <si>
     <t>I953</t>
   </si>
   <si>
-    <t>A42C</t>
+    <t>A1N1</t>
+  </si>
+  <si>
+    <t>F298</t>
   </si>
   <si>
     <t>A42D</t>
@@ -562,30 +568,24 @@
     <t>A3DX</t>
   </si>
   <si>
-    <t>F298</t>
-  </si>
-  <si>
-    <t>A1N1</t>
+    <t>I999</t>
+  </si>
+  <si>
+    <t>D6215</t>
+  </si>
+  <si>
+    <t>Housekeeping</t>
   </si>
   <si>
     <t>H341</t>
   </si>
   <si>
-    <t>D6215</t>
-  </si>
-  <si>
-    <t>Housekeeping</t>
-  </si>
-  <si>
     <t>A3DT</t>
   </si>
   <si>
     <t>J489</t>
   </si>
   <si>
-    <t>I999</t>
-  </si>
-  <si>
     <t>J492</t>
   </si>
   <si>
@@ -604,12 +604,12 @@
     <t>Guest Services</t>
   </si>
   <si>
+    <t>A2RO</t>
+  </si>
+  <si>
     <t>A37G</t>
   </si>
   <si>
-    <t>A2RO</t>
-  </si>
-  <si>
     <t>B421</t>
   </si>
   <si>
@@ -622,54 +622,54 @@
     <t>A3FH</t>
   </si>
   <si>
+    <t>A3HC</t>
+  </si>
+  <si>
+    <t>D6750</t>
+  </si>
+  <si>
+    <t>Engineering</t>
+  </si>
+  <si>
+    <t>A3HI</t>
+  </si>
+  <si>
     <t>F396</t>
   </si>
   <si>
-    <t>D6750</t>
-  </si>
-  <si>
-    <t>Engineering</t>
-  </si>
-  <si>
-    <t>A3HI</t>
-  </si>
-  <si>
     <t>C516</t>
   </si>
   <si>
-    <t>A3HC</t>
-  </si>
-  <si>
     <t>A2DH</t>
   </si>
   <si>
+    <t>D6780</t>
+  </si>
+  <si>
+    <t>Grounds Maintenance</t>
+  </si>
+  <si>
+    <t>A2UO</t>
+  </si>
+  <si>
+    <t>E609</t>
+  </si>
+  <si>
     <t>A3PE</t>
   </si>
   <si>
-    <t>D6780</t>
-  </si>
-  <si>
-    <t>Grounds Maintenance</t>
-  </si>
-  <si>
-    <t>A2UO</t>
-  </si>
-  <si>
     <t>D736</t>
   </si>
   <si>
-    <t>E609</t>
-  </si>
-  <si>
     <t>A2JA</t>
   </si>
   <si>
+    <t>A1WB</t>
+  </si>
+  <si>
     <t>A2SD</t>
   </si>
   <si>
-    <t>A1WB</t>
-  </si>
-  <si>
     <t>A3N2</t>
   </si>
   <si>
@@ -679,46 +679,46 @@
     <t>Snow Removal</t>
   </si>
   <si>
+    <t>A03K</t>
+  </si>
+  <si>
+    <t>D6790</t>
+  </si>
+  <si>
+    <t>Transportation</t>
+  </si>
+  <si>
+    <t>J483</t>
+  </si>
+  <si>
     <t>A3SY</t>
   </si>
   <si>
-    <t>D6790</t>
-  </si>
-  <si>
-    <t>Transportation</t>
-  </si>
-  <si>
-    <t>J483</t>
-  </si>
-  <si>
-    <t>A03K</t>
+    <t>A1Z8</t>
+  </si>
+  <si>
+    <t>D7010</t>
+  </si>
+  <si>
+    <t>Marketing</t>
+  </si>
+  <si>
+    <t>G322</t>
   </si>
   <si>
     <t>F033</t>
   </si>
   <si>
-    <t>D7010</t>
-  </si>
-  <si>
-    <t>Marketing</t>
-  </si>
-  <si>
-    <t>G322</t>
-  </si>
-  <si>
-    <t>A1Z8</t>
+    <t>A3WZ</t>
+  </si>
+  <si>
+    <t>D8020</t>
+  </si>
+  <si>
+    <t>Accounting</t>
   </si>
   <si>
     <t>D737</t>
-  </si>
-  <si>
-    <t>D8020</t>
-  </si>
-  <si>
-    <t>Accounting</t>
-  </si>
-  <si>
-    <t>A3WZ</t>
   </si>
   <si>
     <t>A3C3</t>
@@ -1155,13 +1155,13 @@
         <v>8</v>
       </c>
       <c r="B2" s="2">
-        <v>45992.28875</v>
+        <v>45992.32686342593</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D2" s="2">
-        <v>45992.71085648148</v>
+        <v>45992.70833333334</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>10</v>
@@ -1170,7 +1170,7 @@
         <v>11</v>
       </c>
       <c r="G2" s="2">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>12</v>
@@ -1181,13 +1181,13 @@
         <v>13</v>
       </c>
       <c r="B3" s="2">
-        <v>45992.32686342593</v>
+        <v>45992.32587962963</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D3" s="2">
-        <v>45992.70833333334</v>
+        <v>45992.68709490741</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>10</v>
@@ -1196,7 +1196,7 @@
         <v>11</v>
       </c>
       <c r="G3" s="2">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>12</v>
@@ -1204,16 +1204,16 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B4" s="2">
-        <v>45993.30665509259</v>
+        <v>45993.31658564815</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D4" s="2">
-        <v>45993.723125</v>
+        <v>45993.70996527778</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>10</v>
@@ -1233,13 +1233,13 @@
         <v>14</v>
       </c>
       <c r="B5" s="2">
-        <v>45992.31020833334</v>
+        <v>45992.29166666666</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D5" s="2">
-        <v>45992.70743055556</v>
+        <v>45992.71875</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>10</v>
@@ -1248,7 +1248,7 @@
         <v>11</v>
       </c>
       <c r="G5" s="2">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>12</v>
@@ -1256,16 +1256,16 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" s="2">
-        <v>45992.28857638889</v>
+        <v>45992.71596064815</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D6" s="2">
-        <v>45992.71381944444</v>
+        <v>45992.71875</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>10</v>
@@ -1282,25 +1282,25 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B7" s="2">
-        <v>45992.55469907408</v>
+        <v>45993.29166666666</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D7" s="2">
-        <v>45992.68180555556</v>
+        <v>45993.29166666666</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G7" s="2">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>12</v>
@@ -1308,16 +1308,16 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B8" s="2">
-        <v>45993.32325231482</v>
+        <v>45992.28875</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D8" s="2">
-        <v>45993.70679398148</v>
+        <v>45992.71085648148</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>10</v>
@@ -1326,7 +1326,7 @@
         <v>11</v>
       </c>
       <c r="G8" s="2">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>12</v>
@@ -1334,16 +1334,16 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B9" s="2">
-        <v>45992.32587962963</v>
+        <v>45993.30665509259</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="2">
-        <v>45992.68709490741</v>
+        <v>45993.723125</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>10</v>
@@ -1360,16 +1360,16 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B10" s="2">
-        <v>45993.31658564815</v>
+        <v>45992.3065162037</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D10" s="2">
-        <v>45993.70996527778</v>
+        <v>45992.71550925926</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>10</v>
@@ -1386,16 +1386,16 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B11" s="2">
-        <v>45993.29755787037</v>
+        <v>45993.31125</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D11" s="2">
-        <v>45993.70832175926</v>
+        <v>45993.72252314815</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>10</v>
@@ -1404,7 +1404,7 @@
         <v>11</v>
       </c>
       <c r="G11" s="2">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>12</v>
@@ -1412,16 +1412,16 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B12" s="2">
-        <v>45992.31201388889</v>
+        <v>45992.29747685185</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D12" s="2">
-        <v>45992.68565972222</v>
+        <v>45992.68304398148</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>10</v>
@@ -1430,7 +1430,7 @@
         <v>11</v>
       </c>
       <c r="G12" s="2">
-        <v>16</v>
+        <v>19.57</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>12</v>
@@ -1438,16 +1438,16 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B13" s="2">
-        <v>45992.29674768518</v>
+        <v>45993.29910879629</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D13" s="2">
-        <v>45992.71288194445</v>
+        <v>45993.7230324074</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>10</v>
@@ -1456,7 +1456,7 @@
         <v>11</v>
       </c>
       <c r="G13" s="2">
-        <v>23.69</v>
+        <v>19.57</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>12</v>
@@ -1464,16 +1464,16 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B14" s="2">
-        <v>45992.29166666666</v>
+        <v>45992.31201388889</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="2">
-        <v>45992.71875</v>
+        <v>45992.68565972222</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>10</v>
@@ -1490,16 +1490,16 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B15" s="2">
-        <v>45992.71596064815</v>
+        <v>45993.29755787037</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D15" s="2">
-        <v>45992.71875</v>
+        <v>45993.70832175926</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>10</v>
@@ -1516,19 +1516,19 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B16" s="2">
-        <v>45993.29166666666</v>
+        <v>45993.29893518519</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2">
-        <v>45993.29166666666</v>
+        <v>45993.70039351852</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>11</v>
@@ -1542,16 +1542,16 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B17" s="2">
-        <v>45992.29747685185</v>
+        <v>45992.29674768518</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D17" s="2">
-        <v>45992.68304398148</v>
+        <v>45992.71288194445</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>10</v>
@@ -1560,7 +1560,7 @@
         <v>11</v>
       </c>
       <c r="G17" s="2">
-        <v>19.57</v>
+        <v>23.69</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>12</v>
@@ -1568,16 +1568,16 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B18" s="2">
-        <v>45993.29910879629</v>
+        <v>45993.32325231482</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D18" s="2">
-        <v>45993.7230324074</v>
+        <v>45993.70679398148</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>10</v>
@@ -1586,7 +1586,7 @@
         <v>11</v>
       </c>
       <c r="G18" s="2">
-        <v>19.57</v>
+        <v>14.5</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>12</v>
@@ -1594,16 +1594,16 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B19" s="2">
-        <v>45992.3065162037</v>
+        <v>45992.55469907408</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D19" s="2">
-        <v>45992.71550925926</v>
+        <v>45992.68180555556</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>10</v>
@@ -1623,13 +1623,13 @@
         <v>26</v>
       </c>
       <c r="B20" s="2">
-        <v>45993.31125</v>
+        <v>45992.33238425926</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D20" s="2">
-        <v>45993.72252314815</v>
+        <v>45992.67116898148</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>10</v>
@@ -1638,7 +1638,7 @@
         <v>11</v>
       </c>
       <c r="G20" s="2">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>12</v>
@@ -1649,13 +1649,13 @@
         <v>27</v>
       </c>
       <c r="B21" s="2">
-        <v>45992.33238425926</v>
+        <v>45992.31020833334</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D21" s="2">
-        <v>45992.67116898148</v>
+        <v>45992.70743055556</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>10</v>
@@ -1664,7 +1664,7 @@
         <v>11</v>
       </c>
       <c r="G21" s="2">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>12</v>
@@ -1675,13 +1675,13 @@
         <v>28</v>
       </c>
       <c r="B22" s="2">
-        <v>45993.29893518519</v>
+        <v>45992.28857638889</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D22" s="2">
-        <v>45993.70039351852</v>
+        <v>45992.71381944444</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>10</v>
@@ -1701,13 +1701,13 @@
         <v>29</v>
       </c>
       <c r="B23" s="2">
-        <v>45992.27777777778</v>
+        <v>45992.26872685185</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D23" s="2">
-        <v>45992.70017361111</v>
+        <v>45992.68879629629</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>10</v>
@@ -1716,7 +1716,7 @@
         <v>30</v>
       </c>
       <c r="G23" s="2">
-        <v>35.43</v>
+        <v>23.63</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>31</v>
@@ -1727,13 +1727,13 @@
         <v>32</v>
       </c>
       <c r="B24" s="2">
-        <v>45992.27606481482</v>
+        <v>45992.26055555556</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D24" s="2">
-        <v>45992.70167824074</v>
+        <v>45992.68293981482</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>10</v>
@@ -1742,7 +1742,7 @@
         <v>30</v>
       </c>
       <c r="G24" s="2">
-        <v>21.57</v>
+        <v>25.69</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>31</v>
@@ -1750,16 +1750,16 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B25" s="2">
-        <v>45993.27314814815</v>
+        <v>45992.27179398148</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D25" s="2">
-        <v>45993.70487268519</v>
+        <v>45992.69628472222</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>10</v>
@@ -1768,7 +1768,7 @@
         <v>30</v>
       </c>
       <c r="G25" s="2">
-        <v>21.57</v>
+        <v>17</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>31</v>
@@ -1776,16 +1776,16 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="2" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B26" s="2">
-        <v>45993.26789351852</v>
+        <v>45993.27181712963</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D26" s="2">
-        <v>45993.70138888889</v>
+        <v>45993.70261574074</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>10</v>
@@ -1794,7 +1794,7 @@
         <v>30</v>
       </c>
       <c r="G26" s="2">
-        <v>35.43</v>
+        <v>29.87</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>31</v>
@@ -1802,16 +1802,16 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B27" s="2">
-        <v>45992.26872685185</v>
+        <v>45992.27083333334</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D27" s="2">
-        <v>45992.68879629629</v>
+        <v>45992.69840277778</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>10</v>
@@ -1820,7 +1820,7 @@
         <v>30</v>
       </c>
       <c r="G27" s="2">
-        <v>23.63</v>
+        <v>29.87</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>31</v>
@@ -1828,16 +1828,16 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B28" s="2">
-        <v>45993.27181712963</v>
+        <v>45992.27606481482</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D28" s="2">
-        <v>45993.70261574074</v>
+        <v>45992.70167824074</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>10</v>
@@ -1846,7 +1846,7 @@
         <v>30</v>
       </c>
       <c r="G28" s="2">
-        <v>29.87</v>
+        <v>21.57</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>31</v>
@@ -1857,13 +1857,13 @@
         <v>35</v>
       </c>
       <c r="B29" s="2">
-        <v>45992.26055555556</v>
+        <v>45993.27314814815</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D29" s="2">
-        <v>45992.68293981482</v>
+        <v>45993.70487268519</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>10</v>
@@ -1872,7 +1872,7 @@
         <v>30</v>
       </c>
       <c r="G29" s="2">
-        <v>25.69</v>
+        <v>21.57</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>31</v>
@@ -1883,13 +1883,13 @@
         <v>36</v>
       </c>
       <c r="B30" s="2">
-        <v>45992.27179398148</v>
+        <v>45993.26789351852</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D30" s="2">
-        <v>45992.69628472222</v>
+        <v>45993.70138888889</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>10</v>
@@ -1898,7 +1898,7 @@
         <v>30</v>
       </c>
       <c r="G30" s="2">
-        <v>17</v>
+        <v>35.43</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>31</v>
@@ -1906,16 +1906,16 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B31" s="2">
-        <v>45992.27083333334</v>
+        <v>45992.27777777778</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D31" s="2">
-        <v>45992.69840277778</v>
+        <v>45992.70017361111</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>10</v>
@@ -1924,7 +1924,7 @@
         <v>30</v>
       </c>
       <c r="G31" s="2">
-        <v>29.87</v>
+        <v>35.43</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>31</v>
@@ -1935,7 +1935,7 @@
         <v>37</v>
       </c>
       <c r="B32" s="2">
-        <v>45993.44041666666</v>
+        <v>45992.43916666666</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>9</v>
@@ -1957,13 +1957,13 @@
         <v>40</v>
       </c>
       <c r="B33" s="2">
-        <v>45992.47134259259</v>
+        <v>45993.46209490741</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D33" s="2">
-        <v>45992.95304398148</v>
+        <v>45993.97168981482</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>10</v>
@@ -1983,13 +1983,13 @@
         <v>40</v>
       </c>
       <c r="B34" s="2">
-        <v>45993.46209490741</v>
+        <v>45992.47134259259</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D34" s="2">
-        <v>45993.97168981482</v>
+        <v>45992.95304398148</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>10</v>
@@ -2009,13 +2009,17 @@
         <v>41</v>
       </c>
       <c r="B35" s="2">
-        <v>45992.43916666666</v>
+        <v>45992.46755787037</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
+      <c r="D35" s="2">
+        <v>45992.98403935185</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="F35" s="2" t="s">
         <v>38</v>
       </c>
@@ -2031,13 +2035,13 @@
         <v>42</v>
       </c>
       <c r="B36" s="2">
-        <v>45993.38255787037</v>
+        <v>45993.4521875</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D36" s="2">
-        <v>45993.70826388889</v>
+        <v>45994.0188425926</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>10</v>
@@ -2046,7 +2050,7 @@
         <v>38</v>
       </c>
       <c r="G36" s="2">
-        <v>19</v>
+        <v>18.55</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>39</v>
@@ -2057,13 +2061,13 @@
         <v>43</v>
       </c>
       <c r="B37" s="2">
-        <v>45992.46368055556</v>
+        <v>45993.45630787037</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D37" s="2">
-        <v>45992.96348379629</v>
+        <v>45994.00210648148</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>10</v>
@@ -2083,13 +2087,13 @@
         <v>43</v>
       </c>
       <c r="B38" s="2">
-        <v>45993.45630787037</v>
+        <v>45992.46368055556</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D38" s="2">
-        <v>45994.00210648148</v>
+        <v>45992.96348379629</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>10</v>
@@ -2109,13 +2113,13 @@
         <v>44</v>
       </c>
       <c r="B39" s="2">
-        <v>45993.4521875</v>
+        <v>45993.38255787037</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D39" s="2">
-        <v>45994.0188425926</v>
+        <v>45993.70826388889</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>10</v>
@@ -2124,7 +2128,7 @@
         <v>38</v>
       </c>
       <c r="G39" s="2">
-        <v>18.55</v>
+        <v>19</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>39</v>
@@ -2158,20 +2162,16 @@
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B41" s="2">
-        <v>45992.46755787037</v>
+        <v>45993.44041666666</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D41" s="2">
-        <v>45992.98403935185</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>10</v>
-      </c>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
       <c r="F41" s="2" t="s">
         <v>38</v>
       </c>
@@ -2187,13 +2187,13 @@
         <v>46</v>
       </c>
       <c r="B42" s="2">
-        <v>45993.30012731482</v>
+        <v>45992.31195601852</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D42" s="2">
-        <v>45993.73251157408</v>
+        <v>45992.73530092592</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>10</v>
@@ -2202,7 +2202,7 @@
         <v>47</v>
       </c>
       <c r="G42" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>48</v>
@@ -2213,13 +2213,13 @@
         <v>49</v>
       </c>
       <c r="B43" s="2">
-        <v>45993.3184375</v>
+        <v>45993.31822916667</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D43" s="2">
-        <v>45993.73899305556</v>
+        <v>45993.73927083334</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>10</v>
@@ -2228,7 +2228,7 @@
         <v>47</v>
       </c>
       <c r="G43" s="2">
-        <v>26</v>
+        <v>12.35</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>48</v>
@@ -2236,25 +2236,21 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B44" s="2">
-        <v>45992.3125</v>
+        <v>45993.3125</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D44" s="2">
-        <v>45992.94791666666</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>10</v>
-      </c>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
       <c r="F44" s="2" t="s">
         <v>47</v>
       </c>
       <c r="G44" s="2">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>48</v>
@@ -2262,16 +2258,16 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B45" s="2">
-        <v>45992.31195601852</v>
+        <v>45993.3184375</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D45" s="2">
-        <v>45992.73530092592</v>
+        <v>45993.73899305556</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>10</v>
@@ -2280,7 +2276,7 @@
         <v>47</v>
       </c>
       <c r="G45" s="2">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>48</v>
@@ -2291,13 +2287,13 @@
         <v>51</v>
       </c>
       <c r="B46" s="2">
-        <v>45993.31822916667</v>
+        <v>45992.3125</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D46" s="2">
-        <v>45993.73927083334</v>
+        <v>45992.94791666666</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>10</v>
@@ -2306,7 +2302,7 @@
         <v>47</v>
       </c>
       <c r="G46" s="2">
-        <v>12.35</v>
+        <v>26</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>48</v>
@@ -2317,18 +2313,22 @@
         <v>52</v>
       </c>
       <c r="B47" s="2">
-        <v>45993.67045138889</v>
+        <v>45993.30012731482</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D47" s="2"/>
-      <c r="E47" s="2"/>
+      <c r="D47" s="2">
+        <v>45993.73251157408</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="F47" s="2" t="s">
         <v>47</v>
       </c>
       <c r="G47" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>48</v>
@@ -2339,7 +2339,7 @@
         <v>53</v>
       </c>
       <c r="B48" s="2">
-        <v>45993.3125</v>
+        <v>45993.67045138889</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>9</v>
@@ -2350,7 +2350,7 @@
         <v>47</v>
       </c>
       <c r="G48" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>48</v>
@@ -2361,13 +2361,13 @@
         <v>54</v>
       </c>
       <c r="B49" s="2">
-        <v>45992.98611111111</v>
+        <v>45993.28452546296</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D49" s="2">
-        <v>45993.54166666666</v>
+        <v>45993.72278935185</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>10</v>
@@ -2376,7 +2376,7 @@
         <v>55</v>
       </c>
       <c r="G49" s="2">
-        <v>24.26</v>
+        <v>26</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>56</v>
@@ -2384,16 +2384,16 @@
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B50" s="2">
-        <v>45992.92275462963</v>
+        <v>45992.28890046296</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D50" s="2">
-        <v>45993.4577662037</v>
+        <v>45992.71565972222</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>10</v>
@@ -2402,7 +2402,7 @@
         <v>55</v>
       </c>
       <c r="G50" s="2">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>56</v>
@@ -2410,16 +2410,16 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B51" s="2">
-        <v>45993.72826388889</v>
+        <v>45993.47743055555</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D51" s="2">
-        <v>45994.21900462963</v>
+        <v>45993.95138888889</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>10</v>
@@ -2428,7 +2428,7 @@
         <v>55</v>
       </c>
       <c r="G51" s="2">
-        <v>23</v>
+        <v>23.33</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>56</v>
@@ -2436,16 +2436,16 @@
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B52" s="2">
-        <v>45993.95633101852</v>
+        <v>45992.48701388889</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D52" s="2">
-        <v>45994.46997685185</v>
+        <v>45992.58333333334</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>10</v>
@@ -2454,7 +2454,7 @@
         <v>55</v>
       </c>
       <c r="G52" s="2">
-        <v>19.5</v>
+        <v>23.33</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>56</v>
@@ -2462,21 +2462,25 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B53" s="2">
-        <v>45993.46145833333</v>
+        <v>45993.72826388889</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D53" s="2"/>
-      <c r="E53" s="2"/>
+      <c r="D53" s="2">
+        <v>45994.21900462963</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="F53" s="2" t="s">
         <v>55</v>
       </c>
       <c r="G53" s="2">
-        <v>16.5</v>
+        <v>23</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>56</v>
@@ -2484,16 +2488,16 @@
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B54" s="2">
-        <v>45992.46166666667</v>
+        <v>45993.95633101852</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D54" s="2">
-        <v>45992.97331018518</v>
+        <v>45994.46997685185</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>10</v>
@@ -2502,7 +2506,7 @@
         <v>55</v>
       </c>
       <c r="G54" s="2">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>56</v>
@@ -2510,16 +2514,16 @@
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B55" s="2">
-        <v>45992.44806712963</v>
+        <v>45992.98611111111</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D55" s="2">
-        <v>45992.78056712963</v>
+        <v>45993.54166666666</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>10</v>
@@ -2528,7 +2532,7 @@
         <v>55</v>
       </c>
       <c r="G55" s="2">
-        <v>18.36</v>
+        <v>24.26</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>56</v>
@@ -2536,16 +2540,16 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B56" s="2">
-        <v>45993.47743055555</v>
+        <v>45992.92275462963</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D56" s="2">
-        <v>45993.95138888889</v>
+        <v>45993.4577662037</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>10</v>
@@ -2554,7 +2558,7 @@
         <v>55</v>
       </c>
       <c r="G56" s="2">
-        <v>23.33</v>
+        <v>18</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>56</v>
@@ -2562,16 +2566,16 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B57" s="2">
-        <v>45993.28452546296</v>
+        <v>45992.44806712963</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D57" s="2">
-        <v>45993.72278935185</v>
+        <v>45992.78056712963</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>10</v>
@@ -2580,7 +2584,7 @@
         <v>55</v>
       </c>
       <c r="G57" s="2">
-        <v>26</v>
+        <v>18.36</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>56</v>
@@ -2591,22 +2595,18 @@
         <v>63</v>
       </c>
       <c r="B58" s="2">
-        <v>45992.28890046296</v>
+        <v>45993.46145833333</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D58" s="2">
-        <v>45992.71565972222</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>10</v>
-      </c>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
       <c r="F58" s="2" t="s">
         <v>55</v>
       </c>
       <c r="G58" s="2">
-        <v>26</v>
+        <v>16.5</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>56</v>
@@ -2614,7 +2614,7 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B59" s="2">
         <v>45993.97611111111</v>
@@ -2640,16 +2640,16 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B60" s="2">
-        <v>45992.48701388889</v>
+        <v>45992.46166666667</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D60" s="2">
-        <v>45992.58333333334</v>
+        <v>45992.97331018518</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>10</v>
@@ -2658,7 +2658,7 @@
         <v>55</v>
       </c>
       <c r="G60" s="2">
-        <v>23.33</v>
+        <v>16.5</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>56</v>
@@ -2773,13 +2773,13 @@
         <v>68</v>
       </c>
       <c r="B65" s="2">
-        <v>45993.31121527778</v>
+        <v>45992.31912037037</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D65" s="2">
-        <v>45993.7146875</v>
+        <v>45992.71261574074</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>10</v>
@@ -2788,7 +2788,7 @@
         <v>69</v>
       </c>
       <c r="G65" s="2">
-        <v>19</v>
+        <v>12.56</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>70</v>
@@ -2799,13 +2799,13 @@
         <v>71</v>
       </c>
       <c r="B66" s="2">
-        <v>45992.3168287037</v>
+        <v>45993.44508101852</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D66" s="2">
-        <v>45992.71090277778</v>
+        <v>45993.61892361111</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>10</v>
@@ -2814,7 +2814,7 @@
         <v>69</v>
       </c>
       <c r="G66" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>70</v>
@@ -2825,13 +2825,13 @@
         <v>71</v>
       </c>
       <c r="B67" s="2">
-        <v>45993.31672453704</v>
+        <v>45992.36817129629</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D67" s="2">
-        <v>45993.71502314815</v>
+        <v>45992.60943287037</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>10</v>
@@ -2840,7 +2840,7 @@
         <v>69</v>
       </c>
       <c r="G67" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>70</v>
@@ -2851,13 +2851,13 @@
         <v>72</v>
       </c>
       <c r="B68" s="2">
-        <v>45992.31704861111</v>
+        <v>45992.31878472222</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D68" s="2">
-        <v>45992.7106712963</v>
+        <v>45992.71140046296</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>10</v>
@@ -2866,7 +2866,7 @@
         <v>69</v>
       </c>
       <c r="G68" s="2">
-        <v>25.09</v>
+        <v>19</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>70</v>
@@ -2874,16 +2874,16 @@
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B69" s="2">
-        <v>45993.31684027778</v>
+        <v>45992.31655092593</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D69" s="2">
-        <v>45993.71487268519</v>
+        <v>45992.71273148148</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>10</v>
@@ -2892,7 +2892,7 @@
         <v>69</v>
       </c>
       <c r="G69" s="2">
-        <v>25.09</v>
+        <v>21.06</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>70</v>
@@ -2900,16 +2900,16 @@
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B70" s="2">
-        <v>45992.31818287037</v>
+        <v>45992.31442129629</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D70" s="2">
-        <v>45992.70214120371</v>
+        <v>45992.71223379629</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>10</v>
@@ -2918,7 +2918,7 @@
         <v>69</v>
       </c>
       <c r="G70" s="2">
-        <v>18.03</v>
+        <v>19.03</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>70</v>
@@ -2929,13 +2929,13 @@
         <v>74</v>
       </c>
       <c r="B71" s="2">
-        <v>45993.31284722222</v>
+        <v>45993.31137731481</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D71" s="2">
-        <v>45993.71363425926</v>
+        <v>45993.71450231481</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>10</v>
@@ -2944,7 +2944,7 @@
         <v>69</v>
       </c>
       <c r="G71" s="2">
-        <v>18.77</v>
+        <v>19.03</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>70</v>
@@ -2952,16 +2952,16 @@
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B72" s="2">
-        <v>45993.32466435185</v>
+        <v>45993.31121527778</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D72" s="2">
-        <v>45993.7155787037</v>
+        <v>45993.7146875</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>10</v>
@@ -2970,7 +2970,7 @@
         <v>69</v>
       </c>
       <c r="G72" s="2">
-        <v>23.84</v>
+        <v>19</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>70</v>
@@ -2978,16 +2978,16 @@
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B73" s="2">
-        <v>45992.31633101852</v>
+        <v>45993.31162037037</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D73" s="2">
-        <v>45992.71246527778</v>
+        <v>45993.71590277777</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>10</v>
@@ -2996,7 +2996,7 @@
         <v>69</v>
       </c>
       <c r="G73" s="2">
-        <v>19.77</v>
+        <v>22.34</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>70</v>
@@ -3007,13 +3007,13 @@
         <v>76</v>
       </c>
       <c r="B74" s="2">
-        <v>45993.31208333333</v>
+        <v>45993.31616898148</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D74" s="2">
-        <v>45993.71381944444</v>
+        <v>45993.71172453704</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>10</v>
@@ -3022,7 +3022,7 @@
         <v>69</v>
       </c>
       <c r="G74" s="2">
-        <v>19.77</v>
+        <v>16.63</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>70</v>
@@ -3030,16 +3030,16 @@
     </row>
     <row r="75" spans="1:8">
       <c r="A75" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B75" s="2">
-        <v>45993.71408564815</v>
+        <v>45993.32466435185</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D75" s="2">
-        <v>45993.71423611111</v>
+        <v>45993.7155787037</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>10</v>
@@ -3048,7 +3048,7 @@
         <v>69</v>
       </c>
       <c r="G75" s="2">
-        <v>19.77</v>
+        <v>23.84</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>70</v>
@@ -3056,16 +3056,16 @@
     </row>
     <row r="76" spans="1:8">
       <c r="A76" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B76" s="2">
-        <v>45992.31655092593</v>
+        <v>45992.3171875</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D76" s="2">
-        <v>45992.71273148148</v>
+        <v>45992.71112268518</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>10</v>
@@ -3074,7 +3074,7 @@
         <v>69</v>
       </c>
       <c r="G76" s="2">
-        <v>21.06</v>
+        <v>25.84</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>70</v>
@@ -3082,16 +3082,16 @@
     </row>
     <row r="77" spans="1:8">
       <c r="A77" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B77" s="2">
-        <v>45992.3171875</v>
+        <v>45993.31284722222</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D77" s="2">
-        <v>45992.71112268518</v>
+        <v>45993.71363425926</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>10</v>
@@ -3100,7 +3100,7 @@
         <v>69</v>
       </c>
       <c r="G77" s="2">
-        <v>25.84</v>
+        <v>18.77</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>70</v>
@@ -3108,7 +3108,7 @@
     </row>
     <row r="78" spans="1:8">
       <c r="A78" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B78" s="2">
         <v>45992.31730324074</v>
@@ -3134,16 +3134,16 @@
     </row>
     <row r="79" spans="1:8">
       <c r="A79" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B79" s="2">
-        <v>45992.31912037037</v>
+        <v>45992.32019675926</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D79" s="2">
-        <v>45992.71261574074</v>
+        <v>45992.71041666667</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>10</v>
@@ -3152,7 +3152,7 @@
         <v>69</v>
       </c>
       <c r="G79" s="2">
-        <v>12.56</v>
+        <v>24.09</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>70</v>
@@ -3160,16 +3160,16 @@
     </row>
     <row r="80" spans="1:8">
       <c r="A80" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B80" s="2">
-        <v>45992.32019675926</v>
+        <v>45993.31199074074</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D80" s="2">
-        <v>45992.71041666667</v>
+        <v>45993.71875</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>10</v>
@@ -3178,7 +3178,7 @@
         <v>69</v>
       </c>
       <c r="G80" s="2">
-        <v>24.09</v>
+        <v>24.59</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>70</v>
@@ -3186,16 +3186,16 @@
     </row>
     <row r="81" spans="1:8">
       <c r="A81" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B81" s="2">
-        <v>45993.31699074074</v>
+        <v>45992.31704861111</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D81" s="2">
-        <v>45993.71618055556</v>
+        <v>45992.7106712963</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>10</v>
@@ -3204,7 +3204,7 @@
         <v>69</v>
       </c>
       <c r="G81" s="2">
-        <v>24.09</v>
+        <v>25.09</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>70</v>
@@ -3212,16 +3212,16 @@
     </row>
     <row r="82" spans="1:8">
       <c r="A82" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B82" s="2">
-        <v>45992.31442129629</v>
+        <v>45993.31684027778</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D82" s="2">
-        <v>45992.71223379629</v>
+        <v>45993.71487268519</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>10</v>
@@ -3230,7 +3230,7 @@
         <v>69</v>
       </c>
       <c r="G82" s="2">
-        <v>19.03</v>
+        <v>25.09</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>70</v>
@@ -3238,16 +3238,16 @@
     </row>
     <row r="83" spans="1:8">
       <c r="A83" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B83" s="2">
-        <v>45993.31137731481</v>
+        <v>45992.3168287037</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D83" s="2">
-        <v>45993.71450231481</v>
+        <v>45992.71090277778</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>10</v>
@@ -3256,7 +3256,7 @@
         <v>69</v>
       </c>
       <c r="G83" s="2">
-        <v>19.03</v>
+        <v>19</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>70</v>
@@ -3264,16 +3264,16 @@
     </row>
     <row r="84" spans="1:8">
       <c r="A84" s="2" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="B84" s="2">
-        <v>45992.31878472222</v>
+        <v>45993.31672453704</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D84" s="2">
-        <v>45992.71140046296</v>
+        <v>45993.71502314815</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>10</v>
@@ -3290,16 +3290,16 @@
     </row>
     <row r="85" spans="1:8">
       <c r="A85" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B85" s="2">
-        <v>45993.31616898148</v>
+        <v>45992.31818287037</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D85" s="2">
-        <v>45993.71172453704</v>
+        <v>45992.70214120371</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>10</v>
@@ -3308,7 +3308,7 @@
         <v>69</v>
       </c>
       <c r="G85" s="2">
-        <v>16.63</v>
+        <v>18.03</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>70</v>
@@ -3316,16 +3316,16 @@
     </row>
     <row r="86" spans="1:8">
       <c r="A86" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B86" s="2">
-        <v>45993.31162037037</v>
+        <v>45992.31633101852</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D86" s="2">
-        <v>45993.71590277777</v>
+        <v>45992.71246527778</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>10</v>
@@ -3334,7 +3334,7 @@
         <v>69</v>
       </c>
       <c r="G86" s="2">
-        <v>22.34</v>
+        <v>19.77</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>70</v>
@@ -3342,16 +3342,16 @@
     </row>
     <row r="87" spans="1:8">
       <c r="A87" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B87" s="2">
-        <v>45992.36817129629</v>
+        <v>45993.31208333333</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D87" s="2">
-        <v>45992.60943287037</v>
+        <v>45993.71381944444</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>10</v>
@@ -3360,7 +3360,7 @@
         <v>69</v>
       </c>
       <c r="G87" s="2">
-        <v>22</v>
+        <v>19.77</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>70</v>
@@ -3368,16 +3368,16 @@
     </row>
     <row r="88" spans="1:8">
       <c r="A88" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B88" s="2">
-        <v>45993.44508101852</v>
+        <v>45993.71408564815</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D88" s="2">
-        <v>45993.61892361111</v>
+        <v>45993.71423611111</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>10</v>
@@ -3386,7 +3386,7 @@
         <v>69</v>
       </c>
       <c r="G88" s="2">
-        <v>22</v>
+        <v>19.77</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>70</v>
@@ -3394,16 +3394,16 @@
     </row>
     <row r="89" spans="1:8">
       <c r="A89" s="2" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B89" s="2">
-        <v>45993.31199074074</v>
+        <v>45993.31699074074</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D89" s="2">
-        <v>45993.71875</v>
+        <v>45993.71618055556</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>10</v>
@@ -3412,7 +3412,7 @@
         <v>69</v>
       </c>
       <c r="G89" s="2">
-        <v>24.59</v>
+        <v>24.09</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>70</v>
@@ -3423,13 +3423,13 @@
         <v>87</v>
       </c>
       <c r="B90" s="2">
-        <v>45992.34856481481</v>
+        <v>45993.33755787037</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D90" s="2">
-        <v>45992.3864699074</v>
+        <v>45993.68662037037</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>10</v>
@@ -3438,7 +3438,7 @@
         <v>88</v>
       </c>
       <c r="G90" s="2">
-        <v>22.5</v>
+        <v>17.5</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>89</v>
@@ -3449,22 +3449,22 @@
         <v>90</v>
       </c>
       <c r="B91" s="2">
-        <v>45993.33197916667</v>
+        <v>45993.55333333334</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D91" s="2">
-        <v>45993.57767361111</v>
+        <v>45993.7515162037</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G91" s="2">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="H91" s="2" t="s">
         <v>89</v>
@@ -3472,25 +3472,25 @@
     </row>
     <row r="92" spans="1:8">
       <c r="A92" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B92" s="2">
-        <v>45993.54564814815</v>
+        <v>45993.33243055556</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D92" s="2">
-        <v>45993.71084490741</v>
+        <v>45993.50996527778</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G92" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>89</v>
@@ -3501,13 +3501,13 @@
         <v>92</v>
       </c>
       <c r="B93" s="2">
-        <v>45992.54113425926</v>
+        <v>45992.58793981482</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D93" s="2">
-        <v>45992.70725694444</v>
+        <v>45992.75136574074</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>10</v>
@@ -3516,7 +3516,7 @@
         <v>88</v>
       </c>
       <c r="G93" s="2">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="H93" s="2" t="s">
         <v>89</v>
@@ -3527,22 +3527,22 @@
         <v>93</v>
       </c>
       <c r="B94" s="2">
-        <v>45993.375</v>
+        <v>45992.33369212963</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D94" s="2">
-        <v>45993.70833333334</v>
+        <v>45992.48134259259</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G94" s="2">
-        <v>22.5</v>
+        <v>17.5</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>89</v>
@@ -3550,25 +3550,25 @@
     </row>
     <row r="95" spans="1:8">
       <c r="A95" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B95" s="2">
-        <v>45992.375</v>
+        <v>45993.33583333333</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D95" s="2">
-        <v>45992.66666666666</v>
+        <v>45993.59112268518</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="F95" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G95" s="2">
-        <v>22.5</v>
+        <v>15</v>
       </c>
       <c r="H95" s="2" t="s">
         <v>89</v>
@@ -3576,19 +3576,19 @@
     </row>
     <row r="96" spans="1:8">
       <c r="A96" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B96" s="2">
-        <v>45992.32902777778</v>
+        <v>45992.33872685185</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D96" s="2">
-        <v>45992.6815162037</v>
+        <v>45992.46394675926</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>88</v>
@@ -3602,36 +3602,42 @@
     </row>
     <row r="97" spans="1:8">
       <c r="A97" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B97" s="2">
-        <v>45992.32043981482</v>
+        <v>45993.33037037037</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D97" s="2"/>
-      <c r="E97" s="2"/>
+      <c r="D97" s="2">
+        <v>45993.50478009259</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="F97" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="G97" s="2"/>
+      <c r="G97" s="2">
+        <v>17.5</v>
+      </c>
       <c r="H97" s="2" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="98" spans="1:8">
       <c r="A98" s="2" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="B98" s="2">
-        <v>45993.59668981482</v>
+        <v>45993.54019675926</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D98" s="2">
-        <v>45993.70082175926</v>
+        <v>45993.70605324074</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>10</v>
@@ -3648,25 +3654,25 @@
     </row>
     <row r="99" spans="1:8">
       <c r="A99" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B99" s="2">
-        <v>45993.52398148148</v>
+        <v>45993.33644675926</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D99" s="2">
-        <v>45993.6846412037</v>
+        <v>45993.52070601852</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G99" s="2">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="H99" s="2" t="s">
         <v>89</v>
@@ -3674,16 +3680,16 @@
     </row>
     <row r="100" spans="1:8">
       <c r="A100" s="2" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="B100" s="2">
-        <v>45992.50671296296</v>
+        <v>45992.55483796296</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D100" s="2">
-        <v>45992.70057870371</v>
+        <v>45992.68207175926</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>10</v>
@@ -3700,25 +3706,25 @@
     </row>
     <row r="101" spans="1:8">
       <c r="A101" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B101" s="2">
-        <v>45993.33243055556</v>
+        <v>45992.50671296296</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D101" s="2">
-        <v>45993.50996527778</v>
+        <v>45992.70057870371</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G101" s="2">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>89</v>
@@ -3726,19 +3732,19 @@
     </row>
     <row r="102" spans="1:8">
       <c r="A102" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B102" s="2">
-        <v>45993.33755787037</v>
+        <v>45992.33802083333</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D102" s="2">
-        <v>45993.68662037037</v>
+        <v>45992.51306712963</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="F102" s="2" t="s">
         <v>88</v>
@@ -3752,16 +3758,16 @@
     </row>
     <row r="103" spans="1:8">
       <c r="A103" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B103" s="2">
-        <v>45992.58793981482</v>
+        <v>45993.58587962963</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D103" s="2">
-        <v>45992.75136574074</v>
+        <v>45993.75435185185</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>10</v>
@@ -3778,25 +3784,25 @@
     </row>
     <row r="104" spans="1:8">
       <c r="A104" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B104" s="2">
-        <v>45993.55333333334</v>
+        <v>45993.33197916667</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D104" s="2">
-        <v>45993.7515162037</v>
+        <v>45993.57767361111</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="F104" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G104" s="2">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>89</v>
@@ -3804,16 +3810,16 @@
     </row>
     <row r="105" spans="1:8">
       <c r="A105" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B105" s="2">
-        <v>45993.51013888889</v>
+        <v>45992.33333333334</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D105" s="2">
-        <v>45993.70188657408</v>
+        <v>45992.67053240741</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>10</v>
@@ -3830,42 +3836,36 @@
     </row>
     <row r="106" spans="1:8">
       <c r="A106" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B106" s="2">
-        <v>45992.33951388889</v>
+        <v>45992.32043981482</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D106" s="2">
-        <v>45992.42443287037</v>
-      </c>
-      <c r="E106" s="2" t="s">
-        <v>91</v>
-      </c>
+      <c r="D106" s="2"/>
+      <c r="E106" s="2"/>
       <c r="F106" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="G106" s="2">
-        <v>15</v>
-      </c>
+      <c r="G106" s="2"/>
       <c r="H106" s="2" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="107" spans="1:8">
       <c r="A107" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B107" s="2">
-        <v>45993.55407407408</v>
+        <v>45992.603125</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D107" s="2">
-        <v>45993.68141203704</v>
+        <v>45992.75163194445</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>10</v>
@@ -3874,7 +3874,7 @@
         <v>88</v>
       </c>
       <c r="G107" s="2">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="H107" s="2" t="s">
         <v>89</v>
@@ -3882,16 +3882,16 @@
     </row>
     <row r="108" spans="1:8">
       <c r="A108" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B108" s="2">
-        <v>45993.33417824074</v>
+        <v>45992.32556712963</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D108" s="2">
-        <v>45993.54109953704</v>
+        <v>45992.56069444444</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>91</v>
@@ -3900,7 +3900,7 @@
         <v>88</v>
       </c>
       <c r="G108" s="2">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>89</v>
@@ -3908,16 +3908,16 @@
     </row>
     <row r="109" spans="1:8">
       <c r="A109" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B109" s="2">
-        <v>45992.33333333334</v>
+        <v>45993.54564814815</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D109" s="2">
-        <v>45992.67103009259</v>
+        <v>45993.71084490741</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>10</v>
@@ -3926,7 +3926,7 @@
         <v>88</v>
       </c>
       <c r="G109" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H109" s="2" t="s">
         <v>89</v>
@@ -3934,25 +3934,25 @@
     </row>
     <row r="110" spans="1:8">
       <c r="A110" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B110" s="2">
-        <v>45993.33459490741</v>
+        <v>45992.54113425926</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D110" s="2">
-        <v>45993.49261574074</v>
+        <v>45992.70725694444</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G110" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>89</v>
@@ -3960,25 +3960,25 @@
     </row>
     <row r="111" spans="1:8">
       <c r="A111" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B111" s="2">
-        <v>45993.33659722222</v>
+        <v>45993.375</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D111" s="2">
-        <v>45993.54575231481</v>
+        <v>45993.70833333334</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="F111" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G111" s="2">
-        <v>15</v>
+        <v>22.5</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>89</v>
@@ -3986,25 +3986,25 @@
     </row>
     <row r="112" spans="1:8">
       <c r="A112" s="2" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="B112" s="2">
-        <v>45992.33369212963</v>
+        <v>45992.375</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D112" s="2">
-        <v>45992.48134259259</v>
+        <v>45992.66666666666</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="F112" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G112" s="2">
-        <v>17.5</v>
+        <v>22.5</v>
       </c>
       <c r="H112" s="2" t="s">
         <v>89</v>
@@ -4015,13 +4015,13 @@
         <v>103</v>
       </c>
       <c r="B113" s="2">
-        <v>45992.58239583333</v>
+        <v>45993.3166087963</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D113" s="2">
-        <v>45992.67513888889</v>
+        <v>45993.70063657407</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>10</v>
@@ -4038,16 +4038,16 @@
     </row>
     <row r="114" spans="1:8">
       <c r="A114" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B114" s="2">
-        <v>45992.603125</v>
+        <v>45992.32601851852</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D114" s="2">
-        <v>45992.75163194445</v>
+        <v>45992.68008101852</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>10</v>
@@ -4056,7 +4056,7 @@
         <v>88</v>
       </c>
       <c r="G114" s="2">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="H114" s="2" t="s">
         <v>89</v>
@@ -4064,16 +4064,16 @@
     </row>
     <row r="115" spans="1:8">
       <c r="A115" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B115" s="2">
-        <v>45993.55733796296</v>
+        <v>45993.375</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D115" s="2">
-        <v>45993.70209490741</v>
+        <v>45993.70833333334</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>10</v>
@@ -4082,7 +4082,7 @@
         <v>88</v>
       </c>
       <c r="G115" s="2">
-        <v>18</v>
+        <v>22.5</v>
       </c>
       <c r="H115" s="2" t="s">
         <v>89</v>
@@ -4093,22 +4093,22 @@
         <v>104</v>
       </c>
       <c r="B116" s="2">
-        <v>45993.32962962963</v>
+        <v>45992.375</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D116" s="2">
-        <v>45993.59543981482</v>
+        <v>45992.66666666666</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="F116" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G116" s="2">
-        <v>17.5</v>
+        <v>22.5</v>
       </c>
       <c r="H116" s="2" t="s">
         <v>89</v>
@@ -4116,16 +4116,16 @@
     </row>
     <row r="117" spans="1:8">
       <c r="A117" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B117" s="2">
-        <v>45993.62835648148</v>
+        <v>45993.33652777778</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D117" s="2">
-        <v>45993.75800925926</v>
+        <v>45993.61788194445</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>10</v>
@@ -4134,7 +4134,7 @@
         <v>88</v>
       </c>
       <c r="G117" s="2">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="H117" s="2" t="s">
         <v>89</v>
@@ -4142,25 +4142,25 @@
     </row>
     <row r="118" spans="1:8">
       <c r="A118" s="2" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="B118" s="2">
-        <v>45992.44226851852</v>
+        <v>45993.33407407408</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D118" s="2">
-        <v>45992.44354166667</v>
+        <v>45993.54098379629</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G118" s="2">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="H118" s="2" t="s">
         <v>89</v>
@@ -4194,25 +4194,25 @@
     </row>
     <row r="120" spans="1:8">
       <c r="A120" s="2" t="s">
-        <v>16</v>
+        <v>107</v>
       </c>
       <c r="B120" s="2">
-        <v>45992.33506944445</v>
+        <v>45992.4390625</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D120" s="2">
-        <v>45992.53091435185</v>
+        <v>45992.6797337963</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G120" s="2">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="H120" s="2" t="s">
         <v>89</v>
@@ -4220,16 +4220,16 @@
     </row>
     <row r="121" spans="1:8">
       <c r="A121" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B121" s="2">
-        <v>45992.33333333334</v>
+        <v>45992.33135416666</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D121" s="2">
-        <v>45992.67053240741</v>
+        <v>45992.60255787037</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>10</v>
@@ -4246,16 +4246,16 @@
     </row>
     <row r="122" spans="1:8">
       <c r="A122" s="2" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="B122" s="2">
-        <v>45993.33407407408</v>
+        <v>45993.32962962963</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D122" s="2">
-        <v>45993.54098379629</v>
+        <v>45993.59543981482</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>91</v>
@@ -4264,7 +4264,7 @@
         <v>88</v>
       </c>
       <c r="G122" s="2">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="H122" s="2" t="s">
         <v>89</v>
@@ -4272,25 +4272,25 @@
     </row>
     <row r="123" spans="1:8">
       <c r="A123" s="2" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="B123" s="2">
-        <v>45992.33872685185</v>
+        <v>45993.59668981482</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D123" s="2">
-        <v>45992.46394675926</v>
+        <v>45993.70082175926</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="F123" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G123" s="2">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="H123" s="2" t="s">
         <v>89</v>
@@ -4298,25 +4298,25 @@
     </row>
     <row r="124" spans="1:8">
       <c r="A124" s="2" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="B124" s="2">
-        <v>45992.340625</v>
+        <v>45993.33659722222</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D124" s="2">
-        <v>45992.5102662037</v>
+        <v>45993.54575231481</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="F124" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G124" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H124" s="2" t="s">
         <v>89</v>
@@ -4324,25 +4324,25 @@
     </row>
     <row r="125" spans="1:8">
       <c r="A125" s="2" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="B125" s="2">
-        <v>45993.33226851852</v>
+        <v>45992.34856481481</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D125" s="2">
-        <v>45993.48760416666</v>
+        <v>45992.3864699074</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="F125" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G125" s="2">
-        <v>16</v>
+        <v>22.5</v>
       </c>
       <c r="H125" s="2" t="s">
         <v>89</v>
@@ -4350,25 +4350,25 @@
     </row>
     <row r="126" spans="1:8">
       <c r="A126" s="2" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="B126" s="2">
-        <v>45992.32942129629</v>
+        <v>45992.32902777778</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D126" s="2">
-        <v>45992.5415162037</v>
+        <v>45992.6815162037</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="F126" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G126" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H126" s="2" t="s">
         <v>89</v>
@@ -4376,16 +4376,16 @@
     </row>
     <row r="127" spans="1:8">
       <c r="A127" s="2" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="B127" s="2">
-        <v>45993.33652777778</v>
+        <v>45993.62835648148</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D127" s="2">
-        <v>45993.61788194445</v>
+        <v>45993.75800925926</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>10</v>
@@ -4394,7 +4394,7 @@
         <v>88</v>
       </c>
       <c r="G127" s="2">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="H127" s="2" t="s">
         <v>89</v>
@@ -4402,16 +4402,16 @@
     </row>
     <row r="128" spans="1:8">
       <c r="A128" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B128" s="2">
-        <v>45992.33135416666</v>
+        <v>45992.340625</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D128" s="2">
-        <v>45992.60255787037</v>
+        <v>45992.5102662037</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>10</v>
@@ -4428,25 +4428,25 @@
     </row>
     <row r="129" spans="1:8">
       <c r="A129" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B129" s="2">
-        <v>45992.375</v>
+        <v>45993.33226851852</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D129" s="2">
-        <v>45992.66666666666</v>
+        <v>45993.48760416666</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="F129" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G129" s="2">
-        <v>22.5</v>
+        <v>16</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>89</v>
@@ -4454,25 +4454,25 @@
     </row>
     <row r="130" spans="1:8">
       <c r="A130" s="2" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="B130" s="2">
-        <v>45993.33475694444</v>
+        <v>45993.51013888889</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D130" s="2">
-        <v>45993.53561342593</v>
+        <v>45993.70188657408</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="F130" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G130" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H130" s="2" t="s">
         <v>89</v>
@@ -4480,16 +4480,16 @@
     </row>
     <row r="131" spans="1:8">
       <c r="A131" s="2" t="s">
-        <v>111</v>
+        <v>24</v>
       </c>
       <c r="B131" s="2">
-        <v>45993.33583333333</v>
+        <v>45992.33506944445</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D131" s="2">
-        <v>45993.59112268518</v>
+        <v>45992.53091435185</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>91</v>
@@ -4498,7 +4498,7 @@
         <v>88</v>
       </c>
       <c r="G131" s="2">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="H131" s="2" t="s">
         <v>89</v>
@@ -4509,13 +4509,13 @@
         <v>112</v>
       </c>
       <c r="B132" s="2">
-        <v>45993.58587962963</v>
+        <v>45992.33333333334</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D132" s="2">
-        <v>45993.75435185185</v>
+        <v>45992.67103009259</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>10</v>
@@ -4524,7 +4524,7 @@
         <v>88</v>
       </c>
       <c r="G132" s="2">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="H132" s="2" t="s">
         <v>89</v>
@@ -4532,25 +4532,25 @@
     </row>
     <row r="133" spans="1:8">
       <c r="A133" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B133" s="2">
-        <v>45992.4390625</v>
+        <v>45993.33417824074</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D133" s="2">
-        <v>45992.6797337963</v>
+        <v>45993.54109953704</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="F133" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G133" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H133" s="2" t="s">
         <v>89</v>
@@ -4558,16 +4558,16 @@
     </row>
     <row r="134" spans="1:8">
       <c r="A134" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B134" s="2">
-        <v>45993.54019675926</v>
+        <v>45993.55407407408</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D134" s="2">
-        <v>45993.70605324074</v>
+        <v>45993.68141203704</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>10</v>
@@ -4576,7 +4576,7 @@
         <v>88</v>
       </c>
       <c r="G134" s="2">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>89</v>
@@ -4584,25 +4584,25 @@
     </row>
     <row r="135" spans="1:8">
       <c r="A135" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B135" s="2">
-        <v>45993.33037037037</v>
+        <v>45993.33475694444</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D135" s="2">
-        <v>45993.50478009259</v>
+        <v>45993.53561342593</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="F135" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G135" s="2">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>89</v>
@@ -4610,16 +4610,16 @@
     </row>
     <row r="136" spans="1:8">
       <c r="A136" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B136" s="2">
-        <v>45992.55483796296</v>
+        <v>45993.55733796296</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D136" s="2">
-        <v>45992.68207175926</v>
+        <v>45993.70209490741</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>10</v>
@@ -4628,7 +4628,7 @@
         <v>88</v>
       </c>
       <c r="G136" s="2">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>89</v>
@@ -4639,13 +4639,13 @@
         <v>114</v>
       </c>
       <c r="B137" s="2">
-        <v>45992.33802083333</v>
+        <v>45992.32942129629</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D137" s="2">
-        <v>45992.51306712963</v>
+        <v>45992.5415162037</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>91</v>
@@ -4654,7 +4654,7 @@
         <v>88</v>
       </c>
       <c r="G137" s="2">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="H137" s="2" t="s">
         <v>89</v>
@@ -4662,25 +4662,25 @@
     </row>
     <row r="138" spans="1:8">
       <c r="A138" s="2" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="B138" s="2">
-        <v>45992.32556712963</v>
+        <v>45992.58239583333</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D138" s="2">
-        <v>45992.56069444444</v>
+        <v>45992.67513888889</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="F138" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G138" s="2">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="H138" s="2" t="s">
         <v>89</v>
@@ -4691,16 +4691,16 @@
         <v>115</v>
       </c>
       <c r="B139" s="2">
-        <v>45992.32601851852</v>
+        <v>45993.33459490741</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D139" s="2">
-        <v>45992.68008101852</v>
+        <v>45993.49261574074</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="F139" s="2" t="s">
         <v>88</v>
@@ -4714,16 +4714,16 @@
     </row>
     <row r="140" spans="1:8">
       <c r="A140" s="2" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B140" s="2">
-        <v>45993.375</v>
+        <v>45993.52398148148</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D140" s="2">
-        <v>45993.70833333334</v>
+        <v>45993.6846412037</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>10</v>
@@ -4732,7 +4732,7 @@
         <v>88</v>
       </c>
       <c r="G140" s="2">
-        <v>22.5</v>
+        <v>18</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>89</v>
@@ -4740,16 +4740,16 @@
     </row>
     <row r="141" spans="1:8">
       <c r="A141" s="2" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="B141" s="2">
-        <v>45993.33644675926</v>
+        <v>45992.33951388889</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D141" s="2">
-        <v>45993.52070601852</v>
+        <v>45992.42443287037</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>91</v>
@@ -4758,7 +4758,7 @@
         <v>88</v>
       </c>
       <c r="G141" s="2">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="H141" s="2" t="s">
         <v>89</v>
@@ -4766,16 +4766,16 @@
     </row>
     <row r="142" spans="1:8">
       <c r="A142" s="2" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="B142" s="2">
-        <v>45993.3166087963</v>
+        <v>45992.44226851852</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D142" s="2">
-        <v>45993.70063657407</v>
+        <v>45992.44354166667</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>10</v>
@@ -4784,7 +4784,7 @@
         <v>88</v>
       </c>
       <c r="G142" s="2">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="H142" s="2" t="s">
         <v>89</v>
@@ -4795,16 +4795,16 @@
         <v>116</v>
       </c>
       <c r="B143" s="2">
-        <v>45993.33333333334</v>
+        <v>45992.3477662037</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D143" s="2">
-        <v>45993.33333333334</v>
+        <v>45992.713125</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F143" s="2" t="s">
         <v>117</v>
@@ -4818,25 +4818,25 @@
     </row>
     <row r="144" spans="1:8">
       <c r="A144" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B144" s="2">
-        <v>45992.3477662037</v>
+        <v>45993</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D144" s="2">
-        <v>45992.713125</v>
+        <v>45993</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F144" s="2" t="s">
         <v>117</v>
       </c>
       <c r="G144" s="2">
-        <v>17.51</v>
+        <v>17.5</v>
       </c>
       <c r="H144" s="2" t="s">
         <v>118</v>
@@ -4844,25 +4844,25 @@
     </row>
     <row r="145" spans="1:8">
       <c r="A145" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B145" s="2">
-        <v>45993</v>
+        <v>45993.33333333334</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D145" s="2">
-        <v>45993</v>
+        <v>45993.33333333334</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F145" s="2" t="s">
         <v>117</v>
       </c>
       <c r="G145" s="2">
-        <v>17.5</v>
+        <v>17.51</v>
       </c>
       <c r="H145" s="2" t="s">
         <v>118</v>
@@ -4870,39 +4870,39 @@
     </row>
     <row r="146" spans="1:8">
       <c r="A146" s="2" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="B146" s="2">
-        <v>45993.58836805556</v>
+        <v>45992.54988425926</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D146" s="2">
-        <v>45993.70449074074</v>
+        <v>45992.6850462963</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G146" s="2">
         <v>15</v>
       </c>
       <c r="H146" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="147" spans="1:8">
       <c r="A147" s="2" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="B147" s="2">
         <v>45992.48001157407</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D147" s="2">
         <v>45992.70277777778</v>
@@ -4911,50 +4911,50 @@
         <v>10</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G147" s="2">
         <v>15</v>
       </c>
       <c r="H147" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="148" spans="1:8">
       <c r="A148" s="2" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B148" s="2">
-        <v>45992.54988425926</v>
+        <v>45993.58836805556</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D148" s="2">
-        <v>45992.6850462963</v>
+        <v>45993.70449074074</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G148" s="2">
         <v>15</v>
       </c>
       <c r="H148" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="149" spans="1:8">
       <c r="A149" s="2" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="B149" s="2">
         <v>45993.61039351852</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D149" s="2">
         <v>45993.68513888889</v>
@@ -5003,13 +5003,13 @@
         <v>128</v>
       </c>
       <c r="B151" s="2">
-        <v>45993.34043981481</v>
+        <v>45993.32821759259</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D151" s="2">
-        <v>45993.68324074074</v>
+        <v>45993.34375</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>10</v>
@@ -5018,7 +5018,7 @@
         <v>129</v>
       </c>
       <c r="G151" s="2">
-        <v>13.65</v>
+        <v>17.48</v>
       </c>
       <c r="H151" s="2" t="s">
         <v>130</v>
@@ -5026,16 +5026,16 @@
     </row>
     <row r="152" spans="1:8">
       <c r="A152" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B152" s="2">
-        <v>45993.32821759259</v>
+        <v>45992.32685185185</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D152" s="2">
-        <v>45993.34375</v>
+        <v>45992.66329861111</v>
       </c>
       <c r="E152" s="2" t="s">
         <v>10</v>
@@ -5052,16 +5052,16 @@
     </row>
     <row r="153" spans="1:8">
       <c r="A153" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B153" s="2">
-        <v>45993.33630787037</v>
+        <v>45993.34569444445</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D153" s="2">
-        <v>45993.66971064815</v>
+        <v>45993.69732638889</v>
       </c>
       <c r="E153" s="2" t="s">
         <v>10</v>
@@ -5070,7 +5070,7 @@
         <v>129</v>
       </c>
       <c r="G153" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H153" s="2" t="s">
         <v>130</v>
@@ -5078,16 +5078,16 @@
     </row>
     <row r="154" spans="1:8">
       <c r="A154" s="2" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B154" s="2">
-        <v>45992.34711805556</v>
+        <v>45992.30037037037</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D154" s="2">
-        <v>45992.68376157407</v>
+        <v>45992.70363425926</v>
       </c>
       <c r="E154" s="2" t="s">
         <v>10</v>
@@ -5096,7 +5096,7 @@
         <v>129</v>
       </c>
       <c r="G154" s="2">
-        <v>13.65</v>
+        <v>18</v>
       </c>
       <c r="H154" s="2" t="s">
         <v>130</v>
@@ -5104,16 +5104,16 @@
     </row>
     <row r="155" spans="1:8">
       <c r="A155" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B155" s="2">
-        <v>45992.32685185185</v>
+        <v>45993.33630787037</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D155" s="2">
-        <v>45992.66329861111</v>
+        <v>45993.66971064815</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>10</v>
@@ -5122,7 +5122,7 @@
         <v>129</v>
       </c>
       <c r="G155" s="2">
-        <v>17.48</v>
+        <v>21</v>
       </c>
       <c r="H155" s="2" t="s">
         <v>130</v>
@@ -5133,13 +5133,13 @@
         <v>133</v>
       </c>
       <c r="B156" s="2">
-        <v>45993.34569444445</v>
+        <v>45993.34043981481</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D156" s="2">
-        <v>45993.69732638889</v>
+        <v>45993.68324074074</v>
       </c>
       <c r="E156" s="2" t="s">
         <v>10</v>
@@ -5148,7 +5148,7 @@
         <v>129</v>
       </c>
       <c r="G156" s="2">
-        <v>18</v>
+        <v>13.65</v>
       </c>
       <c r="H156" s="2" t="s">
         <v>130</v>
@@ -5159,13 +5159,13 @@
         <v>133</v>
       </c>
       <c r="B157" s="2">
-        <v>45992.30037037037</v>
+        <v>45992.34711805556</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D157" s="2">
-        <v>45992.70363425926</v>
+        <v>45992.68376157407</v>
       </c>
       <c r="E157" s="2" t="s">
         <v>10</v>
@@ -5174,7 +5174,7 @@
         <v>129</v>
       </c>
       <c r="G157" s="2">
-        <v>18</v>
+        <v>13.65</v>
       </c>
       <c r="H157" s="2" t="s">
         <v>130</v>
@@ -5182,7 +5182,7 @@
     </row>
     <row r="158" spans="1:8">
       <c r="A158" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B158" s="2">
         <v>45992.35592592593</v>
@@ -5214,7 +5214,7 @@
         <v>45993.83056712963</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D159" s="2">
         <v>45993.91854166667</v>
@@ -5289,13 +5289,13 @@
         <v>141</v>
       </c>
       <c r="B162" s="2">
-        <v>45993.3390625</v>
+        <v>45992.32082175926</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D162" s="2">
-        <v>45993.61498842593</v>
+        <v>45992.61207175926</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>10</v>
@@ -5304,7 +5304,7 @@
         <v>142</v>
       </c>
       <c r="G162" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H162" s="2" t="s">
         <v>143</v>
@@ -5419,13 +5419,13 @@
         <v>147</v>
       </c>
       <c r="B167" s="2">
-        <v>45992.33707175926</v>
+        <v>45993.3390625</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D167" s="2">
-        <v>45992.59480324074</v>
+        <v>45993.61498842593</v>
       </c>
       <c r="E167" s="2" t="s">
         <v>10</v>
@@ -5434,7 +5434,7 @@
         <v>142</v>
       </c>
       <c r="G167" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H167" s="2" t="s">
         <v>143</v>
@@ -5442,7 +5442,7 @@
     </row>
     <row r="168" spans="1:8">
       <c r="A168" s="2" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="B168" s="2">
         <v>45993.32221064815</v>
@@ -5471,13 +5471,13 @@
         <v>148</v>
       </c>
       <c r="B169" s="2">
-        <v>45992.32082175926</v>
+        <v>45992.33707175926</v>
       </c>
       <c r="C169" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D169" s="2">
-        <v>45992.61207175926</v>
+        <v>45992.59480324074</v>
       </c>
       <c r="E169" s="2" t="s">
         <v>10</v>
@@ -5497,22 +5497,22 @@
         <v>149</v>
       </c>
       <c r="B170" s="2">
-        <v>45993.34152777777</v>
+        <v>45992.4106712963</v>
       </c>
       <c r="C170" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D170" s="2">
-        <v>45993.58498842592</v>
+        <v>45992.52935185185</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="F170" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G170" s="2">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H170" s="2" t="s">
         <v>151</v>
@@ -5520,16 +5520,16 @@
     </row>
     <row r="171" spans="1:8">
       <c r="A171" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B171" s="2">
-        <v>45992.89799768518</v>
+        <v>45993.42930555555</v>
       </c>
       <c r="C171" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D171" s="2">
-        <v>45992.89809027778</v>
+        <v>45993.82324074074</v>
       </c>
       <c r="E171" s="2" t="s">
         <v>10</v>
@@ -5538,7 +5538,7 @@
         <v>150</v>
       </c>
       <c r="G171" s="2">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H171" s="2" t="s">
         <v>151</v>
@@ -5546,19 +5546,19 @@
     </row>
     <row r="172" spans="1:8">
       <c r="A172" s="2" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B172" s="2">
-        <v>45992.4106712963</v>
+        <v>45992.87222222222</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D172" s="2">
-        <v>45992.52935185185</v>
+        <v>45992.87225694444</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="F172" s="2" t="s">
         <v>150</v>
@@ -5572,16 +5572,16 @@
     </row>
     <row r="173" spans="1:8">
       <c r="A173" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B173" s="2">
-        <v>45992.55707175926</v>
+        <v>45993.41944444444</v>
       </c>
       <c r="C173" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D173" s="2">
-        <v>45992.87207175926</v>
+        <v>45993.82296296296</v>
       </c>
       <c r="E173" s="2" t="s">
         <v>10</v>
@@ -5598,16 +5598,16 @@
     </row>
     <row r="174" spans="1:8">
       <c r="A174" s="2" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B174" s="2">
-        <v>45993.47211805556</v>
+        <v>45992.55707175926</v>
       </c>
       <c r="C174" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D174" s="2">
-        <v>45993.69221064815</v>
+        <v>45992.87207175926</v>
       </c>
       <c r="E174" s="2" t="s">
         <v>10</v>
@@ -5616,7 +5616,7 @@
         <v>150</v>
       </c>
       <c r="G174" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H174" s="2" t="s">
         <v>151</v>
@@ -5627,13 +5627,13 @@
         <v>153</v>
       </c>
       <c r="B175" s="2">
-        <v>45993.42930555555</v>
+        <v>45993.47211805556</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D175" s="2">
-        <v>45993.82324074074</v>
+        <v>45993.69221064815</v>
       </c>
       <c r="E175" s="2" t="s">
         <v>10</v>
@@ -5642,7 +5642,7 @@
         <v>150</v>
       </c>
       <c r="G175" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H175" s="2" t="s">
         <v>151</v>
@@ -5650,16 +5650,16 @@
     </row>
     <row r="176" spans="1:8">
       <c r="A176" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B176" s="2">
-        <v>45992.87222222222</v>
+        <v>45993.34152777777</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D176" s="2">
-        <v>45992.87225694444</v>
+        <v>45993.58498842592</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>10</v>
@@ -5668,7 +5668,7 @@
         <v>150</v>
       </c>
       <c r="G176" s="2">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H176" s="2" t="s">
         <v>151</v>
@@ -5676,16 +5676,16 @@
     </row>
     <row r="177" spans="1:8">
       <c r="A177" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B177" s="2">
-        <v>45993.41944444444</v>
+        <v>45992.89799768518</v>
       </c>
       <c r="C177" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D177" s="2">
-        <v>45993.82296296296</v>
+        <v>45992.89809027778</v>
       </c>
       <c r="E177" s="2" t="s">
         <v>10</v>
@@ -5694,7 +5694,7 @@
         <v>150</v>
       </c>
       <c r="G177" s="2">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H177" s="2" t="s">
         <v>151</v>
@@ -5705,13 +5705,13 @@
         <v>156</v>
       </c>
       <c r="B178" s="2">
-        <v>45993.58287037037</v>
+        <v>45992.40159722222</v>
       </c>
       <c r="C178" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D178" s="2">
-        <v>45993.91707175926</v>
+        <v>45992.67126157408</v>
       </c>
       <c r="E178" s="2" t="s">
         <v>10</v>
@@ -5720,7 +5720,7 @@
         <v>157</v>
       </c>
       <c r="G178" s="2">
-        <v>24</v>
+        <v>15.16</v>
       </c>
       <c r="H178" s="2" t="s">
         <v>158</v>
@@ -5731,22 +5731,22 @@
         <v>159</v>
       </c>
       <c r="B179" s="2">
-        <v>45993.39545138889</v>
+        <v>45992.33333333334</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D179" s="2">
-        <v>45993.68545138889</v>
+        <v>45992.33333333334</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F179" s="2" t="s">
         <v>157</v>
       </c>
       <c r="G179" s="2">
-        <v>15.16</v>
+        <v>13.65</v>
       </c>
       <c r="H179" s="2" t="s">
         <v>158</v>
@@ -5754,16 +5754,16 @@
     </row>
     <row r="180" spans="1:8">
       <c r="A180" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B180" s="2">
-        <v>45992.40159722222</v>
+        <v>45992.33592592592</v>
       </c>
       <c r="C180" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D180" s="2">
-        <v>45992.67126157408</v>
+        <v>45992.69883101852</v>
       </c>
       <c r="E180" s="2" t="s">
         <v>10</v>
@@ -5772,7 +5772,7 @@
         <v>157</v>
       </c>
       <c r="G180" s="2">
-        <v>15.16</v>
+        <v>15</v>
       </c>
       <c r="H180" s="2" t="s">
         <v>158</v>
@@ -5780,16 +5780,16 @@
     </row>
     <row r="181" spans="1:8">
       <c r="A181" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B181" s="2">
-        <v>45993.32638888889</v>
+        <v>45992.58358796296</v>
       </c>
       <c r="C181" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D181" s="2">
-        <v>45993.58686342592</v>
+        <v>45992.89682870371</v>
       </c>
       <c r="E181" s="2" t="s">
         <v>10</v>
@@ -5798,7 +5798,7 @@
         <v>157</v>
       </c>
       <c r="G181" s="2">
-        <v>23.69</v>
+        <v>22</v>
       </c>
       <c r="H181" s="2" t="s">
         <v>158</v>
@@ -5806,16 +5806,16 @@
     </row>
     <row r="182" spans="1:8">
       <c r="A182" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B182" s="2">
-        <v>45992.32685185185</v>
+        <v>45993.5765625</v>
       </c>
       <c r="C182" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D182" s="2">
-        <v>45992.67736111111</v>
+        <v>45993.91775462963</v>
       </c>
       <c r="E182" s="2" t="s">
         <v>10</v>
@@ -5824,7 +5824,7 @@
         <v>157</v>
       </c>
       <c r="G182" s="2">
-        <v>23.69</v>
+        <v>22</v>
       </c>
       <c r="H182" s="2" t="s">
         <v>158</v>
@@ -5832,16 +5832,16 @@
     </row>
     <row r="183" spans="1:8">
       <c r="A183" s="2" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B183" s="2">
-        <v>45992.58297453704</v>
+        <v>45992.71581018518</v>
       </c>
       <c r="C183" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D183" s="2">
-        <v>45992.89854166667</v>
+        <v>45992.72916666666</v>
       </c>
       <c r="E183" s="2" t="s">
         <v>10</v>
@@ -5850,7 +5850,7 @@
         <v>157</v>
       </c>
       <c r="G183" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H183" s="2" t="s">
         <v>158</v>
@@ -5858,19 +5858,19 @@
     </row>
     <row r="184" spans="1:8">
       <c r="A184" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B184" s="2">
-        <v>45993.37516203704</v>
+        <v>45993.33333333334</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D184" s="2">
-        <v>45993.6992824074</v>
+        <v>45993.33333333334</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F184" s="2" t="s">
         <v>157</v>
@@ -5884,21 +5884,25 @@
     </row>
     <row r="185" spans="1:8">
       <c r="A185" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B185" s="2">
-        <v>45992.31797453704</v>
+        <v>45993.37694444445</v>
       </c>
       <c r="C185" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D185" s="2"/>
-      <c r="E185" s="2"/>
+      <c r="D185" s="2">
+        <v>45993.72078703704</v>
+      </c>
+      <c r="E185" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="F185" s="2" t="s">
         <v>157</v>
       </c>
       <c r="G185" s="2">
-        <v>20</v>
+        <v>13.65</v>
       </c>
       <c r="H185" s="2" t="s">
         <v>158</v>
@@ -5906,16 +5910,16 @@
     </row>
     <row r="186" spans="1:8">
       <c r="A186" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B186" s="2">
-        <v>45992.58358796296</v>
+        <v>45992.3703587963</v>
       </c>
       <c r="C186" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D186" s="2">
-        <v>45992.89682870371</v>
+        <v>45992.69907407407</v>
       </c>
       <c r="E186" s="2" t="s">
         <v>10</v>
@@ -5932,25 +5936,21 @@
     </row>
     <row r="187" spans="1:8">
       <c r="A187" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B187" s="2">
-        <v>45993.5765625</v>
+        <v>45992.6641087963</v>
       </c>
       <c r="C187" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D187" s="2">
-        <v>45993.91775462963</v>
-      </c>
-      <c r="E187" s="2" t="s">
-        <v>10</v>
-      </c>
+      <c r="D187" s="2"/>
+      <c r="E187" s="2"/>
       <c r="F187" s="2" t="s">
         <v>157</v>
       </c>
       <c r="G187" s="2">
-        <v>22</v>
+        <v>13.65</v>
       </c>
       <c r="H187" s="2" t="s">
         <v>158</v>
@@ -5958,25 +5958,25 @@
     </row>
     <row r="188" spans="1:8">
       <c r="A188" s="2" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
       <c r="B188" s="2">
-        <v>45993.57520833334</v>
+        <v>45993.39545138889</v>
       </c>
       <c r="C188" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D188" s="2">
-        <v>45993.80771990741</v>
+        <v>45993.68545138889</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="F188" s="2" t="s">
         <v>157</v>
       </c>
       <c r="G188" s="2">
-        <v>24</v>
+        <v>15.16</v>
       </c>
       <c r="H188" s="2" t="s">
         <v>158</v>
@@ -5984,25 +5984,25 @@
     </row>
     <row r="189" spans="1:8">
       <c r="A189" s="2" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="B189" s="2">
-        <v>45993.33333333334</v>
+        <v>45992.36230324074</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D189" s="2">
-        <v>45993.33333333334</v>
+        <v>45992.68001157408</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F189" s="2" t="s">
         <v>157</v>
       </c>
       <c r="G189" s="2">
-        <v>13.65</v>
+        <v>21</v>
       </c>
       <c r="H189" s="2" t="s">
         <v>158</v>
@@ -6010,16 +6010,16 @@
     </row>
     <row r="190" spans="1:8">
       <c r="A190" s="2" t="s">
-        <v>165</v>
+        <v>148</v>
       </c>
       <c r="B190" s="2">
-        <v>45993.37694444445</v>
+        <v>45993.33579861111</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D190" s="2">
-        <v>45993.72078703704</v>
+        <v>45993.64005787037</v>
       </c>
       <c r="E190" s="2" t="s">
         <v>10</v>
@@ -6028,7 +6028,7 @@
         <v>157</v>
       </c>
       <c r="G190" s="2">
-        <v>13.65</v>
+        <v>19</v>
       </c>
       <c r="H190" s="2" t="s">
         <v>158</v>
@@ -6036,16 +6036,16 @@
     </row>
     <row r="191" spans="1:8">
       <c r="A191" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B191" s="2">
-        <v>45992.3703587963</v>
+        <v>45992.58297453704</v>
       </c>
       <c r="C191" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D191" s="2">
-        <v>45992.69907407407</v>
+        <v>45992.89854166667</v>
       </c>
       <c r="E191" s="2" t="s">
         <v>10</v>
@@ -6054,7 +6054,7 @@
         <v>157</v>
       </c>
       <c r="G191" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H191" s="2" t="s">
         <v>158</v>
@@ -6062,16 +6062,16 @@
     </row>
     <row r="192" spans="1:8">
       <c r="A192" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B192" s="2">
-        <v>45992.71581018518</v>
+        <v>45993.58287037037</v>
       </c>
       <c r="C192" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D192" s="2">
-        <v>45992.72916666666</v>
+        <v>45993.91707175926</v>
       </c>
       <c r="E192" s="2" t="s">
         <v>10</v>
@@ -6080,7 +6080,7 @@
         <v>157</v>
       </c>
       <c r="G192" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H192" s="2" t="s">
         <v>158</v>
@@ -6088,16 +6088,16 @@
     </row>
     <row r="193" spans="1:8">
       <c r="A193" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B193" s="2">
-        <v>45992.33592592592</v>
+        <v>45992.32685185185</v>
       </c>
       <c r="C193" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D193" s="2">
-        <v>45992.69883101852</v>
+        <v>45992.67736111111</v>
       </c>
       <c r="E193" s="2" t="s">
         <v>10</v>
@@ -6106,7 +6106,7 @@
         <v>157</v>
       </c>
       <c r="G193" s="2">
-        <v>15</v>
+        <v>23.69</v>
       </c>
       <c r="H193" s="2" t="s">
         <v>158</v>
@@ -6114,25 +6114,25 @@
     </row>
     <row r="194" spans="1:8">
       <c r="A194" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B194" s="2">
-        <v>45992.33333333334</v>
+        <v>45993.32638888889</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D194" s="2">
-        <v>45992.33333333334</v>
+        <v>45993.58686342592</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F194" s="2" t="s">
         <v>157</v>
       </c>
       <c r="G194" s="2">
-        <v>13.65</v>
+        <v>23.69</v>
       </c>
       <c r="H194" s="2" t="s">
         <v>158</v>
@@ -6140,62 +6140,62 @@
     </row>
     <row r="195" spans="1:8">
       <c r="A195" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B195" s="2">
-        <v>45993.69541666667</v>
+        <v>45992.64875</v>
       </c>
       <c r="C195" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D195" s="2">
-        <v>45993.9084375</v>
-      </c>
-      <c r="E195" s="2" t="s">
-        <v>10</v>
-      </c>
+      <c r="D195" s="2"/>
+      <c r="E195" s="2"/>
       <c r="F195" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="G195" s="2">
-        <v>13.65</v>
-      </c>
+      <c r="G195" s="2"/>
       <c r="H195" s="2" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="196" spans="1:8">
       <c r="A196" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B196" s="2">
-        <v>45992.64875</v>
+        <v>45993.69541666667</v>
       </c>
       <c r="C196" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D196" s="2"/>
-      <c r="E196" s="2"/>
+      <c r="D196" s="2">
+        <v>45993.9084375</v>
+      </c>
+      <c r="E196" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="F196" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="G196" s="2"/>
+      <c r="G196" s="2">
+        <v>13.65</v>
+      </c>
       <c r="H196" s="2" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="197" spans="1:8">
       <c r="A197" s="2" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="B197" s="2">
-        <v>45993.33579861111</v>
+        <v>45992.58185185185</v>
       </c>
       <c r="C197" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D197" s="2">
-        <v>45993.64005787037</v>
+        <v>45992.8978125</v>
       </c>
       <c r="E197" s="2" t="s">
         <v>10</v>
@@ -6204,7 +6204,7 @@
         <v>157</v>
       </c>
       <c r="G197" s="2">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="H197" s="2" t="s">
         <v>158</v>
@@ -6212,16 +6212,16 @@
     </row>
     <row r="198" spans="1:8">
       <c r="A198" s="2" t="s">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="B198" s="2">
-        <v>45992.58185185185</v>
+        <v>45992.37811342593</v>
       </c>
       <c r="C198" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D198" s="2">
-        <v>45992.8978125</v>
+        <v>45992.69790509259</v>
       </c>
       <c r="E198" s="2" t="s">
         <v>10</v>
@@ -6230,7 +6230,7 @@
         <v>157</v>
       </c>
       <c r="G198" s="2">
-        <v>0</v>
+        <v>13.65</v>
       </c>
       <c r="H198" s="2" t="s">
         <v>158</v>
@@ -6238,16 +6238,16 @@
     </row>
     <row r="199" spans="1:8">
       <c r="A199" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B199" s="2">
-        <v>45993.62489583333</v>
+        <v>45993.37516203704</v>
       </c>
       <c r="C199" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D199" s="2">
-        <v>45993.90871527778</v>
+        <v>45993.6992824074</v>
       </c>
       <c r="E199" s="2" t="s">
         <v>10</v>
@@ -6264,25 +6264,21 @@
     </row>
     <row r="200" spans="1:8">
       <c r="A200" s="2" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="B200" s="2">
-        <v>45992.36230324074</v>
+        <v>45992.31797453704</v>
       </c>
       <c r="C200" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D200" s="2">
-        <v>45992.68001157408</v>
-      </c>
-      <c r="E200" s="2" t="s">
-        <v>10</v>
-      </c>
+      <c r="D200" s="2"/>
+      <c r="E200" s="2"/>
       <c r="F200" s="2" t="s">
         <v>157</v>
       </c>
       <c r="G200" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H200" s="2" t="s">
         <v>158</v>
@@ -6290,16 +6286,16 @@
     </row>
     <row r="201" spans="1:8">
       <c r="A201" s="2" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="B201" s="2">
-        <v>45992.37811342593</v>
+        <v>45993.62489583333</v>
       </c>
       <c r="C201" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D201" s="2">
-        <v>45992.69790509259</v>
+        <v>45993.90871527778</v>
       </c>
       <c r="E201" s="2" t="s">
         <v>10</v>
@@ -6316,21 +6312,25 @@
     </row>
     <row r="202" spans="1:8">
       <c r="A202" s="2" t="s">
-        <v>171</v>
+        <v>134</v>
       </c>
       <c r="B202" s="2">
-        <v>45992.6641087963</v>
+        <v>45993.57520833334</v>
       </c>
       <c r="C202" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D202" s="2"/>
-      <c r="E202" s="2"/>
+      <c r="D202" s="2">
+        <v>45993.80771990741</v>
+      </c>
+      <c r="E202" s="2" t="s">
+        <v>91</v>
+      </c>
       <c r="F202" s="2" t="s">
         <v>157</v>
       </c>
       <c r="G202" s="2">
-        <v>13.65</v>
+        <v>24</v>
       </c>
       <c r="H202" s="2" t="s">
         <v>158</v>
@@ -6367,13 +6367,13 @@
         <v>174</v>
       </c>
       <c r="B204" s="2">
-        <v>45993.95416666667</v>
+        <v>45992.24747685185</v>
       </c>
       <c r="C204" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D204" s="2">
-        <v>45994.29306712963</v>
+        <v>45992.64570601852</v>
       </c>
       <c r="E204" s="2" t="s">
         <v>10</v>
@@ -6382,7 +6382,7 @@
         <v>175</v>
       </c>
       <c r="G204" s="2">
-        <v>18.5</v>
+        <v>24.72</v>
       </c>
       <c r="H204" s="2" t="s">
         <v>176</v>
@@ -6393,13 +6393,13 @@
         <v>177</v>
       </c>
       <c r="B205" s="2">
-        <v>45992.24747685185</v>
+        <v>45993.62380787037</v>
       </c>
       <c r="C205" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D205" s="2">
-        <v>45992.64570601852</v>
+        <v>45993.95444444445</v>
       </c>
       <c r="E205" s="2" t="s">
         <v>10</v>
@@ -6408,7 +6408,7 @@
         <v>175</v>
       </c>
       <c r="G205" s="2">
-        <v>24.72</v>
+        <v>16.5</v>
       </c>
       <c r="H205" s="2" t="s">
         <v>176</v>
@@ -6419,13 +6419,13 @@
         <v>178</v>
       </c>
       <c r="B206" s="2">
-        <v>45992.33770833333</v>
+        <v>45992.9528587963</v>
       </c>
       <c r="C206" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D206" s="2">
-        <v>45992.66642361111</v>
+        <v>45993.29563657408</v>
       </c>
       <c r="E206" s="2" t="s">
         <v>10</v>
@@ -6434,7 +6434,7 @@
         <v>175</v>
       </c>
       <c r="G206" s="2">
-        <v>15.25</v>
+        <v>18.5</v>
       </c>
       <c r="H206" s="2" t="s">
         <v>176</v>
@@ -6442,16 +6442,16 @@
     </row>
     <row r="207" spans="1:8">
       <c r="A207" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B207" s="2">
-        <v>45992.62354166667</v>
+        <v>45993.95416666667</v>
       </c>
       <c r="C207" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D207" s="2">
-        <v>45992.85416666666</v>
+        <v>45994.29306712963</v>
       </c>
       <c r="E207" s="2" t="s">
         <v>10</v>
@@ -6460,7 +6460,7 @@
         <v>175</v>
       </c>
       <c r="G207" s="2">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="H207" s="2" t="s">
         <v>176</v>
@@ -6471,13 +6471,13 @@
         <v>179</v>
       </c>
       <c r="B208" s="2">
-        <v>45993.62380787037</v>
+        <v>45992.33770833333</v>
       </c>
       <c r="C208" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D208" s="2">
-        <v>45993.95444444445</v>
+        <v>45992.66642361111</v>
       </c>
       <c r="E208" s="2" t="s">
         <v>10</v>
@@ -6486,7 +6486,7 @@
         <v>175</v>
       </c>
       <c r="G208" s="2">
-        <v>16.5</v>
+        <v>15.25</v>
       </c>
       <c r="H208" s="2" t="s">
         <v>176</v>
@@ -6497,13 +6497,13 @@
         <v>180</v>
       </c>
       <c r="B209" s="2">
-        <v>45993.29008101852</v>
+        <v>45993.62984953704</v>
       </c>
       <c r="C209" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D209" s="2">
-        <v>45993.58872685185</v>
+        <v>45993.95290509259</v>
       </c>
       <c r="E209" s="2" t="s">
         <v>10</v>
@@ -6512,7 +6512,7 @@
         <v>175</v>
       </c>
       <c r="G209" s="2">
-        <v>16.5</v>
+        <v>17.25</v>
       </c>
       <c r="H209" s="2" t="s">
         <v>176</v>
@@ -6523,22 +6523,22 @@
         <v>181</v>
       </c>
       <c r="B210" s="2">
-        <v>45992.53841435185</v>
+        <v>45992.33333333334</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D210" s="2">
-        <v>45992.95521990741</v>
+        <v>45992.33333333334</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F210" s="2" t="s">
         <v>175</v>
       </c>
       <c r="G210" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H210" s="2" t="s">
         <v>176</v>
@@ -6549,22 +6549,22 @@
         <v>181</v>
       </c>
       <c r="B211" s="2">
-        <v>45993.39311342593</v>
+        <v>45993.33333333334</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D211" s="2">
-        <v>45993.46118055555</v>
+        <v>45993.33333333334</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F211" s="2" t="s">
         <v>175</v>
       </c>
       <c r="G211" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H211" s="2" t="s">
         <v>176</v>
@@ -6572,25 +6572,25 @@
     </row>
     <row r="212" spans="1:8">
       <c r="A212" s="2" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B212" s="2">
-        <v>45993.5</v>
+        <v>45992.62354166667</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D212" s="2">
-        <v>45993.5</v>
+        <v>45992.85416666666</v>
       </c>
       <c r="E212" s="2" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F212" s="2" t="s">
         <v>175</v>
       </c>
       <c r="G212" s="2">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="H212" s="2" t="s">
         <v>176</v>
@@ -6601,22 +6601,22 @@
         <v>182</v>
       </c>
       <c r="B213" s="2">
-        <v>45992.33333333334</v>
+        <v>45993.29008101852</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D213" s="2">
-        <v>45992.33333333334</v>
+        <v>45993.58872685185</v>
       </c>
       <c r="E213" s="2" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F213" s="2" t="s">
         <v>175</v>
       </c>
       <c r="G213" s="2">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="H213" s="2" t="s">
         <v>176</v>
@@ -6624,25 +6624,25 @@
     </row>
     <row r="214" spans="1:8">
       <c r="A214" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B214" s="2">
-        <v>45993.33333333334</v>
+        <v>45992.53841435185</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D214" s="2">
-        <v>45993.33333333334</v>
+        <v>45992.95521990741</v>
       </c>
       <c r="E214" s="2" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F214" s="2" t="s">
         <v>175</v>
       </c>
       <c r="G214" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H214" s="2" t="s">
         <v>176</v>
@@ -6650,16 +6650,16 @@
     </row>
     <row r="215" spans="1:8">
       <c r="A215" s="2" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="B215" s="2">
-        <v>45992.9528587963</v>
+        <v>45993.39311342593</v>
       </c>
       <c r="C215" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D215" s="2">
-        <v>45993.29563657408</v>
+        <v>45993.46118055555</v>
       </c>
       <c r="E215" s="2" t="s">
         <v>10</v>
@@ -6668,7 +6668,7 @@
         <v>175</v>
       </c>
       <c r="G215" s="2">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="H215" s="2" t="s">
         <v>176</v>
@@ -6679,22 +6679,22 @@
         <v>183</v>
       </c>
       <c r="B216" s="2">
-        <v>45993.62984953704</v>
+        <v>45993.5</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D216" s="2">
-        <v>45993.95290509259</v>
+        <v>45993.5</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F216" s="2" t="s">
         <v>175</v>
       </c>
       <c r="G216" s="2">
-        <v>17.25</v>
+        <v>20</v>
       </c>
       <c r="H216" s="2" t="s">
         <v>176</v>
@@ -6705,13 +6705,13 @@
         <v>184</v>
       </c>
       <c r="B217" s="2">
-        <v>45992.30857638889</v>
+        <v>45993.33015046296</v>
       </c>
       <c r="C217" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D217" s="2">
-        <v>45992.63498842593</v>
+        <v>45993.49803240741</v>
       </c>
       <c r="E217" s="2" t="s">
         <v>10</v>
@@ -6720,7 +6720,7 @@
         <v>185</v>
       </c>
       <c r="G217" s="2">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="H217" s="2" t="s">
         <v>186</v>
@@ -6731,13 +6731,13 @@
         <v>187</v>
       </c>
       <c r="B218" s="2">
-        <v>45993.36116898148</v>
+        <v>45993.30981481481</v>
       </c>
       <c r="C218" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D218" s="2">
-        <v>45993.64501157407</v>
+        <v>45993.67152777778</v>
       </c>
       <c r="E218" s="2" t="s">
         <v>10</v>
@@ -6746,7 +6746,7 @@
         <v>185</v>
       </c>
       <c r="G218" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H218" s="2" t="s">
         <v>186</v>
@@ -6754,16 +6754,16 @@
     </row>
     <row r="219" spans="1:8">
       <c r="A219" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B219" s="2">
-        <v>45993.40340277777</v>
+        <v>45992.30857638889</v>
       </c>
       <c r="C219" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D219" s="2">
-        <v>45993.67043981481</v>
+        <v>45992.63498842593</v>
       </c>
       <c r="E219" s="2" t="s">
         <v>10</v>
@@ -6772,7 +6772,7 @@
         <v>185</v>
       </c>
       <c r="G219" s="2">
-        <v>16.61</v>
+        <v>16</v>
       </c>
       <c r="H219" s="2" t="s">
         <v>186</v>
@@ -6783,13 +6783,13 @@
         <v>188</v>
       </c>
       <c r="B220" s="2">
-        <v>45992.39903935185</v>
+        <v>45993.36116898148</v>
       </c>
       <c r="C220" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D220" s="2">
-        <v>45992.78083333333</v>
+        <v>45993.64501157407</v>
       </c>
       <c r="E220" s="2" t="s">
         <v>10</v>
@@ -6798,7 +6798,7 @@
         <v>185</v>
       </c>
       <c r="G220" s="2">
-        <v>16.61</v>
+        <v>20</v>
       </c>
       <c r="H220" s="2" t="s">
         <v>186</v>
@@ -6809,13 +6809,13 @@
         <v>189</v>
       </c>
       <c r="B221" s="2">
-        <v>45993.33015046296</v>
+        <v>45993.40340277777</v>
       </c>
       <c r="C221" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D221" s="2">
-        <v>45993.49803240741</v>
+        <v>45993.67043981481</v>
       </c>
       <c r="E221" s="2" t="s">
         <v>10</v>
@@ -6824,7 +6824,7 @@
         <v>185</v>
       </c>
       <c r="G221" s="2">
-        <v>14.5</v>
+        <v>16.61</v>
       </c>
       <c r="H221" s="2" t="s">
         <v>186</v>
@@ -6835,13 +6835,13 @@
         <v>190</v>
       </c>
       <c r="B222" s="2">
-        <v>45993.47619212963</v>
+        <v>45992.39877314815</v>
       </c>
       <c r="C222" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D222" s="2">
-        <v>45993.66888888889</v>
+        <v>45992.78104166667</v>
       </c>
       <c r="E222" s="2" t="s">
         <v>10</v>
@@ -6861,13 +6861,13 @@
         <v>190</v>
       </c>
       <c r="B223" s="2">
-        <v>45992.39877314815</v>
+        <v>45993.47619212963</v>
       </c>
       <c r="C223" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D223" s="2">
-        <v>45992.78104166667</v>
+        <v>45993.66888888889</v>
       </c>
       <c r="E223" s="2" t="s">
         <v>10</v>
@@ -6884,16 +6884,16 @@
     </row>
     <row r="224" spans="1:8">
       <c r="A224" s="2" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="B224" s="2">
-        <v>45993.30981481481</v>
+        <v>45992.39903935185</v>
       </c>
       <c r="C224" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D224" s="2">
-        <v>45993.67152777778</v>
+        <v>45992.78083333333</v>
       </c>
       <c r="E224" s="2" t="s">
         <v>10</v>
@@ -6902,7 +6902,7 @@
         <v>185</v>
       </c>
       <c r="G224" s="2">
-        <v>16</v>
+        <v>16.61</v>
       </c>
       <c r="H224" s="2" t="s">
         <v>186</v>
@@ -6962,13 +6962,13 @@
     </row>
     <row r="227" spans="1:8">
       <c r="A227" s="2" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="B227" s="2">
         <v>45992.50498842593</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D227" s="2">
         <v>45992.67591435185</v>
@@ -6991,13 +6991,13 @@
         <v>196</v>
       </c>
       <c r="B228" s="2">
-        <v>45992.51815972223</v>
+        <v>45992.58616898148</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D228" s="2">
-        <v>45992.65887731482</v>
+        <v>45992.6752662037</v>
       </c>
       <c r="E228" s="2" t="s">
         <v>10</v>
@@ -7005,7 +7005,9 @@
       <c r="F228" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="G228" s="2"/>
+      <c r="G228" s="2">
+        <v>20</v>
+      </c>
       <c r="H228" s="2" t="s">
         <v>195</v>
       </c>
@@ -7015,13 +7017,13 @@
         <v>197</v>
       </c>
       <c r="B229" s="2">
-        <v>45992.58616898148</v>
+        <v>45992.51815972223</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D229" s="2">
-        <v>45992.6752662037</v>
+        <v>45992.65887731482</v>
       </c>
       <c r="E229" s="2" t="s">
         <v>10</v>
@@ -7029,9 +7031,7 @@
       <c r="F229" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="G229" s="2">
-        <v>20</v>
-      </c>
+      <c r="G229" s="2"/>
       <c r="H229" s="2" t="s">
         <v>195</v>
       </c>
@@ -7093,13 +7093,13 @@
         <v>202</v>
       </c>
       <c r="B232" s="2">
-        <v>45992.33006944445</v>
+        <v>45993.33853009259</v>
       </c>
       <c r="C232" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D232" s="2">
-        <v>45992.4482175926</v>
+        <v>45993.67113425926</v>
       </c>
       <c r="E232" s="2" t="s">
         <v>10</v>
@@ -7108,7 +7108,7 @@
         <v>203</v>
       </c>
       <c r="G232" s="2">
-        <v>23.49</v>
+        <v>18</v>
       </c>
       <c r="H232" s="2" t="s">
         <v>204</v>
@@ -7142,16 +7142,16 @@
     </row>
     <row r="234" spans="1:8">
       <c r="A234" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B234" s="2">
-        <v>45993.34314814815</v>
+        <v>45992.33006944445</v>
       </c>
       <c r="C234" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D234" s="2">
-        <v>45993.66737268519</v>
+        <v>45992.4482175926</v>
       </c>
       <c r="E234" s="2" t="s">
         <v>10</v>
@@ -7160,7 +7160,7 @@
         <v>203</v>
       </c>
       <c r="G234" s="2">
-        <v>20</v>
+        <v>23.49</v>
       </c>
       <c r="H234" s="2" t="s">
         <v>204</v>
@@ -7168,16 +7168,16 @@
     </row>
     <row r="235" spans="1:8">
       <c r="A235" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B235" s="2">
-        <v>45992.34174768518</v>
+        <v>45993.34314814815</v>
       </c>
       <c r="C235" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D235" s="2">
-        <v>45992.67616898148</v>
+        <v>45993.66737268519</v>
       </c>
       <c r="E235" s="2" t="s">
         <v>10</v>
@@ -7186,7 +7186,7 @@
         <v>203</v>
       </c>
       <c r="G235" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H235" s="2" t="s">
         <v>204</v>
@@ -7194,7 +7194,7 @@
     </row>
     <row r="236" spans="1:8">
       <c r="A236" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B236" s="2">
         <v>45993.35118055555</v>
@@ -7223,13 +7223,13 @@
         <v>207</v>
       </c>
       <c r="B237" s="2">
-        <v>45992.34165509259</v>
+        <v>45992.34174768518</v>
       </c>
       <c r="C237" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D237" s="2">
-        <v>45992.66502314815</v>
+        <v>45992.67616898148</v>
       </c>
       <c r="E237" s="2" t="s">
         <v>10</v>
@@ -7238,7 +7238,7 @@
         <v>203</v>
       </c>
       <c r="G237" s="2">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H237" s="2" t="s">
         <v>204</v>
@@ -7272,16 +7272,16 @@
     </row>
     <row r="239" spans="1:8">
       <c r="A239" s="2" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="B239" s="2">
-        <v>45993.33853009259</v>
+        <v>45992.34165509259</v>
       </c>
       <c r="C239" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D239" s="2">
-        <v>45993.67113425926</v>
+        <v>45992.66502314815</v>
       </c>
       <c r="E239" s="2" t="s">
         <v>10</v>
@@ -7298,54 +7298,54 @@
     </row>
     <row r="240" spans="1:8">
       <c r="A240" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B240" s="2">
+        <v>45992.29037037037</v>
+      </c>
+      <c r="C240" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D240" s="2">
+        <v>45992.55635416666</v>
+      </c>
+      <c r="E240" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F240" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="B240" s="2">
-        <v>45993.33333333334</v>
-      </c>
-      <c r="C240" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D240" s="2">
-        <v>45993.33333333334</v>
-      </c>
-      <c r="E240" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F240" s="2" t="s">
+      <c r="G240" s="2">
+        <v>20</v>
+      </c>
+      <c r="H240" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="G240" s="2">
-        <v>18.5</v>
-      </c>
-      <c r="H240" s="2" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="241" spans="1:8">
       <c r="A241" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B241" s="2">
-        <v>45992.3484375</v>
+        <v>45993.33415509259</v>
       </c>
       <c r="C241" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D241" s="2">
-        <v>45992.49106481481</v>
+        <v>45993.52702546296</v>
       </c>
       <c r="E241" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F241" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G241" s="2">
         <v>18</v>
       </c>
       <c r="H241" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="242" spans="1:8">
@@ -7353,103 +7353,103 @@
         <v>212</v>
       </c>
       <c r="B242" s="2">
-        <v>45993.33415509259</v>
+        <v>45992.29172453703</v>
       </c>
       <c r="C242" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D242" s="2">
-        <v>45993.52702546296</v>
+        <v>45992.5741087963</v>
       </c>
       <c r="E242" s="2" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="F242" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G242" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="H242" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="G242" s="2">
-        <v>18</v>
-      </c>
-      <c r="H242" s="2" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="243" spans="1:8">
       <c r="A243" s="2" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="B243" s="2">
-        <v>45992.29037037037</v>
+        <v>45993.33333333334</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D243" s="2">
-        <v>45992.55635416666</v>
+        <v>45993.33333333334</v>
       </c>
       <c r="E243" s="2" t="s">
-        <v>91</v>
+        <v>15</v>
       </c>
       <c r="F243" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G243" s="2">
+        <v>18.5</v>
+      </c>
+      <c r="H243" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="G243" s="2">
-        <v>20</v>
-      </c>
-      <c r="H243" s="2" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="244" spans="1:8">
       <c r="A244" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B244" s="2">
         <v>45992.33333333334</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D244" s="2">
         <v>45992.33333333334</v>
       </c>
       <c r="E244" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F244" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G244" s="2">
         <v>18.5</v>
       </c>
       <c r="H244" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="245" spans="1:8">
       <c r="A245" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B245" s="2">
-        <v>45992.5</v>
+        <v>45992.3484375</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D245" s="2">
-        <v>45992.625</v>
+        <v>45992.49106481481</v>
       </c>
       <c r="E245" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F245" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G245" s="2">
+        <v>18</v>
+      </c>
+      <c r="H245" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="G245" s="2">
-        <v>24</v>
-      </c>
-      <c r="H245" s="2" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="246" spans="1:8">
@@ -7457,129 +7457,129 @@
         <v>214</v>
       </c>
       <c r="B246" s="2">
-        <v>45992.29172453703</v>
+        <v>45992.26368055555</v>
       </c>
       <c r="C246" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D246" s="2">
-        <v>45992.5741087963</v>
+        <v>45992.48032407407</v>
       </c>
       <c r="E246" s="2" t="s">
         <v>91</v>
       </c>
       <c r="F246" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G246" s="2">
+        <v>24</v>
+      </c>
+      <c r="H246" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="G246" s="2">
-        <v>20.5</v>
-      </c>
-      <c r="H246" s="2" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="247" spans="1:8">
       <c r="A247" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B247" s="2">
-        <v>45992.59509259259</v>
+        <v>45993.54071759259</v>
       </c>
       <c r="C247" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D247" s="2">
+        <v>45993.69123842593</v>
+      </c>
+      <c r="E247" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F247" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G247" s="2">
         <v>17</v>
       </c>
-      <c r="D247" s="2">
-        <v>45992.69358796296</v>
-      </c>
-      <c r="E247" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F247" s="2" t="s">
+      <c r="H247" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="G247" s="2">
-        <v>20.5</v>
-      </c>
-      <c r="H247" s="2" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="248" spans="1:8">
       <c r="A248" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B248" s="2">
-        <v>45993.33784722222</v>
+        <v>45992.59509259259</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D248" s="2">
-        <v>45993.5262037037</v>
+        <v>45992.69358796296</v>
       </c>
       <c r="E248" s="2" t="s">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="F248" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G248" s="2">
         <v>20.5</v>
       </c>
       <c r="H248" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="249" spans="1:8">
       <c r="A249" s="2" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B249" s="2">
-        <v>45993.32947916666</v>
+        <v>45993.33784722222</v>
       </c>
       <c r="C249" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D249" s="2">
-        <v>45993.51585648148</v>
+        <v>45993.5262037037</v>
       </c>
       <c r="E249" s="2" t="s">
         <v>91</v>
       </c>
       <c r="F249" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G249" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="H249" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="G249" s="2">
-        <v>17</v>
-      </c>
-      <c r="H249" s="2" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="250" spans="1:8">
       <c r="A250" s="2" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B250" s="2">
-        <v>45993.54071759259</v>
+        <v>45993.54539351852</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D250" s="2">
-        <v>45993.69123842593</v>
+        <v>45993.69030092593</v>
       </c>
       <c r="E250" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F250" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G250" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="H250" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="G250" s="2">
-        <v>17</v>
-      </c>
-      <c r="H250" s="2" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="251" spans="1:8">
@@ -7587,78 +7587,82 @@
         <v>216</v>
       </c>
       <c r="B251" s="2">
-        <v>45992.32515046297</v>
+        <v>45993.33489583333</v>
       </c>
       <c r="C251" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D251" s="2">
-        <v>45992.55366898148</v>
+        <v>45993.46734953704</v>
       </c>
       <c r="E251" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F251" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G251" s="2">
+        <v>15</v>
+      </c>
+      <c r="H251" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="G251" s="2">
-        <v>16</v>
-      </c>
-      <c r="H251" s="2" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="252" spans="1:8">
       <c r="A252" s="2" t="s">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="B252" s="2">
-        <v>45992.33572916667</v>
+        <v>45993.32947916666</v>
       </c>
       <c r="C252" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D252" s="2">
-        <v>45992.49737268518</v>
+        <v>45993.51585648148</v>
       </c>
       <c r="E252" s="2" t="s">
         <v>91</v>
       </c>
       <c r="F252" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G252" s="2">
+        <v>17</v>
+      </c>
+      <c r="H252" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="G252" s="2"/>
-      <c r="H252" s="2" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="253" spans="1:8">
       <c r="A253" s="2" t="s">
-        <v>196</v>
+        <v>101</v>
       </c>
       <c r="B253" s="2">
-        <v>45993.33071759259</v>
+        <v>45993.33440972222</v>
       </c>
       <c r="C253" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D253" s="2">
-        <v>45993.5552662037</v>
+        <v>45993.49506944444</v>
       </c>
       <c r="E253" s="2" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="F253" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G253" s="2">
+        <v>16</v>
+      </c>
+      <c r="H253" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="G253" s="2"/>
-      <c r="H253" s="2" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="254" spans="1:8">
       <c r="A254" s="2" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="B254" s="2">
         <v>45992.33586805555</v>
@@ -7673,91 +7677,87 @@
         <v>91</v>
       </c>
       <c r="F254" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G254" s="2">
         <v>16</v>
       </c>
       <c r="H254" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="255" spans="1:8">
       <c r="A255" s="2" t="s">
-        <v>92</v>
+        <v>197</v>
       </c>
       <c r="B255" s="2">
-        <v>45993.33440972222</v>
+        <v>45993.33071759259</v>
       </c>
       <c r="C255" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D255" s="2">
-        <v>45993.49506944444</v>
+        <v>45993.5552662037</v>
       </c>
       <c r="E255" s="2" t="s">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="F255" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G255" s="2"/>
+      <c r="H255" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="G255" s="2">
-        <v>16</v>
-      </c>
-      <c r="H255" s="2" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="256" spans="1:8">
       <c r="A256" s="2" t="s">
-        <v>217</v>
+        <v>197</v>
       </c>
       <c r="B256" s="2">
-        <v>45993.33489583333</v>
+        <v>45992.33572916667</v>
       </c>
       <c r="C256" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D256" s="2">
-        <v>45993.46734953704</v>
+        <v>45992.49737268518</v>
       </c>
       <c r="E256" s="2" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="F256" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G256" s="2"/>
+      <c r="H256" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="G256" s="2">
-        <v>15</v>
-      </c>
-      <c r="H256" s="2" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="257" spans="1:8">
       <c r="A257" s="2" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B257" s="2">
-        <v>45992.26368055555</v>
+        <v>45992.32515046297</v>
       </c>
       <c r="C257" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D257" s="2">
-        <v>45992.48032407407</v>
+        <v>45992.55366898148</v>
       </c>
       <c r="E257" s="2" t="s">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="F257" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G257" s="2">
+        <v>16</v>
+      </c>
+      <c r="H257" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="G257" s="2">
-        <v>24</v>
-      </c>
-      <c r="H257" s="2" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="258" spans="1:8">
@@ -7765,25 +7765,25 @@
         <v>214</v>
       </c>
       <c r="B258" s="2">
-        <v>45993.54539351852</v>
+        <v>45992.5</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D258" s="2">
-        <v>45993.69030092593</v>
+        <v>45992.625</v>
       </c>
       <c r="E258" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F258" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G258" s="2">
+        <v>24</v>
+      </c>
+      <c r="H258" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="G258" s="2">
-        <v>20.5</v>
-      </c>
-      <c r="H258" s="2" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="259" spans="1:8">
@@ -7817,22 +7817,22 @@
         <v>221</v>
       </c>
       <c r="B260" s="2">
-        <v>45992.55232638889</v>
+        <v>45993.33430555555</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D260" s="2">
-        <v>45992.76518518518</v>
+        <v>45993.53699074074</v>
       </c>
       <c r="E260" s="2" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="F260" s="2" t="s">
         <v>222</v>
       </c>
       <c r="G260" s="2">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="H260" s="2" t="s">
         <v>223</v>
@@ -7840,25 +7840,25 @@
     </row>
     <row r="261" spans="1:8">
       <c r="A261" s="2" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B261" s="2">
-        <v>45993.27287037037</v>
+        <v>45992.55216435185</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D261" s="2">
-        <v>45993.5634375</v>
+        <v>45992.76539351852</v>
       </c>
       <c r="E261" s="2" t="s">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="F261" s="2" t="s">
         <v>222</v>
       </c>
       <c r="G261" s="2">
-        <v>17.72</v>
+        <v>23</v>
       </c>
       <c r="H261" s="2" t="s">
         <v>223</v>
@@ -7866,16 +7866,16 @@
     </row>
     <row r="262" spans="1:8">
       <c r="A262" s="2" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B262" s="2">
-        <v>45993.58417824074</v>
+        <v>45993.55827546296</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D262" s="2">
-        <v>45993.77274305555</v>
+        <v>45993.71579861111</v>
       </c>
       <c r="E262" s="2" t="s">
         <v>10</v>
@@ -7884,7 +7884,7 @@
         <v>222</v>
       </c>
       <c r="G262" s="2">
-        <v>17.72</v>
+        <v>23</v>
       </c>
       <c r="H262" s="2" t="s">
         <v>223</v>
@@ -7892,16 +7892,16 @@
     </row>
     <row r="263" spans="1:8">
       <c r="A263" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B263" s="2">
-        <v>45992.27461805556</v>
+        <v>45993.27287037037</v>
       </c>
       <c r="C263" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D263" s="2">
-        <v>45992.53001157408</v>
+        <v>45993.5634375</v>
       </c>
       <c r="E263" s="2" t="s">
         <v>91</v>
@@ -7910,7 +7910,7 @@
         <v>222</v>
       </c>
       <c r="G263" s="2">
-        <v>23</v>
+        <v>17.72</v>
       </c>
       <c r="H263" s="2" t="s">
         <v>223</v>
@@ -7918,16 +7918,16 @@
     </row>
     <row r="264" spans="1:8">
       <c r="A264" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B264" s="2">
-        <v>45992.55216435185</v>
+        <v>45993.58417824074</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D264" s="2">
-        <v>45992.76539351852</v>
+        <v>45993.77274305555</v>
       </c>
       <c r="E264" s="2" t="s">
         <v>10</v>
@@ -7936,7 +7936,7 @@
         <v>222</v>
       </c>
       <c r="G264" s="2">
-        <v>23</v>
+        <v>17.72</v>
       </c>
       <c r="H264" s="2" t="s">
         <v>223</v>
@@ -7947,13 +7947,13 @@
         <v>225</v>
       </c>
       <c r="B265" s="2">
-        <v>45993.33430555555</v>
+        <v>45992.27319444445</v>
       </c>
       <c r="C265" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D265" s="2">
-        <v>45993.53699074074</v>
+        <v>45992.53025462963</v>
       </c>
       <c r="E265" s="2" t="s">
         <v>91</v>
@@ -7962,7 +7962,7 @@
         <v>222</v>
       </c>
       <c r="G265" s="2">
-        <v>23</v>
+        <v>17.5</v>
       </c>
       <c r="H265" s="2" t="s">
         <v>223</v>
@@ -7973,13 +7973,13 @@
         <v>225</v>
       </c>
       <c r="B266" s="2">
-        <v>45993.55827546296</v>
+        <v>45992.55232638889</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D266" s="2">
-        <v>45993.71579861111</v>
+        <v>45992.76518518518</v>
       </c>
       <c r="E266" s="2" t="s">
         <v>10</v>
@@ -7988,7 +7988,7 @@
         <v>222</v>
       </c>
       <c r="G266" s="2">
-        <v>23</v>
+        <v>17.5</v>
       </c>
       <c r="H266" s="2" t="s">
         <v>223</v>
@@ -7999,13 +7999,13 @@
         <v>221</v>
       </c>
       <c r="B267" s="2">
-        <v>45992.27319444445</v>
+        <v>45992.27461805556</v>
       </c>
       <c r="C267" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D267" s="2">
-        <v>45992.53025462963</v>
+        <v>45992.53001157408</v>
       </c>
       <c r="E267" s="2" t="s">
         <v>91</v>
@@ -8014,7 +8014,7 @@
         <v>222</v>
       </c>
       <c r="G267" s="2">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="H267" s="2" t="s">
         <v>223</v>
@@ -8025,13 +8025,13 @@
         <v>226</v>
       </c>
       <c r="B268" s="2">
-        <v>45992.17318287037</v>
+        <v>45992.34172453704</v>
       </c>
       <c r="C268" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D268" s="2">
-        <v>45992.29707175926</v>
+        <v>45992.6603587963</v>
       </c>
       <c r="E268" s="2" t="s">
         <v>10</v>
@@ -8040,7 +8040,7 @@
         <v>227</v>
       </c>
       <c r="G268" s="2">
-        <v>15</v>
+        <v>19.5</v>
       </c>
       <c r="H268" s="2" t="s">
         <v>228</v>
@@ -8048,16 +8048,16 @@
     </row>
     <row r="269" spans="1:8">
       <c r="A269" s="2" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B269" s="2">
-        <v>45993.66258101852</v>
+        <v>45993.31112268518</v>
       </c>
       <c r="C269" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D269" s="2">
-        <v>45993.67274305555</v>
+        <v>45993.75378472222</v>
       </c>
       <c r="E269" s="2" t="s">
         <v>10</v>
@@ -8066,7 +8066,7 @@
         <v>227</v>
       </c>
       <c r="G269" s="2">
-        <v>20.57</v>
+        <v>19.5</v>
       </c>
       <c r="H269" s="2" t="s">
         <v>228</v>
@@ -8077,13 +8077,13 @@
         <v>229</v>
       </c>
       <c r="B270" s="2">
-        <v>45992.29688657408</v>
+        <v>45993.66258101852</v>
       </c>
       <c r="C270" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D270" s="2">
-        <v>45992.70577546296</v>
+        <v>45993.67274305555</v>
       </c>
       <c r="E270" s="2" t="s">
         <v>10</v>
@@ -8103,13 +8103,13 @@
         <v>230</v>
       </c>
       <c r="B271" s="2">
-        <v>45993.31112268518</v>
+        <v>45992.17318287037</v>
       </c>
       <c r="C271" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D271" s="2">
-        <v>45993.75378472222</v>
+        <v>45992.29707175926</v>
       </c>
       <c r="E271" s="2" t="s">
         <v>10</v>
@@ -8118,7 +8118,7 @@
         <v>227</v>
       </c>
       <c r="G271" s="2">
-        <v>19.5</v>
+        <v>15</v>
       </c>
       <c r="H271" s="2" t="s">
         <v>228</v>
@@ -8126,16 +8126,16 @@
     </row>
     <row r="272" spans="1:8">
       <c r="A272" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B272" s="2">
-        <v>45992.34172453704</v>
+        <v>45992.29688657408</v>
       </c>
       <c r="C272" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D272" s="2">
-        <v>45992.6603587963</v>
+        <v>45992.70577546296</v>
       </c>
       <c r="E272" s="2" t="s">
         <v>10</v>
@@ -8144,7 +8144,7 @@
         <v>227</v>
       </c>
       <c r="G272" s="2">
-        <v>19.5</v>
+        <v>20.57</v>
       </c>
       <c r="H272" s="2" t="s">
         <v>228</v>
@@ -8155,13 +8155,13 @@
         <v>231</v>
       </c>
       <c r="B273" s="2">
-        <v>45992.36092592592</v>
+        <v>45992.33524305555</v>
       </c>
       <c r="C273" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D273" s="2">
-        <v>45992.70349537037</v>
+        <v>45992.69309027777</v>
       </c>
       <c r="E273" s="2" t="s">
         <v>10</v>
@@ -8170,7 +8170,7 @@
         <v>232</v>
       </c>
       <c r="G273" s="2">
-        <v>23.27</v>
+        <v>20</v>
       </c>
       <c r="H273" s="2" t="s">
         <v>233</v>
@@ -8181,13 +8181,13 @@
         <v>234</v>
       </c>
       <c r="B274" s="2">
-        <v>45992.33524305555</v>
+        <v>45992.36092592592</v>
       </c>
       <c r="C274" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D274" s="2">
-        <v>45992.69309027777</v>
+        <v>45992.70349537037</v>
       </c>
       <c r="E274" s="2" t="s">
         <v>10</v>
@@ -8196,7 +8196,7 @@
         <v>232</v>
       </c>
       <c r="G274" s="2">
-        <v>20</v>
+        <v>23.27</v>
       </c>
       <c r="H274" s="2" t="s">
         <v>233</v>
@@ -8207,13 +8207,13 @@
         <v>235</v>
       </c>
       <c r="B275" s="2">
-        <v>45992.29229166666</v>
+        <v>45993.53115740741</v>
       </c>
       <c r="C275" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D275" s="2">
-        <v>45992.48096064815</v>
+        <v>45993.61241898148</v>
       </c>
       <c r="E275" s="2" t="s">
         <v>10</v>
@@ -8225,7 +8225,7 @@
         <v>18</v>
       </c>
       <c r="H275" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="276" spans="1:8">
@@ -8251,7 +8251,7 @@
         <v>16</v>
       </c>
       <c r="H276" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="277" spans="1:8">
@@ -8273,21 +8273,21 @@
         <v>16</v>
       </c>
       <c r="H277" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="278" spans="1:8">
       <c r="A278" s="2" t="s">
-        <v>238</v>
+        <v>98</v>
       </c>
       <c r="B278" s="2">
-        <v>45993.36427083334</v>
+        <v>45993.55390046296</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D278" s="2">
-        <v>45993.7037037037</v>
+        <v>45993.68125</v>
       </c>
       <c r="E278" s="2" t="s">
         <v>10</v>
@@ -8296,24 +8296,24 @@
         <v>236</v>
       </c>
       <c r="G278" s="2">
+        <v>16</v>
+      </c>
+      <c r="H278" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="H278" s="2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="279" spans="1:8">
       <c r="A279" s="2" t="s">
-        <v>107</v>
+        <v>235</v>
       </c>
       <c r="B279" s="2">
-        <v>45993.55390046296</v>
+        <v>45992.29229166666</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D279" s="2">
-        <v>45993.68125</v>
+        <v>45992.48096064815</v>
       </c>
       <c r="E279" s="2" t="s">
         <v>10</v>
@@ -8322,10 +8322,10 @@
         <v>236</v>
       </c>
       <c r="G279" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H279" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="280" spans="1:8">
@@ -8351,7 +8351,7 @@
         <v>18</v>
       </c>
       <c r="H280" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="281" spans="1:8">
@@ -8377,21 +8377,21 @@
         <v>18</v>
       </c>
       <c r="H281" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="282" spans="1:8">
       <c r="A282" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B282" s="2">
-        <v>45993.53115740741</v>
+        <v>45993.36427083334</v>
       </c>
       <c r="C282" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D282" s="2">
-        <v>45993.61241898148</v>
+        <v>45993.7037037037</v>
       </c>
       <c r="E282" s="2" t="s">
         <v>10</v>
@@ -8400,10 +8400,10 @@
         <v>236</v>
       </c>
       <c r="G282" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H282" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="283" spans="1:8">

--- a/reports/Month to Date (Actual)_Payroll.xlsx
+++ b/reports/Month to Date (Actual)_Payroll.xlsx
@@ -40,90 +40,90 @@
     <t>DepartmentTitle</t>
   </si>
   <si>
+    <t>J520</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>OD</t>
+  </si>
+  <si>
+    <t>D1010</t>
+  </si>
+  <si>
+    <t>Lift Operations</t>
+  </si>
+  <si>
+    <t>A3LM</t>
+  </si>
+  <si>
+    <t>A3JX</t>
+  </si>
+  <si>
+    <t>A2D1</t>
+  </si>
+  <si>
+    <t>A2JJ</t>
+  </si>
+  <si>
+    <t>HR</t>
+  </si>
+  <si>
+    <t>G125</t>
+  </si>
+  <si>
+    <t>A29S</t>
+  </si>
+  <si>
+    <t>A1PN</t>
+  </si>
+  <si>
+    <t>IL</t>
+  </si>
+  <si>
+    <t>A3GJ</t>
+  </si>
+  <si>
+    <t>A1ZJ</t>
+  </si>
+  <si>
     <t>A0P4</t>
   </si>
   <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>OD</t>
-  </si>
-  <si>
-    <t>D1010</t>
-  </si>
-  <si>
-    <t>Lift Operations</t>
+    <t>A3JZ</t>
+  </si>
+  <si>
+    <t>A3K1</t>
+  </si>
+  <si>
+    <t>B197</t>
   </si>
   <si>
     <t>A0HA</t>
   </si>
   <si>
-    <t>A2D1</t>
-  </si>
-  <si>
-    <t>A3JX</t>
-  </si>
-  <si>
-    <t>A3LM</t>
-  </si>
-  <si>
-    <t>J520</t>
-  </si>
-  <si>
-    <t>A1ZJ</t>
-  </si>
-  <si>
-    <t>A3K1</t>
-  </si>
-  <si>
-    <t>G125</t>
-  </si>
-  <si>
-    <t>A2JJ</t>
-  </si>
-  <si>
-    <t>HR</t>
-  </si>
-  <si>
-    <t>B197</t>
-  </si>
-  <si>
-    <t>A29S</t>
-  </si>
-  <si>
-    <t>A1PN</t>
-  </si>
-  <si>
-    <t>IL</t>
-  </si>
-  <si>
-    <t>A3GJ</t>
-  </si>
-  <si>
-    <t>A3JZ</t>
+    <t>D519</t>
+  </si>
+  <si>
+    <t>D1020</t>
+  </si>
+  <si>
+    <t>Lift Maintenance</t>
   </si>
   <si>
     <t>E270</t>
   </si>
   <si>
-    <t>D1020</t>
-  </si>
-  <si>
-    <t>Lift Maintenance</t>
-  </si>
-  <si>
-    <t>D519</t>
+    <t>E302</t>
+  </si>
+  <si>
+    <t>A1JS</t>
   </si>
   <si>
     <t>B903</t>
   </si>
   <si>
-    <t>E302</t>
-  </si>
-  <si>
-    <t>A1JS</t>
-  </si>
-  <si>
     <t>F406</t>
   </si>
   <si>
@@ -136,234 +136,234 @@
     <t>Snowmaking</t>
   </si>
   <si>
+    <t>D941</t>
+  </si>
+  <si>
+    <t>G397</t>
+  </si>
+  <si>
+    <t>H716</t>
+  </si>
+  <si>
+    <t>J169</t>
+  </si>
+  <si>
+    <t>A3SK</t>
+  </si>
+  <si>
     <t>A3SJ</t>
   </si>
   <si>
-    <t>A3SK</t>
-  </si>
-  <si>
-    <t>G397</t>
-  </si>
-  <si>
-    <t>H716</t>
-  </si>
-  <si>
-    <t>J169</t>
-  </si>
-  <si>
-    <t>D941</t>
+    <t>I540</t>
+  </si>
+  <si>
+    <t>D1060</t>
+  </si>
+  <si>
+    <t>Terrain Park</t>
+  </si>
+  <si>
+    <t>J056</t>
+  </si>
+  <si>
+    <t>A3DS</t>
+  </si>
+  <si>
+    <t>H101</t>
+  </si>
+  <si>
+    <t>H125</t>
   </si>
   <si>
     <t>I238</t>
   </si>
   <si>
-    <t>D1060</t>
-  </si>
-  <si>
-    <t>Terrain Park</t>
-  </si>
-  <si>
-    <t>H101</t>
-  </si>
-  <si>
-    <t>H125</t>
-  </si>
-  <si>
-    <t>A3DS</t>
-  </si>
-  <si>
-    <t>J056</t>
-  </si>
-  <si>
-    <t>I540</t>
+    <t>B797</t>
+  </si>
+  <si>
+    <t>D1070</t>
+  </si>
+  <si>
+    <t>Trail Maintenance</t>
+  </si>
+  <si>
+    <t>E877</t>
+  </si>
+  <si>
+    <t>A23C</t>
   </si>
   <si>
     <t>A1ZX</t>
   </si>
   <si>
-    <t>D1070</t>
-  </si>
-  <si>
-    <t>Trail Maintenance</t>
+    <t>D826</t>
   </si>
   <si>
     <t>A2UN</t>
   </si>
   <si>
+    <t>E436</t>
+  </si>
+  <si>
     <t>B250</t>
   </si>
   <si>
-    <t>E877</t>
-  </si>
-  <si>
-    <t>A23C</t>
-  </si>
-  <si>
-    <t>D826</t>
-  </si>
-  <si>
-    <t>E436</t>
-  </si>
-  <si>
-    <t>B797</t>
+    <t>J185</t>
+  </si>
+  <si>
+    <t>D1100</t>
+  </si>
+  <si>
+    <t>Vehicle Maintenance</t>
   </si>
   <si>
     <t>A1T8</t>
   </si>
   <si>
-    <t>D1100</t>
-  </si>
-  <si>
-    <t>Vehicle Maintenance</t>
-  </si>
-  <si>
-    <t>J185</t>
+    <t>A3LN</t>
+  </si>
+  <si>
+    <t>D1200</t>
+  </si>
+  <si>
+    <t>Ski Patrol</t>
+  </si>
+  <si>
+    <t>E950</t>
+  </si>
+  <si>
+    <t>E471</t>
+  </si>
+  <si>
+    <t>J024</t>
+  </si>
+  <si>
+    <t>A0JG</t>
+  </si>
+  <si>
+    <t>A3L3</t>
+  </si>
+  <si>
+    <t>H620</t>
+  </si>
+  <si>
+    <t>E584</t>
+  </si>
+  <si>
+    <t>G076</t>
+  </si>
+  <si>
+    <t>B162</t>
+  </si>
+  <si>
+    <t>B898</t>
   </si>
   <si>
     <t>J471</t>
   </si>
   <si>
-    <t>D1200</t>
-  </si>
-  <si>
-    <t>Ski Patrol</t>
+    <t>A889</t>
+  </si>
+  <si>
+    <t>B878</t>
   </si>
   <si>
     <t>B924</t>
   </si>
   <si>
-    <t>B878</t>
-  </si>
-  <si>
-    <t>A889</t>
-  </si>
-  <si>
-    <t>J024</t>
+    <t>I762</t>
   </si>
   <si>
     <t>D855</t>
   </si>
   <si>
-    <t>E471</t>
-  </si>
-  <si>
-    <t>A3LN</t>
-  </si>
-  <si>
-    <t>B898</t>
-  </si>
-  <si>
-    <t>G076</t>
-  </si>
-  <si>
-    <t>B162</t>
-  </si>
-  <si>
-    <t>H620</t>
-  </si>
-  <si>
-    <t>E950</t>
-  </si>
-  <si>
-    <t>A3L3</t>
-  </si>
-  <si>
-    <t>E584</t>
-  </si>
-  <si>
-    <t>I762</t>
-  </si>
-  <si>
-    <t>A0JG</t>
+    <t>I552</t>
+  </si>
+  <si>
+    <t>D1500</t>
+  </si>
+  <si>
+    <t>Tickets</t>
+  </si>
+  <si>
+    <t>D126</t>
+  </si>
+  <si>
+    <t>OL</t>
+  </si>
+  <si>
+    <t>A34H</t>
   </si>
   <si>
     <t>A3AD</t>
   </si>
   <si>
-    <t>D1500</t>
-  </si>
-  <si>
-    <t>Tickets</t>
+    <t>C173</t>
+  </si>
+  <si>
+    <t>D071</t>
+  </si>
+  <si>
+    <t>A3S9</t>
+  </si>
+  <si>
+    <t>A3PB</t>
+  </si>
+  <si>
+    <t>A37H</t>
+  </si>
+  <si>
+    <t>J071</t>
+  </si>
+  <si>
+    <t>A3NY</t>
+  </si>
+  <si>
+    <t>A3M3</t>
+  </si>
+  <si>
+    <t>I563</t>
+  </si>
+  <si>
+    <t>A3PT</t>
+  </si>
+  <si>
+    <t>B341</t>
+  </si>
+  <si>
+    <t>A3M1</t>
+  </si>
+  <si>
+    <t>A3NV</t>
   </si>
   <si>
     <t>A3SA</t>
   </si>
   <si>
-    <t>OL</t>
-  </si>
-  <si>
     <t>D441</t>
   </si>
   <si>
+    <t>A2O6</t>
+  </si>
+  <si>
     <t>A1FE</t>
   </si>
   <si>
+    <t>A2KR</t>
+  </si>
+  <si>
+    <t>A2TY</t>
+  </si>
+  <si>
     <t>E547</t>
   </si>
   <si>
+    <t>A3NW</t>
+  </si>
+  <si>
     <t>I565</t>
   </si>
   <si>
-    <t>A2TY</t>
-  </si>
-  <si>
-    <t>A2KR</t>
-  </si>
-  <si>
-    <t>A34H</t>
-  </si>
-  <si>
-    <t>A3NW</t>
-  </si>
-  <si>
-    <t>I563</t>
-  </si>
-  <si>
-    <t>A37H</t>
-  </si>
-  <si>
-    <t>A3S9</t>
-  </si>
-  <si>
-    <t>A3PB</t>
-  </si>
-  <si>
-    <t>A3NV</t>
-  </si>
-  <si>
-    <t>D126</t>
-  </si>
-  <si>
-    <t>A3M3</t>
-  </si>
-  <si>
-    <t>A3PT</t>
-  </si>
-  <si>
-    <t>B341</t>
-  </si>
-  <si>
-    <t>C173</t>
-  </si>
-  <si>
-    <t>D071</t>
-  </si>
-  <si>
-    <t>I552</t>
-  </si>
-  <si>
-    <t>J071</t>
-  </si>
-  <si>
-    <t>A3NY</t>
-  </si>
-  <si>
-    <t>A2O6</t>
-  </si>
-  <si>
-    <t>A3M1</t>
-  </si>
-  <si>
     <t>A29N</t>
   </si>
   <si>
@@ -376,15 +376,15 @@
     <t>G327</t>
   </si>
   <si>
+    <t>D3000</t>
+  </si>
+  <si>
+    <t>Rentals</t>
+  </si>
+  <si>
     <t>A2AA</t>
   </si>
   <si>
-    <t>D3000</t>
-  </si>
-  <si>
-    <t>Rentals</t>
-  </si>
-  <si>
     <t>D4054</t>
   </si>
   <si>
@@ -400,36 +400,36 @@
     <t>Purg Sports Main Ave</t>
   </si>
   <si>
+    <t>E655</t>
+  </si>
+  <si>
+    <t>D5201</t>
+  </si>
+  <si>
+    <t>Powderhouse</t>
+  </si>
+  <si>
     <t>A2LP</t>
   </si>
   <si>
-    <t>D5201</t>
-  </si>
-  <si>
-    <t>Powderhouse</t>
-  </si>
-  <si>
     <t>E181</t>
   </si>
   <si>
-    <t>E655</t>
-  </si>
-  <si>
     <t>I216</t>
   </si>
   <si>
+    <t>A3V5</t>
+  </si>
+  <si>
+    <t>D5202</t>
+  </si>
+  <si>
+    <t>Dante's</t>
+  </si>
+  <si>
     <t>A3VR</t>
   </si>
   <si>
-    <t>D5202</t>
-  </si>
-  <si>
-    <t>Dante's</t>
-  </si>
-  <si>
-    <t>A3V5</t>
-  </si>
-  <si>
     <t>A3ZN</t>
   </si>
   <si>
@@ -439,156 +439,156 @@
     <t>Waffle Cabin</t>
   </si>
   <si>
+    <t>I704</t>
+  </si>
+  <si>
+    <t>D5206</t>
+  </si>
+  <si>
+    <t>Hoody's</t>
+  </si>
+  <si>
+    <t>A3ZI</t>
+  </si>
+  <si>
     <t>A36T</t>
   </si>
   <si>
-    <t>D5206</t>
-  </si>
-  <si>
-    <t>Hoody's</t>
+    <t>G724</t>
+  </si>
+  <si>
+    <t>A3PX</t>
   </si>
   <si>
     <t>A3FO</t>
   </si>
   <si>
-    <t>A3PX</t>
-  </si>
-  <si>
-    <t>G724</t>
-  </si>
-  <si>
-    <t>A3ZI</t>
-  </si>
-  <si>
-    <t>I704</t>
+    <t>I517</t>
+  </si>
+  <si>
+    <t>D5207</t>
+  </si>
+  <si>
+    <t>Paradise</t>
+  </si>
+  <si>
+    <t>J434</t>
+  </si>
+  <si>
+    <t>J335</t>
   </si>
   <si>
     <t>A1MU</t>
   </si>
   <si>
-    <t>D5207</t>
-  </si>
-  <si>
-    <t>Paradise</t>
-  </si>
-  <si>
-    <t>I517</t>
-  </si>
-  <si>
-    <t>J335</t>
-  </si>
-  <si>
     <t>I518</t>
   </si>
   <si>
-    <t>J434</t>
+    <t>A739</t>
+  </si>
+  <si>
+    <t>D5208</t>
+  </si>
+  <si>
+    <t>Purgy's</t>
+  </si>
+  <si>
+    <t>A2HN</t>
+  </si>
+  <si>
+    <t>A43Z</t>
   </si>
   <si>
     <t>A2SG</t>
   </si>
   <si>
-    <t>D5208</t>
-  </si>
-  <si>
-    <t>Purgy's</t>
+    <t>I666</t>
+  </si>
+  <si>
+    <t>B101</t>
+  </si>
+  <si>
+    <t>A38R</t>
   </si>
   <si>
     <t>A3VO</t>
   </si>
   <si>
-    <t>I666</t>
+    <t>A3GE</t>
+  </si>
+  <si>
+    <t>D274</t>
   </si>
   <si>
     <t>A3UA</t>
   </si>
   <si>
-    <t>D274</t>
+    <t>A2RM</t>
+  </si>
+  <si>
+    <t>A15N</t>
   </si>
   <si>
     <t>D499</t>
   </si>
   <si>
-    <t>B101</t>
-  </si>
-  <si>
-    <t>A15N</t>
-  </si>
-  <si>
-    <t>A2RM</t>
-  </si>
-  <si>
-    <t>A43Z</t>
-  </si>
-  <si>
-    <t>A739</t>
-  </si>
-  <si>
-    <t>A3GE</t>
-  </si>
-  <si>
-    <t>A2HN</t>
-  </si>
-  <si>
-    <t>A38R</t>
-  </si>
-  <si>
     <t>D5209</t>
   </si>
   <si>
     <t>Village Market Deli</t>
   </si>
   <si>
+    <t>A3DX</t>
+  </si>
+  <si>
+    <t>D6212</t>
+  </si>
+  <si>
+    <t>Purgatory</t>
+  </si>
+  <si>
+    <t>A42D</t>
+  </si>
+  <si>
+    <t>A42C</t>
+  </si>
+  <si>
+    <t>A1N1</t>
+  </si>
+  <si>
+    <t>I953</t>
+  </si>
+  <si>
+    <t>F298</t>
+  </si>
+  <si>
     <t>D283</t>
   </si>
   <si>
-    <t>D6212</t>
-  </si>
-  <si>
-    <t>Purgatory</t>
-  </si>
-  <si>
-    <t>I953</t>
-  </si>
-  <si>
-    <t>A3DX</t>
-  </si>
-  <si>
-    <t>A42C</t>
-  </si>
-  <si>
-    <t>A42D</t>
-  </si>
-  <si>
-    <t>F298</t>
-  </si>
-  <si>
     <t>F313</t>
   </si>
   <si>
-    <t>A1N1</t>
+    <t>J489</t>
+  </si>
+  <si>
+    <t>D6215</t>
+  </si>
+  <si>
+    <t>Housekeeping</t>
+  </si>
+  <si>
+    <t>I999</t>
   </si>
   <si>
     <t>J492</t>
   </si>
   <si>
-    <t>D6215</t>
-  </si>
-  <si>
-    <t>Housekeeping</t>
+    <t>H341</t>
   </si>
   <si>
     <t>A3DT</t>
   </si>
   <si>
-    <t>J489</t>
-  </si>
-  <si>
-    <t>I999</t>
-  </si>
-  <si>
-    <t>H341</t>
-  </si>
-  <si>
     <t>C825</t>
   </si>
   <si>
@@ -622,54 +622,54 @@
     <t>A3FH</t>
   </si>
   <si>
+    <t>A2DH</t>
+  </si>
+  <si>
+    <t>D6750</t>
+  </si>
+  <si>
+    <t>Engineering</t>
+  </si>
+  <si>
+    <t>A3HI</t>
+  </si>
+  <si>
+    <t>C516</t>
+  </si>
+  <si>
+    <t>A3HC</t>
+  </si>
+  <si>
     <t>F396</t>
   </si>
   <si>
-    <t>D6750</t>
-  </si>
-  <si>
-    <t>Engineering</t>
-  </si>
-  <si>
-    <t>C516</t>
-  </si>
-  <si>
-    <t>A3HC</t>
-  </si>
-  <si>
-    <t>A3HI</t>
-  </si>
-  <si>
-    <t>A2DH</t>
+    <t>D6780</t>
+  </si>
+  <si>
+    <t>Grounds Maintenance</t>
+  </si>
+  <si>
+    <t>D736</t>
   </si>
   <si>
     <t>A2UO</t>
   </si>
   <si>
-    <t>D6780</t>
-  </si>
-  <si>
-    <t>Grounds Maintenance</t>
+    <t>A3PE</t>
+  </si>
+  <si>
+    <t>E609</t>
   </si>
   <si>
     <t>A2JA</t>
   </si>
   <si>
-    <t>A3PE</t>
+    <t>A2SD</t>
   </si>
   <si>
     <t>A1WB</t>
   </si>
   <si>
-    <t>E609</t>
-  </si>
-  <si>
-    <t>A2SD</t>
-  </si>
-  <si>
-    <t>D736</t>
-  </si>
-  <si>
     <t>A3N2</t>
   </si>
   <si>
@@ -709,28 +709,28 @@
     <t>A1Z8</t>
   </si>
   <si>
+    <t>A3WZ</t>
+  </si>
+  <si>
+    <t>D8020</t>
+  </si>
+  <si>
+    <t>Accounting</t>
+  </si>
+  <si>
     <t>D737</t>
   </si>
   <si>
-    <t>D8020</t>
-  </si>
-  <si>
-    <t>Accounting</t>
-  </si>
-  <si>
-    <t>A3WZ</t>
+    <t>A39Q</t>
+  </si>
+  <si>
+    <t>D8040</t>
+  </si>
+  <si>
+    <t>A1BT</t>
   </si>
   <si>
     <t>A3C3</t>
-  </si>
-  <si>
-    <t>D8040</t>
-  </si>
-  <si>
-    <t>A39Q</t>
-  </si>
-  <si>
-    <t>A1BT</t>
   </si>
   <si>
     <t>A1ZP</t>
@@ -1155,13 +1155,13 @@
         <v>8</v>
       </c>
       <c r="B2" s="2">
-        <v>45992.3065162037</v>
+        <v>45992.29674768518</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D2" s="2">
-        <v>45992.71550925926</v>
+        <v>45992.71288194445</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>10</v>
@@ -1170,7 +1170,7 @@
         <v>11</v>
       </c>
       <c r="G2" s="2">
-        <v>15.5</v>
+        <v>23.69</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>12</v>
@@ -1181,13 +1181,13 @@
         <v>13</v>
       </c>
       <c r="B3" s="2">
-        <v>45992.28875</v>
+        <v>45993.29893518519</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D3" s="2">
-        <v>45992.71085648148</v>
+        <v>45993.70039351852</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>10</v>
@@ -1196,7 +1196,7 @@
         <v>11</v>
       </c>
       <c r="G3" s="2">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>12</v>
@@ -1204,16 +1204,16 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4" s="2">
-        <v>45993.30665509259</v>
+        <v>45993.29755787037</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D4" s="2">
-        <v>45993.723125</v>
+        <v>45993.70832175926</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>10</v>
@@ -1222,7 +1222,7 @@
         <v>11</v>
       </c>
       <c r="G4" s="2">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>12</v>
@@ -1230,7 +1230,7 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5" s="2">
         <v>45992.31201388889</v>
@@ -1256,19 +1256,19 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" s="2">
-        <v>45993.29755787037</v>
+        <v>45993.29166666666</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D6" s="2">
-        <v>45993.70832175926</v>
+        <v>45993.29166666666</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>11</v>
@@ -1285,13 +1285,13 @@
         <v>16</v>
       </c>
       <c r="B7" s="2">
-        <v>45993.29893518519</v>
+        <v>45992.71596064815</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D7" s="2">
-        <v>45993.70039351852</v>
+        <v>45992.71875</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>10</v>
@@ -1308,16 +1308,16 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="2">
-        <v>45992.29674768518</v>
+        <v>45992.29166666666</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D8" s="2">
-        <v>45992.71288194445</v>
+        <v>45992.71875</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>10</v>
@@ -1326,7 +1326,7 @@
         <v>11</v>
       </c>
       <c r="G8" s="2">
-        <v>23.69</v>
+        <v>16</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>12</v>
@@ -1334,16 +1334,16 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="2" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B9" s="2">
-        <v>45993.31125</v>
+        <v>45993.31658564815</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="2">
-        <v>45993.72252314815</v>
+        <v>45993.70996527778</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>10</v>
@@ -1363,13 +1363,13 @@
         <v>18</v>
       </c>
       <c r="B10" s="2">
-        <v>45992.31020833334</v>
+        <v>45992.32587962963</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D10" s="2">
-        <v>45992.70743055556</v>
+        <v>45992.68709490741</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>10</v>
@@ -1378,7 +1378,7 @@
         <v>11</v>
       </c>
       <c r="G10" s="2">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>12</v>
@@ -1389,13 +1389,13 @@
         <v>19</v>
       </c>
       <c r="B11" s="2">
-        <v>45992.32686342593</v>
+        <v>45993.32325231482</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D11" s="2">
-        <v>45992.70833333334</v>
+        <v>45993.70679398148</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>10</v>
@@ -1404,7 +1404,7 @@
         <v>11</v>
       </c>
       <c r="G11" s="2">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>12</v>
@@ -1415,13 +1415,13 @@
         <v>20</v>
       </c>
       <c r="B12" s="2">
-        <v>45993.31658564815</v>
+        <v>45992.55469907408</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D12" s="2">
-        <v>45993.70996527778</v>
+        <v>45992.68180555556</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>10</v>
@@ -1438,19 +1438,19 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13" s="2">
-        <v>45993.29166666666</v>
+        <v>45992.28857638889</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2">
-        <v>45993.29166666666</v>
+        <v>45992.71381944444</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>11</v>
@@ -1464,16 +1464,16 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B14" s="2">
-        <v>45992.71596064815</v>
+        <v>45992.31020833334</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="2">
-        <v>45992.71875</v>
+        <v>45992.70743055556</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>10</v>
@@ -1482,7 +1482,7 @@
         <v>11</v>
       </c>
       <c r="G14" s="2">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>12</v>
@@ -1490,16 +1490,16 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B15" s="2">
-        <v>45992.29166666666</v>
+        <v>45993.31125</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D15" s="2">
-        <v>45992.71875</v>
+        <v>45993.72252314815</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>10</v>
@@ -1508,7 +1508,7 @@
         <v>11</v>
       </c>
       <c r="G15" s="2">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>12</v>
@@ -1516,16 +1516,16 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B16" s="2">
-        <v>45993.29910879629</v>
+        <v>45992.3065162037</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D16" s="2">
-        <v>45993.7230324074</v>
+        <v>45992.71550925926</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>10</v>
@@ -1534,7 +1534,7 @@
         <v>11</v>
       </c>
       <c r="G16" s="2">
-        <v>19.57</v>
+        <v>15.5</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>12</v>
@@ -1542,16 +1542,16 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B17" s="2">
-        <v>45992.29747685185</v>
+        <v>45992.33238425926</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D17" s="2">
-        <v>45992.68304398148</v>
+        <v>45992.67116898148</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>10</v>
@@ -1560,7 +1560,7 @@
         <v>11</v>
       </c>
       <c r="G17" s="2">
-        <v>19.57</v>
+        <v>15</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>12</v>
@@ -1568,16 +1568,16 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B18" s="2">
-        <v>45993.32325231482</v>
+        <v>45992.32686342593</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D18" s="2">
-        <v>45993.70679398148</v>
+        <v>45992.70833333334</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>10</v>
@@ -1586,7 +1586,7 @@
         <v>11</v>
       </c>
       <c r="G18" s="2">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>12</v>
@@ -1594,16 +1594,16 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B19" s="2">
-        <v>45992.55469907408</v>
+        <v>45992.29747685185</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2">
-        <v>45992.68180555556</v>
+        <v>45992.68304398148</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>10</v>
@@ -1612,7 +1612,7 @@
         <v>11</v>
       </c>
       <c r="G19" s="2">
-        <v>15.5</v>
+        <v>19.57</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>12</v>
@@ -1623,13 +1623,13 @@
         <v>27</v>
       </c>
       <c r="B20" s="2">
-        <v>45992.28857638889</v>
+        <v>45993.29910879629</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D20" s="2">
-        <v>45992.71381944444</v>
+        <v>45993.7230324074</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>10</v>
@@ -1638,7 +1638,7 @@
         <v>11</v>
       </c>
       <c r="G20" s="2">
-        <v>16</v>
+        <v>19.57</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>12</v>
@@ -1646,16 +1646,16 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="2" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="B21" s="2">
-        <v>45992.32587962963</v>
+        <v>45992.28875</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D21" s="2">
-        <v>45992.68709490741</v>
+        <v>45992.71085648148</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>10</v>
@@ -1675,13 +1675,13 @@
         <v>28</v>
       </c>
       <c r="B22" s="2">
-        <v>45992.33238425926</v>
+        <v>45993.30665509259</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D22" s="2">
-        <v>45992.67116898148</v>
+        <v>45993.723125</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>10</v>
@@ -1690,7 +1690,7 @@
         <v>11</v>
       </c>
       <c r="G22" s="2">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>12</v>
@@ -1701,13 +1701,13 @@
         <v>29</v>
       </c>
       <c r="B23" s="2">
-        <v>45993.26789351852</v>
+        <v>45992.27606481482</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D23" s="2">
-        <v>45993.70138888889</v>
+        <v>45992.70167824074</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>10</v>
@@ -1716,7 +1716,7 @@
         <v>30</v>
       </c>
       <c r="G23" s="2">
-        <v>35.43</v>
+        <v>21.57</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>31</v>
@@ -1724,16 +1724,16 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B24" s="2">
-        <v>45992.27777777778</v>
+        <v>45993.26789351852</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D24" s="2">
-        <v>45992.70017361111</v>
+        <v>45993.70138888889</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>10</v>
@@ -1750,16 +1750,16 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B25" s="2">
-        <v>45993.27314814815</v>
+        <v>45992.27083333334</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D25" s="2">
-        <v>45993.70487268519</v>
+        <v>45992.69840277778</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>10</v>
@@ -1768,7 +1768,7 @@
         <v>30</v>
       </c>
       <c r="G25" s="2">
-        <v>21.57</v>
+        <v>29.87</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>31</v>
@@ -1776,16 +1776,16 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B26" s="2">
-        <v>45992.27606481482</v>
+        <v>45993.27181712963</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D26" s="2">
-        <v>45992.70167824074</v>
+        <v>45993.70261574074</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>10</v>
@@ -1794,7 +1794,7 @@
         <v>30</v>
       </c>
       <c r="G26" s="2">
-        <v>21.57</v>
+        <v>29.87</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>31</v>
@@ -1802,16 +1802,16 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B27" s="2">
-        <v>45992.26872685185</v>
+        <v>45992.27179398148</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D27" s="2">
-        <v>45992.68879629629</v>
+        <v>45992.69628472222</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>10</v>
@@ -1820,7 +1820,7 @@
         <v>30</v>
       </c>
       <c r="G27" s="2">
-        <v>23.63</v>
+        <v>17</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>31</v>
@@ -1828,16 +1828,16 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B28" s="2">
-        <v>45992.27083333334</v>
+        <v>45992.26872685185</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D28" s="2">
-        <v>45992.69840277778</v>
+        <v>45992.68879629629</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>10</v>
@@ -1846,7 +1846,7 @@
         <v>30</v>
       </c>
       <c r="G28" s="2">
-        <v>29.87</v>
+        <v>23.63</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>31</v>
@@ -1854,16 +1854,16 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B29" s="2">
-        <v>45993.27181712963</v>
+        <v>45992.26055555556</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D29" s="2">
-        <v>45993.70261574074</v>
+        <v>45992.68293981482</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>10</v>
@@ -1872,7 +1872,7 @@
         <v>30</v>
       </c>
       <c r="G29" s="2">
-        <v>29.87</v>
+        <v>25.69</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>31</v>
@@ -1880,16 +1880,16 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B30" s="2">
-        <v>45992.27179398148</v>
+        <v>45992.27777777778</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D30" s="2">
-        <v>45992.69628472222</v>
+        <v>45992.70017361111</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>10</v>
@@ -1898,7 +1898,7 @@
         <v>30</v>
       </c>
       <c r="G30" s="2">
-        <v>17</v>
+        <v>35.43</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>31</v>
@@ -1906,16 +1906,16 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="2" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B31" s="2">
-        <v>45992.26055555556</v>
+        <v>45993.27314814815</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D31" s="2">
-        <v>45992.68293981482</v>
+        <v>45993.70487268519</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>10</v>
@@ -1924,7 +1924,7 @@
         <v>30</v>
       </c>
       <c r="G31" s="2">
-        <v>25.69</v>
+        <v>21.57</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>31</v>
@@ -1961,13 +1961,13 @@
         <v>40</v>
       </c>
       <c r="B33" s="2">
-        <v>45992.4428587963</v>
+        <v>45993.4521875</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D33" s="2">
-        <v>45992.98121527778</v>
+        <v>45994.0188425926</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>10</v>
@@ -1976,7 +1976,7 @@
         <v>38</v>
       </c>
       <c r="G33" s="2">
-        <v>19.1</v>
+        <v>18.55</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>39</v>
@@ -1987,22 +1987,18 @@
         <v>41</v>
       </c>
       <c r="B34" s="2">
-        <v>45993.45630787037</v>
+        <v>45993.44041666666</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D34" s="2">
-        <v>45994.00210648148</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>10</v>
-      </c>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
       <c r="F34" s="2" t="s">
         <v>38</v>
       </c>
       <c r="G34" s="2">
-        <v>19.1</v>
+        <v>18.55</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>39</v>
@@ -2013,13 +2009,13 @@
         <v>42</v>
       </c>
       <c r="B35" s="2">
-        <v>45992.46755787037</v>
+        <v>45993.46209490741</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D35" s="2">
-        <v>45992.98403935185</v>
+        <v>45993.97168981482</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>10</v>
@@ -2028,7 +2024,7 @@
         <v>38</v>
       </c>
       <c r="G35" s="2">
-        <v>18.55</v>
+        <v>15</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>39</v>
@@ -2036,10 +2032,10 @@
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B36" s="2">
-        <v>45993.44041666666</v>
+        <v>45992.43916666666</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>9</v>
@@ -2058,7 +2054,7 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B37" s="2">
         <v>45992.47134259259</v>
@@ -2084,16 +2080,16 @@
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B38" s="2">
-        <v>45993.46209490741</v>
+        <v>45992.46368055556</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D38" s="2">
-        <v>45993.97168981482</v>
+        <v>45992.96348379629</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>10</v>
@@ -2102,7 +2098,7 @@
         <v>38</v>
       </c>
       <c r="G38" s="2">
-        <v>15</v>
+        <v>19.1</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>39</v>
@@ -2113,18 +2109,22 @@
         <v>44</v>
       </c>
       <c r="B39" s="2">
-        <v>45992.43916666666</v>
+        <v>45993.45630787037</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
+      <c r="D39" s="2">
+        <v>45994.00210648148</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="F39" s="2" t="s">
         <v>38</v>
       </c>
       <c r="G39" s="2">
-        <v>18.55</v>
+        <v>19.1</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>39</v>
@@ -2135,13 +2135,13 @@
         <v>45</v>
       </c>
       <c r="B40" s="2">
-        <v>45993.4521875</v>
+        <v>45992.4428587963</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D40" s="2">
-        <v>45994.0188425926</v>
+        <v>45992.98121527778</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>10</v>
@@ -2150,7 +2150,7 @@
         <v>38</v>
       </c>
       <c r="G40" s="2">
-        <v>18.55</v>
+        <v>19.1</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>39</v>
@@ -2161,13 +2161,13 @@
         <v>41</v>
       </c>
       <c r="B41" s="2">
-        <v>45992.46368055556</v>
+        <v>45992.46755787037</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D41" s="2">
-        <v>45992.96348379629</v>
+        <v>45992.98403935185</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>10</v>
@@ -2176,7 +2176,7 @@
         <v>38</v>
       </c>
       <c r="G41" s="2">
-        <v>19.1</v>
+        <v>18.55</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>39</v>
@@ -2187,13 +2187,13 @@
         <v>46</v>
       </c>
       <c r="B42" s="2">
-        <v>45993.30012731482</v>
+        <v>45993.31822916667</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D42" s="2">
-        <v>45993.73251157408</v>
+        <v>45993.73927083334</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>10</v>
@@ -2202,7 +2202,7 @@
         <v>47</v>
       </c>
       <c r="G42" s="2">
-        <v>16</v>
+        <v>12.35</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>48</v>
@@ -2213,18 +2213,22 @@
         <v>49</v>
       </c>
       <c r="B43" s="2">
-        <v>45993.3125</v>
+        <v>45992.31195601852</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D43" s="2"/>
-      <c r="E43" s="2"/>
+      <c r="D43" s="2">
+        <v>45992.73530092592</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="F43" s="2" t="s">
         <v>47</v>
       </c>
       <c r="G43" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>48</v>
@@ -2235,18 +2239,22 @@
         <v>50</v>
       </c>
       <c r="B44" s="2">
-        <v>45993.67045138889</v>
+        <v>45992.3125</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
+      <c r="D44" s="2">
+        <v>45992.94791666666</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="F44" s="2" t="s">
         <v>47</v>
       </c>
       <c r="G44" s="2">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>48</v>
@@ -2254,7 +2262,7 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B45" s="2">
         <v>45993.3184375</v>
@@ -2283,22 +2291,18 @@
         <v>51</v>
       </c>
       <c r="B46" s="2">
-        <v>45992.3125</v>
+        <v>45993.3125</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D46" s="2">
-        <v>45992.94791666666</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>10</v>
-      </c>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
       <c r="F46" s="2" t="s">
         <v>47</v>
       </c>
       <c r="G46" s="2">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>48</v>
@@ -2309,17 +2313,13 @@
         <v>52</v>
       </c>
       <c r="B47" s="2">
-        <v>45992.31195601852</v>
+        <v>45993.67045138889</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D47" s="2">
-        <v>45992.73530092592</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>10</v>
-      </c>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
       <c r="F47" s="2" t="s">
         <v>47</v>
       </c>
@@ -2335,13 +2335,13 @@
         <v>53</v>
       </c>
       <c r="B48" s="2">
-        <v>45993.31822916667</v>
+        <v>45993.30012731482</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D48" s="2">
-        <v>45993.73927083334</v>
+        <v>45993.73251157408</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>10</v>
@@ -2350,7 +2350,7 @@
         <v>47</v>
       </c>
       <c r="G48" s="2">
-        <v>12.35</v>
+        <v>16</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>48</v>
@@ -2361,13 +2361,13 @@
         <v>54</v>
       </c>
       <c r="B49" s="2">
-        <v>45992.92275462963</v>
+        <v>45993.95633101852</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D49" s="2">
-        <v>45993.4577662037</v>
+        <v>45994.46997685185</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>10</v>
@@ -2376,7 +2376,7 @@
         <v>55</v>
       </c>
       <c r="G49" s="2">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>56</v>
@@ -2387,22 +2387,18 @@
         <v>57</v>
       </c>
       <c r="B50" s="2">
-        <v>45993.47743055555</v>
+        <v>45993.46145833333</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D50" s="2">
-        <v>45993.95138888889</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>10</v>
-      </c>
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
       <c r="F50" s="2" t="s">
         <v>55</v>
       </c>
       <c r="G50" s="2">
-        <v>23.33</v>
+        <v>16.5</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>56</v>
@@ -2413,13 +2409,13 @@
         <v>57</v>
       </c>
       <c r="B51" s="2">
-        <v>45992.48701388889</v>
+        <v>45992.46166666667</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D51" s="2">
-        <v>45992.58333333334</v>
+        <v>45992.97331018518</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>10</v>
@@ -2428,7 +2424,7 @@
         <v>55</v>
       </c>
       <c r="G51" s="2">
-        <v>23.33</v>
+        <v>16.5</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>56</v>
@@ -2439,13 +2435,13 @@
         <v>58</v>
       </c>
       <c r="B52" s="2">
-        <v>45992.98611111111</v>
+        <v>45992.44806712963</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D52" s="2">
-        <v>45993.54166666666</v>
+        <v>45992.78056712963</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>10</v>
@@ -2454,7 +2450,7 @@
         <v>55</v>
       </c>
       <c r="G52" s="2">
-        <v>24.26</v>
+        <v>18.36</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>56</v>
@@ -2462,16 +2458,16 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B53" s="2">
-        <v>45993.97611111111</v>
+        <v>45992.92275462963</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D53" s="2">
-        <v>45994.45969907408</v>
+        <v>45993.4577662037</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>10</v>
@@ -2491,18 +2487,22 @@
         <v>59</v>
       </c>
       <c r="B54" s="2">
-        <v>45993.46145833333</v>
+        <v>45993.97611111111</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D54" s="2"/>
-      <c r="E54" s="2"/>
+      <c r="D54" s="2">
+        <v>45994.45969907408</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="F54" s="2" t="s">
         <v>55</v>
       </c>
       <c r="G54" s="2">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>56</v>
@@ -2513,13 +2513,13 @@
         <v>60</v>
       </c>
       <c r="B55" s="2">
-        <v>45992.44806712963</v>
+        <v>45993.28452546296</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D55" s="2">
-        <v>45992.78056712963</v>
+        <v>45993.72278935185</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>10</v>
@@ -2528,7 +2528,7 @@
         <v>55</v>
       </c>
       <c r="G55" s="2">
-        <v>18.36</v>
+        <v>26</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>56</v>
@@ -2536,16 +2536,16 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B56" s="2">
-        <v>45992.46166666667</v>
+        <v>45993.47743055555</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D56" s="2">
-        <v>45992.97331018518</v>
+        <v>45993.95138888889</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>10</v>
@@ -2554,7 +2554,7 @@
         <v>55</v>
       </c>
       <c r="G56" s="2">
-        <v>16.5</v>
+        <v>23.33</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>56</v>
@@ -2562,16 +2562,16 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B57" s="2">
-        <v>45993.28452546296</v>
+        <v>45993.72826388889</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D57" s="2">
-        <v>45993.72278935185</v>
+        <v>45994.21900462963</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>10</v>
@@ -2580,7 +2580,7 @@
         <v>55</v>
       </c>
       <c r="G57" s="2">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>56</v>
@@ -2588,16 +2588,16 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B58" s="2">
-        <v>45992.28890046296</v>
+        <v>45992.98611111111</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D58" s="2">
-        <v>45992.71565972222</v>
+        <v>45993.54166666666</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>10</v>
@@ -2606,7 +2606,7 @@
         <v>55</v>
       </c>
       <c r="G58" s="2">
-        <v>26</v>
+        <v>24.26</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>56</v>
@@ -2614,16 +2614,16 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B59" s="2">
-        <v>45993.72826388889</v>
+        <v>45992.28890046296</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D59" s="2">
-        <v>45994.21900462963</v>
+        <v>45992.71565972222</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>10</v>
@@ -2632,7 +2632,7 @@
         <v>55</v>
       </c>
       <c r="G59" s="2">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H59" s="2" t="s">
         <v>56</v>
@@ -2640,16 +2640,16 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B60" s="2">
-        <v>45993.95633101852</v>
+        <v>45992.48701388889</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D60" s="2">
-        <v>45994.46997685185</v>
+        <v>45992.58333333334</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>10</v>
@@ -2658,7 +2658,7 @@
         <v>55</v>
       </c>
       <c r="G60" s="2">
-        <v>19.5</v>
+        <v>23.33</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>56</v>
@@ -2669,13 +2669,13 @@
         <v>64</v>
       </c>
       <c r="B61" s="2">
-        <v>45992.23543981482</v>
+        <v>45993.22570601852</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D61" s="2">
-        <v>45992.70652777778</v>
+        <v>45993.72601851852</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>10</v>
@@ -2684,7 +2684,7 @@
         <v>65</v>
       </c>
       <c r="G61" s="2">
-        <v>22.66</v>
+        <v>27</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>66</v>
@@ -2695,13 +2695,13 @@
         <v>64</v>
       </c>
       <c r="B62" s="2">
-        <v>45993.22068287037</v>
+        <v>45992.14164351852</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D62" s="2">
-        <v>45993.70631944444</v>
+        <v>45992.66263888889</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>10</v>
@@ -2710,7 +2710,7 @@
         <v>65</v>
       </c>
       <c r="G62" s="2">
-        <v>22.66</v>
+        <v>27</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>66</v>
@@ -2721,13 +2721,13 @@
         <v>67</v>
       </c>
       <c r="B63" s="2">
-        <v>45993.22570601852</v>
+        <v>45993.22068287037</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D63" s="2">
-        <v>45993.72601851852</v>
+        <v>45993.70631944444</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>10</v>
@@ -2736,7 +2736,7 @@
         <v>65</v>
       </c>
       <c r="G63" s="2">
-        <v>27</v>
+        <v>22.66</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>66</v>
@@ -2747,13 +2747,13 @@
         <v>67</v>
       </c>
       <c r="B64" s="2">
-        <v>45992.14164351852</v>
+        <v>45992.23543981482</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D64" s="2">
-        <v>45992.66263888889</v>
+        <v>45992.70652777778</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>10</v>
@@ -2762,7 +2762,7 @@
         <v>65</v>
       </c>
       <c r="G64" s="2">
-        <v>27</v>
+        <v>22.66</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>66</v>
@@ -2773,13 +2773,13 @@
         <v>68</v>
       </c>
       <c r="B65" s="2">
-        <v>45992.36817129629</v>
+        <v>45992.31818287037</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D65" s="2">
-        <v>45992.60943287037</v>
+        <v>45992.70214120371</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>10</v>
@@ -2788,7 +2788,7 @@
         <v>69</v>
       </c>
       <c r="G65" s="2">
-        <v>22</v>
+        <v>18.03</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>70</v>
@@ -2799,13 +2799,13 @@
         <v>71</v>
       </c>
       <c r="B66" s="2">
-        <v>45993.31284722222</v>
+        <v>45993.31121527778</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D66" s="2">
-        <v>45993.71363425926</v>
+        <v>45993.7146875</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>10</v>
@@ -2814,7 +2814,7 @@
         <v>69</v>
       </c>
       <c r="G66" s="2">
-        <v>18.77</v>
+        <v>19</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>70</v>
@@ -2822,16 +2822,16 @@
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B67" s="2">
-        <v>45992.3171875</v>
+        <v>45992.31878472222</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D67" s="2">
-        <v>45992.71112268518</v>
+        <v>45992.71140046296</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>10</v>
@@ -2840,7 +2840,7 @@
         <v>69</v>
       </c>
       <c r="G67" s="2">
-        <v>25.84</v>
+        <v>19</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>70</v>
@@ -2848,16 +2848,16 @@
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B68" s="2">
-        <v>45992.31912037037</v>
+        <v>45993.31199074074</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D68" s="2">
-        <v>45992.71261574074</v>
+        <v>45993.71875</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>10</v>
@@ -2866,7 +2866,7 @@
         <v>69</v>
       </c>
       <c r="G68" s="2">
-        <v>12.56</v>
+        <v>24.59</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>70</v>
@@ -2874,16 +2874,16 @@
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B69" s="2">
-        <v>45993.31699074074</v>
+        <v>45992.32019675926</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D69" s="2">
-        <v>45993.71618055556</v>
+        <v>45992.71041666667</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>10</v>
@@ -2900,16 +2900,16 @@
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B70" s="2">
-        <v>45992.31655092593</v>
+        <v>45993.31672453704</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D70" s="2">
-        <v>45992.71273148148</v>
+        <v>45993.71502314815</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>10</v>
@@ -2918,7 +2918,7 @@
         <v>69</v>
       </c>
       <c r="G70" s="2">
-        <v>21.06</v>
+        <v>19</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>70</v>
@@ -2926,16 +2926,16 @@
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B71" s="2">
-        <v>45993.31199074074</v>
+        <v>45992.31442129629</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D71" s="2">
-        <v>45993.71875</v>
+        <v>45992.71223379629</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>10</v>
@@ -2944,7 +2944,7 @@
         <v>69</v>
       </c>
       <c r="G71" s="2">
-        <v>24.59</v>
+        <v>19.03</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>70</v>
@@ -2952,16 +2952,16 @@
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B72" s="2">
-        <v>45992.31818287037</v>
+        <v>45993.31137731481</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D72" s="2">
-        <v>45992.70214120371</v>
+        <v>45993.71450231481</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>10</v>
@@ -2970,7 +2970,7 @@
         <v>69</v>
       </c>
       <c r="G72" s="2">
-        <v>18.03</v>
+        <v>19.03</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>70</v>
@@ -2978,16 +2978,16 @@
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B73" s="2">
-        <v>45993.31684027778</v>
+        <v>45993.31162037037</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D73" s="2">
-        <v>45993.71487268519</v>
+        <v>45993.71590277777</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>10</v>
@@ -2996,7 +2996,7 @@
         <v>69</v>
       </c>
       <c r="G73" s="2">
-        <v>25.09</v>
+        <v>22.34</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>70</v>
@@ -3004,16 +3004,16 @@
     </row>
     <row r="74" spans="1:8">
       <c r="A74" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B74" s="2">
-        <v>45992.31704861111</v>
+        <v>45992.31730324074</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D74" s="2">
-        <v>45992.7106712963</v>
+        <v>45992.71188657408</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>10</v>
@@ -3022,7 +3022,7 @@
         <v>69</v>
       </c>
       <c r="G74" s="2">
-        <v>25.09</v>
+        <v>22.59</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>70</v>
@@ -3030,7 +3030,7 @@
     </row>
     <row r="75" spans="1:8">
       <c r="A75" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B75" s="2">
         <v>45993.32466435185</v>
@@ -3056,7 +3056,7 @@
     </row>
     <row r="76" spans="1:8">
       <c r="A76" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B76" s="2">
         <v>45993.31616898148</v>
@@ -3082,16 +3082,16 @@
     </row>
     <row r="77" spans="1:8">
       <c r="A77" s="2" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B77" s="2">
-        <v>45993.31162037037</v>
+        <v>45992.3168287037</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D77" s="2">
-        <v>45993.71590277777</v>
+        <v>45992.71090277778</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>10</v>
@@ -3100,7 +3100,7 @@
         <v>69</v>
       </c>
       <c r="G77" s="2">
-        <v>22.34</v>
+        <v>19</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>70</v>
@@ -3108,16 +3108,16 @@
     </row>
     <row r="78" spans="1:8">
       <c r="A78" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B78" s="2">
-        <v>45993.31121527778</v>
+        <v>45993.31684027778</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D78" s="2">
-        <v>45993.7146875</v>
+        <v>45993.71487268519</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>10</v>
@@ -3126,7 +3126,7 @@
         <v>69</v>
       </c>
       <c r="G78" s="2">
-        <v>19</v>
+        <v>25.09</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>70</v>
@@ -3134,16 +3134,16 @@
     </row>
     <row r="79" spans="1:8">
       <c r="A79" s="2" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="B79" s="2">
-        <v>45992.31878472222</v>
+        <v>45993.31699074074</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D79" s="2">
-        <v>45992.71140046296</v>
+        <v>45993.71618055556</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>10</v>
@@ -3152,7 +3152,7 @@
         <v>69</v>
       </c>
       <c r="G79" s="2">
-        <v>19</v>
+        <v>24.09</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>70</v>
@@ -3160,16 +3160,16 @@
     </row>
     <row r="80" spans="1:8">
       <c r="A80" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B80" s="2">
-        <v>45993.31137731481</v>
+        <v>45992.36817129629</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D80" s="2">
-        <v>45993.71450231481</v>
+        <v>45992.60943287037</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>10</v>
@@ -3178,7 +3178,7 @@
         <v>69</v>
       </c>
       <c r="G80" s="2">
-        <v>19.03</v>
+        <v>22</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>70</v>
@@ -3186,16 +3186,16 @@
     </row>
     <row r="81" spans="1:8">
       <c r="A81" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B81" s="2">
-        <v>45992.31730324074</v>
+        <v>45993.44508101852</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D81" s="2">
-        <v>45992.71188657408</v>
+        <v>45993.61892361111</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>10</v>
@@ -3204,7 +3204,7 @@
         <v>69</v>
       </c>
       <c r="G81" s="2">
-        <v>22.59</v>
+        <v>22</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>70</v>
@@ -3212,16 +3212,16 @@
     </row>
     <row r="82" spans="1:8">
       <c r="A82" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B82" s="2">
-        <v>45993.31208333333</v>
+        <v>45992.31912037037</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D82" s="2">
-        <v>45993.71381944444</v>
+        <v>45992.71261574074</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>10</v>
@@ -3230,7 +3230,7 @@
         <v>69</v>
       </c>
       <c r="G82" s="2">
-        <v>19.77</v>
+        <v>12.56</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>70</v>
@@ -3238,16 +3238,16 @@
     </row>
     <row r="83" spans="1:8">
       <c r="A83" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B83" s="2">
-        <v>45993.71408564815</v>
+        <v>45992.3171875</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D83" s="2">
-        <v>45993.71423611111</v>
+        <v>45992.71112268518</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>10</v>
@@ -3256,7 +3256,7 @@
         <v>69</v>
       </c>
       <c r="G83" s="2">
-        <v>19.77</v>
+        <v>25.84</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>70</v>
@@ -3264,16 +3264,16 @@
     </row>
     <row r="84" spans="1:8">
       <c r="A84" s="2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="B84" s="2">
-        <v>45992.3168287037</v>
+        <v>45992.31704861111</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D84" s="2">
-        <v>45992.71090277778</v>
+        <v>45992.7106712963</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>10</v>
@@ -3282,7 +3282,7 @@
         <v>69</v>
       </c>
       <c r="G84" s="2">
-        <v>19</v>
+        <v>25.09</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>70</v>
@@ -3290,16 +3290,16 @@
     </row>
     <row r="85" spans="1:8">
       <c r="A85" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B85" s="2">
-        <v>45993.31672453704</v>
+        <v>45993.31284722222</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D85" s="2">
-        <v>45993.71502314815</v>
+        <v>45993.71363425926</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>10</v>
@@ -3308,7 +3308,7 @@
         <v>69</v>
       </c>
       <c r="G85" s="2">
-        <v>19</v>
+        <v>18.77</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>70</v>
@@ -3316,16 +3316,16 @@
     </row>
     <row r="86" spans="1:8">
       <c r="A86" s="2" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="B86" s="2">
-        <v>45992.32019675926</v>
+        <v>45992.31633101852</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D86" s="2">
-        <v>45992.71041666667</v>
+        <v>45992.71246527778</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>10</v>
@@ -3334,7 +3334,7 @@
         <v>69</v>
       </c>
       <c r="G86" s="2">
-        <v>24.09</v>
+        <v>19.77</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>70</v>
@@ -3342,16 +3342,16 @@
     </row>
     <row r="87" spans="1:8">
       <c r="A87" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="B87" s="2">
-        <v>45993.44508101852</v>
+        <v>45993.31208333333</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D87" s="2">
-        <v>45993.61892361111</v>
+        <v>45993.71381944444</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>10</v>
@@ -3360,7 +3360,7 @@
         <v>69</v>
       </c>
       <c r="G87" s="2">
-        <v>22</v>
+        <v>19.77</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>70</v>
@@ -3371,13 +3371,13 @@
         <v>85</v>
       </c>
       <c r="B88" s="2">
-        <v>45992.31633101852</v>
+        <v>45993.71408564815</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D88" s="2">
-        <v>45992.71246527778</v>
+        <v>45993.71423611111</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>10</v>
@@ -3394,16 +3394,16 @@
     </row>
     <row r="89" spans="1:8">
       <c r="A89" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B89" s="2">
-        <v>45992.31442129629</v>
+        <v>45992.31655092593</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D89" s="2">
-        <v>45992.71223379629</v>
+        <v>45992.71273148148</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>10</v>
@@ -3412,7 +3412,7 @@
         <v>69</v>
       </c>
       <c r="G89" s="2">
-        <v>19.03</v>
+        <v>21.06</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>70</v>
@@ -3423,13 +3423,13 @@
         <v>87</v>
       </c>
       <c r="B90" s="2">
-        <v>45992.32902777778</v>
+        <v>45993.62835648148</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D90" s="2">
-        <v>45992.6815162037</v>
+        <v>45993.75800925926</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>10</v>
@@ -3438,7 +3438,7 @@
         <v>88</v>
       </c>
       <c r="G90" s="2">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>89</v>
@@ -3449,13 +3449,13 @@
         <v>90</v>
       </c>
       <c r="B91" s="2">
-        <v>45993.33459490741</v>
+        <v>45993.33243055556</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D91" s="2">
-        <v>45993.49261574074</v>
+        <v>45993.50996527778</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>91</v>
@@ -3475,13 +3475,13 @@
         <v>90</v>
       </c>
       <c r="B92" s="2">
-        <v>45993.52398148148</v>
+        <v>45993.55333333334</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D92" s="2">
-        <v>45993.6846412037</v>
+        <v>45993.7515162037</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>10</v>
@@ -3501,23 +3501,17 @@
         <v>92</v>
       </c>
       <c r="B93" s="2">
-        <v>45992.34856481481</v>
+        <v>45992.32043981482</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D93" s="2">
-        <v>45992.3864699074</v>
-      </c>
-      <c r="E93" s="2" t="s">
-        <v>10</v>
-      </c>
+      <c r="D93" s="2"/>
+      <c r="E93" s="2"/>
       <c r="F93" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="G93" s="2">
-        <v>22.5</v>
-      </c>
+      <c r="G93" s="2"/>
       <c r="H93" s="2" t="s">
         <v>89</v>
       </c>
@@ -3527,22 +3521,22 @@
         <v>93</v>
       </c>
       <c r="B94" s="2">
-        <v>45992.33951388889</v>
+        <v>45992.32902777778</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D94" s="2">
-        <v>45992.42443287037</v>
+        <v>45992.6815162037</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G94" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>89</v>
@@ -3550,25 +3544,25 @@
     </row>
     <row r="95" spans="1:8">
       <c r="A95" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B95" s="2">
-        <v>45993.33659722222</v>
+        <v>45992.375</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D95" s="2">
-        <v>45993.54575231481</v>
+        <v>45992.66666666666</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="F95" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G95" s="2">
-        <v>15</v>
+        <v>22.5</v>
       </c>
       <c r="H95" s="2" t="s">
         <v>89</v>
@@ -3602,16 +3596,16 @@
     </row>
     <row r="97" spans="1:8">
       <c r="A97" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B97" s="2">
-        <v>45992.375</v>
+        <v>45992.54113425926</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D97" s="2">
-        <v>45992.66666666666</v>
+        <v>45992.70725694444</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>10</v>
@@ -3620,7 +3614,7 @@
         <v>88</v>
       </c>
       <c r="G97" s="2">
-        <v>22.5</v>
+        <v>16</v>
       </c>
       <c r="H97" s="2" t="s">
         <v>89</v>
@@ -3631,13 +3625,13 @@
         <v>95</v>
       </c>
       <c r="B98" s="2">
-        <v>45992.4390625</v>
+        <v>45993.54564814815</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D98" s="2">
-        <v>45992.6797337963</v>
+        <v>45993.71084490741</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>10</v>
@@ -3646,7 +3640,7 @@
         <v>88</v>
       </c>
       <c r="G98" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>89</v>
@@ -3654,25 +3648,25 @@
     </row>
     <row r="99" spans="1:8">
       <c r="A99" s="2" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="B99" s="2">
-        <v>45993.33652777778</v>
+        <v>45992.32556712963</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D99" s="2">
-        <v>45993.61788194445</v>
+        <v>45992.56069444444</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G99" s="2">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="H99" s="2" t="s">
         <v>89</v>
@@ -3683,22 +3677,22 @@
         <v>96</v>
       </c>
       <c r="B100" s="2">
-        <v>45992.33135416666</v>
+        <v>45992.33369212963</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D100" s="2">
-        <v>45992.60255787037</v>
+        <v>45992.48134259259</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="F100" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G100" s="2">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>89</v>
@@ -3709,22 +3703,22 @@
         <v>97</v>
       </c>
       <c r="B101" s="2">
-        <v>45993.33407407408</v>
+        <v>45993.33755787037</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D101" s="2">
-        <v>45993.54098379629</v>
+        <v>45993.68662037037</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G101" s="2">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>89</v>
@@ -3732,45 +3726,51 @@
     </row>
     <row r="102" spans="1:8">
       <c r="A102" s="2" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="B102" s="2">
-        <v>45992.32043981482</v>
+        <v>45992.603125</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D102" s="2"/>
-      <c r="E102" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="D102" s="2">
+        <v>45992.75163194445</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="F102" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="G102" s="2"/>
+      <c r="G102" s="2">
+        <v>17.5</v>
+      </c>
       <c r="H102" s="2" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="103" spans="1:8">
       <c r="A103" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B103" s="2">
-        <v>45993.3166087963</v>
+        <v>45992.33872685185</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D103" s="2">
-        <v>45993.70063657407</v>
+        <v>45992.46394675926</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G103" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>89</v>
@@ -3781,13 +3781,13 @@
         <v>99</v>
       </c>
       <c r="B104" s="2">
-        <v>45992.32601851852</v>
+        <v>45993.33280092593</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D104" s="2">
-        <v>45992.68008101852</v>
+        <v>45993.49769675926</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>10</v>
@@ -3796,7 +3796,7 @@
         <v>88</v>
       </c>
       <c r="G104" s="2">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>89</v>
@@ -3804,16 +3804,16 @@
     </row>
     <row r="105" spans="1:8">
       <c r="A105" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B105" s="2">
-        <v>45993.51013888889</v>
+        <v>45992.44226851852</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D105" s="2">
-        <v>45993.70188657408</v>
+        <v>45992.44354166667</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>10</v>
@@ -3822,7 +3822,7 @@
         <v>88</v>
       </c>
       <c r="G105" s="2">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>89</v>
@@ -3830,16 +3830,16 @@
     </row>
     <row r="106" spans="1:8">
       <c r="A106" s="2" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="B106" s="2">
-        <v>45993.33226851852</v>
+        <v>45993.32962962963</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D106" s="2">
-        <v>45993.48760416666</v>
+        <v>45993.59543981482</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>91</v>
@@ -3848,7 +3848,7 @@
         <v>88</v>
       </c>
       <c r="G106" s="2">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>89</v>
@@ -3859,13 +3859,13 @@
         <v>100</v>
       </c>
       <c r="B107" s="2">
-        <v>45992.340625</v>
+        <v>45992.58793981482</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D107" s="2">
-        <v>45992.5102662037</v>
+        <v>45992.75136574074</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>10</v>
@@ -3874,7 +3874,7 @@
         <v>88</v>
       </c>
       <c r="G107" s="2">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="H107" s="2" t="s">
         <v>89</v>
@@ -3885,22 +3885,22 @@
         <v>101</v>
       </c>
       <c r="B108" s="2">
-        <v>45992.33872685185</v>
+        <v>45993.54019675926</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D108" s="2">
-        <v>45992.46394675926</v>
+        <v>45993.70605324074</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="F108" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G108" s="2">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>89</v>
@@ -3908,19 +3908,19 @@
     </row>
     <row r="109" spans="1:8">
       <c r="A109" s="2" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B109" s="2">
-        <v>45993.59668981482</v>
+        <v>45993.33197916667</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D109" s="2">
-        <v>45993.70082175926</v>
+        <v>45993.57767361111</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>88</v>
@@ -3934,16 +3934,16 @@
     </row>
     <row r="110" spans="1:8">
       <c r="A110" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B110" s="2">
-        <v>45993.33197916667</v>
+        <v>45993.33644675926</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D110" s="2">
-        <v>45993.57767361111</v>
+        <v>45993.52070601852</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>91</v>
@@ -3960,13 +3960,13 @@
     </row>
     <row r="111" spans="1:8">
       <c r="A111" s="2" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B111" s="2">
         <v>45992.50671296296</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D111" s="2">
         <v>45992.70057870371</v>
@@ -3989,22 +3989,22 @@
         <v>102</v>
       </c>
       <c r="B112" s="2">
-        <v>45992.33369212963</v>
+        <v>45993.51013888889</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D112" s="2">
-        <v>45992.48134259259</v>
+        <v>45993.70188657408</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="F112" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G112" s="2">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="H112" s="2" t="s">
         <v>89</v>
@@ -4012,25 +4012,25 @@
     </row>
     <row r="113" spans="1:8">
       <c r="A113" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B113" s="2">
-        <v>45993.33755787037</v>
+        <v>45993.33226851852</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D113" s="2">
-        <v>45993.68662037037</v>
+        <v>45993.48760416666</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="F113" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G113" s="2">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="H113" s="2" t="s">
         <v>89</v>
@@ -4038,16 +4038,16 @@
     </row>
     <row r="114" spans="1:8">
       <c r="A114" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B114" s="2">
-        <v>45992.58239583333</v>
+        <v>45992.340625</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D114" s="2">
-        <v>45992.67513888889</v>
+        <v>45992.5102662037</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>10</v>
@@ -4056,7 +4056,7 @@
         <v>88</v>
       </c>
       <c r="G114" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H114" s="2" t="s">
         <v>89</v>
@@ -4064,25 +4064,25 @@
     </row>
     <row r="115" spans="1:8">
       <c r="A115" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B115" s="2">
-        <v>45992.32942129629</v>
+        <v>45993.58587962963</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D115" s="2">
-        <v>45992.5415162037</v>
+        <v>45993.75435185185</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="F115" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G115" s="2">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="H115" s="2" t="s">
         <v>89</v>
@@ -4090,16 +4090,16 @@
     </row>
     <row r="116" spans="1:8">
       <c r="A116" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B116" s="2">
-        <v>45992.33333333334</v>
+        <v>45992.55483796296</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D116" s="2">
-        <v>45992.67053240741</v>
+        <v>45992.68207175926</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>10</v>
@@ -4108,7 +4108,7 @@
         <v>88</v>
       </c>
       <c r="G116" s="2">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="H116" s="2" t="s">
         <v>89</v>
@@ -4116,25 +4116,25 @@
     </row>
     <row r="117" spans="1:8">
       <c r="A117" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B117" s="2">
-        <v>45993.55333333334</v>
+        <v>45993.33583333333</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D117" s="2">
-        <v>45993.7515162037</v>
+        <v>45993.59112268518</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="F117" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G117" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H117" s="2" t="s">
         <v>89</v>
@@ -4142,25 +4142,25 @@
     </row>
     <row r="118" spans="1:8">
       <c r="A118" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B118" s="2">
-        <v>45993.33644675926</v>
+        <v>45993.55733796296</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D118" s="2">
-        <v>45993.52070601852</v>
+        <v>45993.70209490741</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G118" s="2">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="H118" s="2" t="s">
         <v>89</v>
@@ -4171,22 +4171,22 @@
         <v>106</v>
       </c>
       <c r="B119" s="2">
-        <v>45993.54019675926</v>
+        <v>45992.32942129629</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D119" s="2">
-        <v>45993.70605324074</v>
+        <v>45992.5415162037</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G119" s="2">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="H119" s="2" t="s">
         <v>89</v>
@@ -4194,16 +4194,16 @@
     </row>
     <row r="120" spans="1:8">
       <c r="A120" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B120" s="2">
-        <v>45993.33037037037</v>
+        <v>45992.58239583333</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D120" s="2">
-        <v>45993.50478009259</v>
+        <v>45992.67513888889</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>10</v>
@@ -4212,7 +4212,7 @@
         <v>88</v>
       </c>
       <c r="G120" s="2">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="H120" s="2" t="s">
         <v>89</v>
@@ -4223,22 +4223,22 @@
         <v>107</v>
       </c>
       <c r="B121" s="2">
-        <v>45993.58587962963</v>
+        <v>45993.33459490741</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D121" s="2">
-        <v>45993.75435185185</v>
+        <v>45993.49261574074</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="F121" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G121" s="2">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="H121" s="2" t="s">
         <v>89</v>
@@ -4246,25 +4246,25 @@
     </row>
     <row r="122" spans="1:8">
       <c r="A122" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B122" s="2">
-        <v>45993.33583333333</v>
+        <v>45993.52398148148</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D122" s="2">
-        <v>45993.59112268518</v>
+        <v>45993.6846412037</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G122" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H122" s="2" t="s">
         <v>89</v>
@@ -4272,16 +4272,16 @@
     </row>
     <row r="123" spans="1:8">
       <c r="A123" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B123" s="2">
-        <v>45992.375</v>
+        <v>45992.34856481481</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D123" s="2">
-        <v>45992.66666666666</v>
+        <v>45992.3864699074</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>10</v>
@@ -4298,25 +4298,25 @@
     </row>
     <row r="124" spans="1:8">
       <c r="A124" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B124" s="2">
-        <v>45993.375</v>
+        <v>45993.33475694444</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D124" s="2">
-        <v>45993.70833333334</v>
+        <v>45993.53561342593</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="F124" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G124" s="2">
-        <v>22.5</v>
+        <v>18</v>
       </c>
       <c r="H124" s="2" t="s">
         <v>89</v>
@@ -4324,25 +4324,25 @@
     </row>
     <row r="125" spans="1:8">
       <c r="A125" s="2" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="B125" s="2">
-        <v>45992.54113425926</v>
+        <v>45992.33802083333</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D125" s="2">
-        <v>45992.70725694444</v>
+        <v>45992.51306712963</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="F125" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G125" s="2">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="H125" s="2" t="s">
         <v>89</v>
@@ -4350,16 +4350,16 @@
     </row>
     <row r="126" spans="1:8">
       <c r="A126" s="2" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="B126" s="2">
-        <v>45993.54564814815</v>
+        <v>45993.33037037037</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D126" s="2">
-        <v>45993.71084490741</v>
+        <v>45993.50478009259</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>10</v>
@@ -4368,7 +4368,7 @@
         <v>88</v>
       </c>
       <c r="G126" s="2">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="H126" s="2" t="s">
         <v>89</v>
@@ -4376,16 +4376,16 @@
     </row>
     <row r="127" spans="1:8">
       <c r="A127" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B127" s="2">
-        <v>45992.32556712963</v>
+        <v>45993.33417824074</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D127" s="2">
-        <v>45992.56069444444</v>
+        <v>45993.54109953704</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>91</v>
@@ -4394,7 +4394,7 @@
         <v>88</v>
       </c>
       <c r="G127" s="2">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="H127" s="2" t="s">
         <v>89</v>
@@ -4402,16 +4402,16 @@
     </row>
     <row r="128" spans="1:8">
       <c r="A128" s="2" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="B128" s="2">
-        <v>45992.603125</v>
+        <v>45993.59668981482</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D128" s="2">
-        <v>45992.75163194445</v>
+        <v>45993.70082175926</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>10</v>
@@ -4428,16 +4428,16 @@
     </row>
     <row r="129" spans="1:8">
       <c r="A129" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B129" s="2">
-        <v>45993.32962962963</v>
+        <v>45992.33951388889</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D129" s="2">
-        <v>45993.59543981482</v>
+        <v>45992.42443287037</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>91</v>
@@ -4446,7 +4446,7 @@
         <v>88</v>
       </c>
       <c r="G129" s="2">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>89</v>
@@ -4454,25 +4454,25 @@
     </row>
     <row r="130" spans="1:8">
       <c r="A130" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B130" s="2">
-        <v>45993.62835648148</v>
+        <v>45993.33659722222</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D130" s="2">
-        <v>45993.75800925926</v>
+        <v>45993.54575231481</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="F130" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G130" s="2">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="H130" s="2" t="s">
         <v>89</v>
@@ -4480,16 +4480,16 @@
     </row>
     <row r="131" spans="1:8">
       <c r="A131" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B131" s="2">
-        <v>45992.44226851852</v>
+        <v>45992.33333333334</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D131" s="2">
-        <v>45992.44354166667</v>
+        <v>45992.67053240741</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>10</v>
@@ -4498,7 +4498,7 @@
         <v>88</v>
       </c>
       <c r="G131" s="2">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="H131" s="2" t="s">
         <v>89</v>
@@ -4506,16 +4506,16 @@
     </row>
     <row r="132" spans="1:8">
       <c r="A132" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B132" s="2">
-        <v>45993.33280092593</v>
+        <v>45993.55407407408</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D132" s="2">
-        <v>45993.49769675926</v>
+        <v>45993.68141203704</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>10</v>
@@ -4524,7 +4524,7 @@
         <v>88</v>
       </c>
       <c r="G132" s="2">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="H132" s="2" t="s">
         <v>89</v>
@@ -4532,25 +4532,25 @@
     </row>
     <row r="133" spans="1:8">
       <c r="A133" s="2" t="s">
-        <v>25</v>
+        <v>112</v>
       </c>
       <c r="B133" s="2">
-        <v>45992.33506944445</v>
+        <v>45992.33135416666</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D133" s="2">
-        <v>45992.53091435185</v>
+        <v>45992.60255787037</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="F133" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G133" s="2">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="H133" s="2" t="s">
         <v>89</v>
@@ -4558,16 +4558,16 @@
     </row>
     <row r="134" spans="1:8">
       <c r="A134" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B134" s="2">
-        <v>45992.58793981482</v>
+        <v>45993.33652777778</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D134" s="2">
-        <v>45992.75136574074</v>
+        <v>45993.61788194445</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>10</v>
@@ -4576,7 +4576,7 @@
         <v>88</v>
       </c>
       <c r="G134" s="2">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>89</v>
@@ -4584,25 +4584,25 @@
     </row>
     <row r="135" spans="1:8">
       <c r="A135" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B135" s="2">
-        <v>45992.33333333334</v>
+        <v>45993.33407407408</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D135" s="2">
-        <v>45992.67103009259</v>
+        <v>45993.54098379629</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="F135" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G135" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>89</v>
@@ -4610,25 +4610,25 @@
     </row>
     <row r="136" spans="1:8">
       <c r="A136" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B136" s="2">
-        <v>45993.33417824074</v>
+        <v>45992.375</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D136" s="2">
-        <v>45993.54109953704</v>
+        <v>45992.66666666666</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="F136" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G136" s="2">
-        <v>15</v>
+        <v>22.5</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>89</v>
@@ -4636,16 +4636,16 @@
     </row>
     <row r="137" spans="1:8">
       <c r="A137" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B137" s="2">
-        <v>45993.55407407408</v>
+        <v>45993.375</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D137" s="2">
-        <v>45993.68141203704</v>
+        <v>45993.70833333334</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>10</v>
@@ -4654,7 +4654,7 @@
         <v>88</v>
       </c>
       <c r="G137" s="2">
-        <v>15</v>
+        <v>22.5</v>
       </c>
       <c r="H137" s="2" t="s">
         <v>89</v>
@@ -4662,19 +4662,19 @@
     </row>
     <row r="138" spans="1:8">
       <c r="A138" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B138" s="2">
-        <v>45993.33475694444</v>
+        <v>45992.32601851852</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D138" s="2">
-        <v>45993.53561342593</v>
+        <v>45992.68008101852</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="F138" s="2" t="s">
         <v>88</v>
@@ -4688,16 +4688,16 @@
     </row>
     <row r="139" spans="1:8">
       <c r="A139" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B139" s="2">
-        <v>45993.55733796296</v>
+        <v>45993.3166087963</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D139" s="2">
-        <v>45993.70209490741</v>
+        <v>45993.70063657407</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>10</v>
@@ -4714,16 +4714,16 @@
     </row>
     <row r="140" spans="1:8">
       <c r="A140" s="2" t="s">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="B140" s="2">
-        <v>45993.33243055556</v>
+        <v>45992.33506944445</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D140" s="2">
-        <v>45993.50996527778</v>
+        <v>45992.53091435185</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>91</v>
@@ -4732,7 +4732,7 @@
         <v>88</v>
       </c>
       <c r="G140" s="2">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>89</v>
@@ -4740,16 +4740,16 @@
     </row>
     <row r="141" spans="1:8">
       <c r="A141" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B141" s="2">
-        <v>45992.55483796296</v>
+        <v>45992.33333333334</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D141" s="2">
-        <v>45992.68207175926</v>
+        <v>45992.67103009259</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>10</v>
@@ -4758,7 +4758,7 @@
         <v>88</v>
       </c>
       <c r="G141" s="2">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="H141" s="2" t="s">
         <v>89</v>
@@ -4766,25 +4766,25 @@
     </row>
     <row r="142" spans="1:8">
       <c r="A142" s="2" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="B142" s="2">
-        <v>45992.33802083333</v>
+        <v>45992.4390625</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D142" s="2">
-        <v>45992.51306712963</v>
+        <v>45992.6797337963</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="F142" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G142" s="2">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="H142" s="2" t="s">
         <v>89</v>
@@ -4798,13 +4798,13 @@
         <v>45993</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D143" s="2">
         <v>45993</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F143" s="2" t="s">
         <v>117</v>
@@ -4824,13 +4824,13 @@
         <v>45993.33333333334</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D144" s="2">
         <v>45993.33333333334</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F144" s="2" t="s">
         <v>117</v>
@@ -4870,39 +4870,39 @@
     </row>
     <row r="146" spans="1:8">
       <c r="A146" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B146" s="2">
+        <v>45993.58836805556</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D146" s="2">
+        <v>45993.70449074074</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F146" s="2" t="s">
         <v>120</v>
-      </c>
-      <c r="B146" s="2">
-        <v>45992.54988425926</v>
-      </c>
-      <c r="C146" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D146" s="2">
-        <v>45992.6850462963</v>
-      </c>
-      <c r="E146" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F146" s="2" t="s">
-        <v>121</v>
       </c>
       <c r="G146" s="2">
         <v>15</v>
       </c>
       <c r="H146" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="147" spans="1:8">
       <c r="A147" s="2" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="B147" s="2">
         <v>45992.48001157407</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D147" s="2">
         <v>45992.70277777778</v>
@@ -4911,50 +4911,50 @@
         <v>10</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G147" s="2">
         <v>15</v>
       </c>
       <c r="H147" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="148" spans="1:8">
       <c r="A148" s="2" t="s">
-        <v>93</v>
+        <v>122</v>
       </c>
       <c r="B148" s="2">
-        <v>45993.58836805556</v>
+        <v>45992.54988425926</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D148" s="2">
-        <v>45993.70449074074</v>
+        <v>45992.6850462963</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G148" s="2">
         <v>15</v>
       </c>
       <c r="H148" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="149" spans="1:8">
       <c r="A149" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B149" s="2">
         <v>45993.61039351852</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D149" s="2">
         <v>45993.68513888889</v>
@@ -5003,13 +5003,13 @@
         <v>128</v>
       </c>
       <c r="B151" s="2">
-        <v>45992.30037037037</v>
+        <v>45992.34711805556</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D151" s="2">
-        <v>45992.70363425926</v>
+        <v>45992.68376157407</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>10</v>
@@ -5018,7 +5018,7 @@
         <v>129</v>
       </c>
       <c r="G151" s="2">
-        <v>18</v>
+        <v>13.65</v>
       </c>
       <c r="H151" s="2" t="s">
         <v>130</v>
@@ -5026,16 +5026,16 @@
     </row>
     <row r="152" spans="1:8">
       <c r="A152" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B152" s="2">
-        <v>45993.32821759259</v>
+        <v>45993.34043981481</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D152" s="2">
-        <v>45993.34375</v>
+        <v>45993.68324074074</v>
       </c>
       <c r="E152" s="2" t="s">
         <v>10</v>
@@ -5044,7 +5044,7 @@
         <v>129</v>
       </c>
       <c r="G152" s="2">
-        <v>17.48</v>
+        <v>13.65</v>
       </c>
       <c r="H152" s="2" t="s">
         <v>130</v>
@@ -5052,25 +5052,25 @@
     </row>
     <row r="153" spans="1:8">
       <c r="A153" s="2" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="B153" s="2">
-        <v>45992.32685185185</v>
+        <v>45992.35592592593</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D153" s="2">
-        <v>45992.66329861111</v>
+        <v>45992.52112268518</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="F153" s="2" t="s">
         <v>129</v>
       </c>
       <c r="G153" s="2">
-        <v>17.48</v>
+        <v>15</v>
       </c>
       <c r="H153" s="2" t="s">
         <v>130</v>
@@ -5078,16 +5078,16 @@
     </row>
     <row r="154" spans="1:8">
       <c r="A154" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B154" s="2">
-        <v>45992.34711805556</v>
+        <v>45992.30037037037</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D154" s="2">
-        <v>45992.68376157407</v>
+        <v>45992.70363425926</v>
       </c>
       <c r="E154" s="2" t="s">
         <v>10</v>
@@ -5096,7 +5096,7 @@
         <v>129</v>
       </c>
       <c r="G154" s="2">
-        <v>13.65</v>
+        <v>18</v>
       </c>
       <c r="H154" s="2" t="s">
         <v>130</v>
@@ -5104,16 +5104,16 @@
     </row>
     <row r="155" spans="1:8">
       <c r="A155" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B155" s="2">
-        <v>45993.34043981481</v>
+        <v>45993.34569444445</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D155" s="2">
-        <v>45993.68324074074</v>
+        <v>45993.69732638889</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>10</v>
@@ -5122,7 +5122,7 @@
         <v>129</v>
       </c>
       <c r="G155" s="2">
-        <v>13.65</v>
+        <v>18</v>
       </c>
       <c r="H155" s="2" t="s">
         <v>130</v>
@@ -5130,16 +5130,16 @@
     </row>
     <row r="156" spans="1:8">
       <c r="A156" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B156" s="2">
-        <v>45993.33630787037</v>
+        <v>45992.32685185185</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D156" s="2">
-        <v>45993.66971064815</v>
+        <v>45992.66329861111</v>
       </c>
       <c r="E156" s="2" t="s">
         <v>10</v>
@@ -5148,7 +5148,7 @@
         <v>129</v>
       </c>
       <c r="G156" s="2">
-        <v>21</v>
+        <v>17.48</v>
       </c>
       <c r="H156" s="2" t="s">
         <v>130</v>
@@ -5156,25 +5156,25 @@
     </row>
     <row r="157" spans="1:8">
       <c r="A157" s="2" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="B157" s="2">
-        <v>45992.35592592593</v>
+        <v>45993.32821759259</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D157" s="2">
-        <v>45992.52112268518</v>
+        <v>45993.34375</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="F157" s="2" t="s">
         <v>129</v>
       </c>
       <c r="G157" s="2">
-        <v>15</v>
+        <v>17.48</v>
       </c>
       <c r="H157" s="2" t="s">
         <v>130</v>
@@ -5182,16 +5182,16 @@
     </row>
     <row r="158" spans="1:8">
       <c r="A158" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="B158" s="2">
-        <v>45993.34569444445</v>
+        <v>45993.33630787037</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D158" s="2">
-        <v>45993.69732638889</v>
+        <v>45993.66971064815</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>10</v>
@@ -5200,7 +5200,7 @@
         <v>129</v>
       </c>
       <c r="G158" s="2">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H158" s="2" t="s">
         <v>130</v>
@@ -5211,13 +5211,13 @@
         <v>134</v>
       </c>
       <c r="B159" s="2">
-        <v>45992.39802083333</v>
+        <v>45993.83056712963</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D159" s="2">
-        <v>45992.63327546296</v>
+        <v>45993.91854166667</v>
       </c>
       <c r="E159" s="2" t="s">
         <v>10</v>
@@ -5226,7 +5226,7 @@
         <v>135</v>
       </c>
       <c r="G159" s="2">
-        <v>15.16</v>
+        <v>24</v>
       </c>
       <c r="H159" s="2" t="s">
         <v>136</v>
@@ -5237,13 +5237,13 @@
         <v>137</v>
       </c>
       <c r="B160" s="2">
-        <v>45993.83056712963</v>
+        <v>45992.39802083333</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D160" s="2">
-        <v>45993.91854166667</v>
+        <v>45992.63327546296</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>10</v>
@@ -5252,7 +5252,7 @@
         <v>135</v>
       </c>
       <c r="G160" s="2">
-        <v>24</v>
+        <v>15.16</v>
       </c>
       <c r="H160" s="2" t="s">
         <v>136</v>
@@ -5289,13 +5289,13 @@
         <v>141</v>
       </c>
       <c r="B162" s="2">
-        <v>45992.32082175926</v>
+        <v>45992.54193287037</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D162" s="2">
-        <v>45992.61207175926</v>
+        <v>45992.72916666666</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>10</v>
@@ -5304,7 +5304,7 @@
         <v>142</v>
       </c>
       <c r="G162" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H162" s="2" t="s">
         <v>143</v>
@@ -5315,13 +5315,13 @@
         <v>144</v>
       </c>
       <c r="B163" s="2">
-        <v>45992.31788194444</v>
+        <v>45992.33707175926</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D163" s="2">
-        <v>45992.62767361111</v>
+        <v>45992.59480324074</v>
       </c>
       <c r="E163" s="2" t="s">
         <v>10</v>
@@ -5330,7 +5330,7 @@
         <v>142</v>
       </c>
       <c r="G163" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H163" s="2" t="s">
         <v>143</v>
@@ -5338,16 +5338,16 @@
     </row>
     <row r="164" spans="1:8">
       <c r="A164" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B164" s="2">
-        <v>45993.32019675926</v>
+        <v>45993.32221064815</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D164" s="2">
-        <v>45993.68831018519</v>
+        <v>45993.67194444445</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>10</v>
@@ -5356,7 +5356,7 @@
         <v>142</v>
       </c>
       <c r="G164" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H164" s="2" t="s">
         <v>143</v>
@@ -5364,16 +5364,16 @@
     </row>
     <row r="165" spans="1:8">
       <c r="A165" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B165" s="2">
-        <v>45993.3390625</v>
+        <v>45993.3440625</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D165" s="2">
-        <v>45993.61498842593</v>
+        <v>45993.61761574074</v>
       </c>
       <c r="E165" s="2" t="s">
         <v>10</v>
@@ -5390,16 +5390,16 @@
     </row>
     <row r="166" spans="1:8">
       <c r="A166" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B166" s="2">
-        <v>45993.3440625</v>
+        <v>45993.3390625</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D166" s="2">
-        <v>45993.61761574074</v>
+        <v>45993.61498842593</v>
       </c>
       <c r="E166" s="2" t="s">
         <v>10</v>
@@ -5416,16 +5416,16 @@
     </row>
     <row r="167" spans="1:8">
       <c r="A167" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B167" s="2">
-        <v>45992.33707175926</v>
+        <v>45993.32019675926</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D167" s="2">
-        <v>45992.59480324074</v>
+        <v>45993.68831018519</v>
       </c>
       <c r="E167" s="2" t="s">
         <v>10</v>
@@ -5434,7 +5434,7 @@
         <v>142</v>
       </c>
       <c r="G167" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H167" s="2" t="s">
         <v>143</v>
@@ -5442,16 +5442,16 @@
     </row>
     <row r="168" spans="1:8">
       <c r="A168" s="2" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="B168" s="2">
-        <v>45993.32221064815</v>
+        <v>45992.31788194444</v>
       </c>
       <c r="C168" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D168" s="2">
-        <v>45993.67194444445</v>
+        <v>45992.62767361111</v>
       </c>
       <c r="E168" s="2" t="s">
         <v>10</v>
@@ -5460,7 +5460,7 @@
         <v>142</v>
       </c>
       <c r="G168" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H168" s="2" t="s">
         <v>143</v>
@@ -5468,16 +5468,16 @@
     </row>
     <row r="169" spans="1:8">
       <c r="A169" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B169" s="2">
-        <v>45992.54193287037</v>
+        <v>45992.32082175926</v>
       </c>
       <c r="C169" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D169" s="2">
-        <v>45992.72916666666</v>
+        <v>45992.61207175926</v>
       </c>
       <c r="E169" s="2" t="s">
         <v>10</v>
@@ -5486,7 +5486,7 @@
         <v>142</v>
       </c>
       <c r="G169" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H169" s="2" t="s">
         <v>143</v>
@@ -5497,13 +5497,13 @@
         <v>149</v>
       </c>
       <c r="B170" s="2">
-        <v>45993.47211805556</v>
+        <v>45993.42930555555</v>
       </c>
       <c r="C170" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D170" s="2">
-        <v>45993.69221064815</v>
+        <v>45993.82324074074</v>
       </c>
       <c r="E170" s="2" t="s">
         <v>10</v>
@@ -5512,7 +5512,7 @@
         <v>150</v>
       </c>
       <c r="G170" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H170" s="2" t="s">
         <v>151</v>
@@ -5520,16 +5520,16 @@
     </row>
     <row r="171" spans="1:8">
       <c r="A171" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B171" s="2">
-        <v>45993.42930555555</v>
+        <v>45992.87222222222</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D171" s="2">
-        <v>45993.82324074074</v>
+        <v>45992.87225694444</v>
       </c>
       <c r="E171" s="2" t="s">
         <v>10</v>
@@ -5546,25 +5546,25 @@
     </row>
     <row r="172" spans="1:8">
       <c r="A172" s="2" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B172" s="2">
-        <v>45993.34152777777</v>
+        <v>45992.4106712963</v>
       </c>
       <c r="C172" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D172" s="2">
-        <v>45993.58498842592</v>
+        <v>45992.52935185185</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="F172" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G172" s="2">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H172" s="2" t="s">
         <v>151</v>
@@ -5572,16 +5572,16 @@
     </row>
     <row r="173" spans="1:8">
       <c r="A173" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B173" s="2">
-        <v>45992.89799768518</v>
+        <v>45993.41944444444</v>
       </c>
       <c r="C173" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D173" s="2">
-        <v>45992.89809027778</v>
+        <v>45993.82296296296</v>
       </c>
       <c r="E173" s="2" t="s">
         <v>10</v>
@@ -5590,7 +5590,7 @@
         <v>150</v>
       </c>
       <c r="G173" s="2">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H173" s="2" t="s">
         <v>151</v>
@@ -5598,16 +5598,16 @@
     </row>
     <row r="174" spans="1:8">
       <c r="A174" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B174" s="2">
-        <v>45992.55707175926</v>
+        <v>45993.34152777777</v>
       </c>
       <c r="C174" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D174" s="2">
-        <v>45992.87207175926</v>
+        <v>45993.58498842592</v>
       </c>
       <c r="E174" s="2" t="s">
         <v>10</v>
@@ -5616,7 +5616,7 @@
         <v>150</v>
       </c>
       <c r="G174" s="2">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H174" s="2" t="s">
         <v>151</v>
@@ -5624,16 +5624,16 @@
     </row>
     <row r="175" spans="1:8">
       <c r="A175" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B175" s="2">
-        <v>45993.41944444444</v>
+        <v>45993.47211805556</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D175" s="2">
-        <v>45993.82296296296</v>
+        <v>45993.69221064815</v>
       </c>
       <c r="E175" s="2" t="s">
         <v>10</v>
@@ -5642,7 +5642,7 @@
         <v>150</v>
       </c>
       <c r="G175" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H175" s="2" t="s">
         <v>151</v>
@@ -5653,13 +5653,13 @@
         <v>152</v>
       </c>
       <c r="B176" s="2">
-        <v>45992.87222222222</v>
+        <v>45992.55707175926</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D176" s="2">
-        <v>45992.87225694444</v>
+        <v>45992.87207175926</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>10</v>
@@ -5668,7 +5668,7 @@
         <v>150</v>
       </c>
       <c r="G176" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H176" s="2" t="s">
         <v>151</v>
@@ -5676,25 +5676,25 @@
     </row>
     <row r="177" spans="1:8">
       <c r="A177" s="2" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B177" s="2">
-        <v>45992.4106712963</v>
+        <v>45992.89799768518</v>
       </c>
       <c r="C177" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D177" s="2">
-        <v>45992.52935185185</v>
+        <v>45992.89809027778</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="F177" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G177" s="2">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H177" s="2" t="s">
         <v>151</v>
@@ -5705,13 +5705,13 @@
         <v>156</v>
       </c>
       <c r="B178" s="2">
-        <v>45993.62489583333</v>
+        <v>45992.32685185185</v>
       </c>
       <c r="C178" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D178" s="2">
-        <v>45993.90871527778</v>
+        <v>45992.67736111111</v>
       </c>
       <c r="E178" s="2" t="s">
         <v>10</v>
@@ -5720,7 +5720,7 @@
         <v>157</v>
       </c>
       <c r="G178" s="2">
-        <v>13.65</v>
+        <v>23.69</v>
       </c>
       <c r="H178" s="2" t="s">
         <v>158</v>
@@ -5728,16 +5728,16 @@
     </row>
     <row r="179" spans="1:8">
       <c r="A179" s="2" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="B179" s="2">
-        <v>45992.40159722222</v>
+        <v>45992.36230324074</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D179" s="2">
-        <v>45992.67126157408</v>
+        <v>45992.68001157408</v>
       </c>
       <c r="E179" s="2" t="s">
         <v>10</v>
@@ -5746,7 +5746,7 @@
         <v>157</v>
       </c>
       <c r="G179" s="2">
-        <v>15.16</v>
+        <v>21</v>
       </c>
       <c r="H179" s="2" t="s">
         <v>158</v>
@@ -5757,13 +5757,13 @@
         <v>159</v>
       </c>
       <c r="B180" s="2">
-        <v>45993.39545138889</v>
+        <v>45992.37811342593</v>
       </c>
       <c r="C180" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D180" s="2">
-        <v>45993.68545138889</v>
+        <v>45992.69790509259</v>
       </c>
       <c r="E180" s="2" t="s">
         <v>10</v>
@@ -5772,7 +5772,7 @@
         <v>157</v>
       </c>
       <c r="G180" s="2">
-        <v>15.16</v>
+        <v>13.65</v>
       </c>
       <c r="H180" s="2" t="s">
         <v>158</v>
@@ -5780,16 +5780,16 @@
     </row>
     <row r="181" spans="1:8">
       <c r="A181" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B181" s="2">
-        <v>45992.33592592592</v>
+        <v>45993.37516203704</v>
       </c>
       <c r="C181" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D181" s="2">
-        <v>45992.69883101852</v>
+        <v>45993.6992824074</v>
       </c>
       <c r="E181" s="2" t="s">
         <v>10</v>
@@ -5798,7 +5798,7 @@
         <v>157</v>
       </c>
       <c r="G181" s="2">
-        <v>15</v>
+        <v>13.65</v>
       </c>
       <c r="H181" s="2" t="s">
         <v>158</v>
@@ -5806,16 +5806,16 @@
     </row>
     <row r="182" spans="1:8">
       <c r="A182" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B182" s="2">
-        <v>45992.58358796296</v>
+        <v>45993.58287037037</v>
       </c>
       <c r="C182" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D182" s="2">
-        <v>45992.89682870371</v>
+        <v>45993.91707175926</v>
       </c>
       <c r="E182" s="2" t="s">
         <v>10</v>
@@ -5824,7 +5824,7 @@
         <v>157</v>
       </c>
       <c r="G182" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H182" s="2" t="s">
         <v>158</v>
@@ -5832,16 +5832,16 @@
     </row>
     <row r="183" spans="1:8">
       <c r="A183" s="2" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="B183" s="2">
-        <v>45993.5765625</v>
+        <v>45993.32638888889</v>
       </c>
       <c r="C183" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D183" s="2">
-        <v>45993.91775462963</v>
+        <v>45993.58686342592</v>
       </c>
       <c r="E183" s="2" t="s">
         <v>10</v>
@@ -5850,7 +5850,7 @@
         <v>157</v>
       </c>
       <c r="G183" s="2">
-        <v>22</v>
+        <v>23.69</v>
       </c>
       <c r="H183" s="2" t="s">
         <v>158</v>
@@ -5858,19 +5858,19 @@
     </row>
     <row r="184" spans="1:8">
       <c r="A184" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B184" s="2">
-        <v>45992.33333333334</v>
+        <v>45993.62489583333</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D184" s="2">
-        <v>45992.33333333334</v>
+        <v>45993.90871527778</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F184" s="2" t="s">
         <v>157</v>
@@ -5884,16 +5884,16 @@
     </row>
     <row r="185" spans="1:8">
       <c r="A185" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B185" s="2">
-        <v>45993.37694444445</v>
+        <v>45992.33592592592</v>
       </c>
       <c r="C185" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D185" s="2">
-        <v>45993.72078703704</v>
+        <v>45992.69883101852</v>
       </c>
       <c r="E185" s="2" t="s">
         <v>10</v>
@@ -5902,7 +5902,7 @@
         <v>157</v>
       </c>
       <c r="G185" s="2">
-        <v>13.65</v>
+        <v>15</v>
       </c>
       <c r="H185" s="2" t="s">
         <v>158</v>
@@ -5910,7 +5910,7 @@
     </row>
     <row r="186" spans="1:8">
       <c r="A186" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B186" s="2">
         <v>45992.3703587963</v>
@@ -5936,7 +5936,7 @@
     </row>
     <row r="187" spans="1:8">
       <c r="A187" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B187" s="2">
         <v>45992.71581018518</v>
@@ -5962,10 +5962,10 @@
     </row>
     <row r="188" spans="1:8">
       <c r="A188" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B188" s="2">
-        <v>45992.6641087963</v>
+        <v>45992.64875</v>
       </c>
       <c r="C188" s="2" t="s">
         <v>9</v>
@@ -5975,25 +5975,23 @@
       <c r="F188" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="G188" s="2">
-        <v>13.65</v>
-      </c>
+      <c r="G188" s="2"/>
       <c r="H188" s="2" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="189" spans="1:8">
       <c r="A189" s="2" t="s">
-        <v>166</v>
+        <v>144</v>
       </c>
       <c r="B189" s="2">
-        <v>45993.69541666667</v>
+        <v>45993.33579861111</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D189" s="2">
-        <v>45993.9084375</v>
+        <v>45993.64005787037</v>
       </c>
       <c r="E189" s="2" t="s">
         <v>10</v>
@@ -6002,7 +6000,7 @@
         <v>157</v>
       </c>
       <c r="G189" s="2">
-        <v>13.65</v>
+        <v>19</v>
       </c>
       <c r="H189" s="2" t="s">
         <v>158</v>
@@ -6010,25 +6008,25 @@
     </row>
     <row r="190" spans="1:8">
       <c r="A190" s="2" t="s">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="B190" s="2">
-        <v>45993.57520833334</v>
+        <v>45992.58185185185</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D190" s="2">
-        <v>45993.80771990741</v>
+        <v>45992.8978125</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="F190" s="2" t="s">
         <v>157</v>
       </c>
       <c r="G190" s="2">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H190" s="2" t="s">
         <v>158</v>
@@ -6036,7 +6034,7 @@
     </row>
     <row r="191" spans="1:8">
       <c r="A191" s="2" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="B191" s="2">
         <v>45992.58297453704</v>
@@ -6062,16 +6060,16 @@
     </row>
     <row r="192" spans="1:8">
       <c r="A192" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B192" s="2">
-        <v>45993.58287037037</v>
+        <v>45992.40159722222</v>
       </c>
       <c r="C192" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D192" s="2">
-        <v>45993.91707175926</v>
+        <v>45992.67126157408</v>
       </c>
       <c r="E192" s="2" t="s">
         <v>10</v>
@@ -6080,7 +6078,7 @@
         <v>157</v>
       </c>
       <c r="G192" s="2">
-        <v>24</v>
+        <v>15.16</v>
       </c>
       <c r="H192" s="2" t="s">
         <v>158</v>
@@ -6088,16 +6086,16 @@
     </row>
     <row r="193" spans="1:8">
       <c r="A193" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B193" s="2">
-        <v>45992.32685185185</v>
+        <v>45992.31797453704</v>
       </c>
       <c r="C193" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D193" s="2">
-        <v>45992.67736111111</v>
+        <v>45992.625</v>
       </c>
       <c r="E193" s="2" t="s">
         <v>10</v>
@@ -6106,7 +6104,7 @@
         <v>157</v>
       </c>
       <c r="G193" s="2">
-        <v>23.69</v>
+        <v>20</v>
       </c>
       <c r="H193" s="2" t="s">
         <v>158</v>
@@ -6114,25 +6112,25 @@
     </row>
     <row r="194" spans="1:8">
       <c r="A194" s="2" t="s">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="B194" s="2">
-        <v>45993.32638888889</v>
+        <v>45993.57520833334</v>
       </c>
       <c r="C194" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D194" s="2">
-        <v>45993.58686342592</v>
+        <v>45993.80771990741</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="F194" s="2" t="s">
         <v>157</v>
       </c>
       <c r="G194" s="2">
-        <v>23.69</v>
+        <v>24</v>
       </c>
       <c r="H194" s="2" t="s">
         <v>158</v>
@@ -6140,25 +6138,25 @@
     </row>
     <row r="195" spans="1:8">
       <c r="A195" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B195" s="2">
-        <v>45993.33333333334</v>
+        <v>45993.39545138889</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D195" s="2">
-        <v>45993.33333333334</v>
+        <v>45993.68545138889</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F195" s="2" t="s">
         <v>157</v>
       </c>
       <c r="G195" s="2">
-        <v>13.65</v>
+        <v>15.16</v>
       </c>
       <c r="H195" s="2" t="s">
         <v>158</v>
@@ -6166,25 +6164,25 @@
     </row>
     <row r="196" spans="1:8">
       <c r="A196" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B196" s="2">
-        <v>45992.31797453704</v>
+        <v>45993.33333333334</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D196" s="2">
-        <v>45992.625</v>
+        <v>45993.33333333334</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F196" s="2" t="s">
         <v>157</v>
       </c>
       <c r="G196" s="2">
-        <v>20</v>
+        <v>13.65</v>
       </c>
       <c r="H196" s="2" t="s">
         <v>158</v>
@@ -6192,19 +6190,19 @@
     </row>
     <row r="197" spans="1:8">
       <c r="A197" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B197" s="2">
-        <v>45993.37516203704</v>
+        <v>45992.33333333334</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D197" s="2">
-        <v>45993.6992824074</v>
+        <v>45992.33333333334</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F197" s="2" t="s">
         <v>157</v>
@@ -6218,16 +6216,16 @@
     </row>
     <row r="198" spans="1:8">
       <c r="A198" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B198" s="2">
-        <v>45992.37811342593</v>
+        <v>45993.5765625</v>
       </c>
       <c r="C198" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D198" s="2">
-        <v>45992.69790509259</v>
+        <v>45993.91775462963</v>
       </c>
       <c r="E198" s="2" t="s">
         <v>10</v>
@@ -6236,7 +6234,7 @@
         <v>157</v>
       </c>
       <c r="G198" s="2">
-        <v>13.65</v>
+        <v>22</v>
       </c>
       <c r="H198" s="2" t="s">
         <v>158</v>
@@ -6244,16 +6242,16 @@
     </row>
     <row r="199" spans="1:8">
       <c r="A199" s="2" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="B199" s="2">
-        <v>45992.58185185185</v>
+        <v>45992.58358796296</v>
       </c>
       <c r="C199" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D199" s="2">
-        <v>45992.8978125</v>
+        <v>45992.89682870371</v>
       </c>
       <c r="E199" s="2" t="s">
         <v>10</v>
@@ -6262,7 +6260,7 @@
         <v>157</v>
       </c>
       <c r="G199" s="2">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H199" s="2" t="s">
         <v>158</v>
@@ -6270,16 +6268,16 @@
     </row>
     <row r="200" spans="1:8">
       <c r="A200" s="2" t="s">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="B200" s="2">
-        <v>45993.33579861111</v>
+        <v>45993.69541666667</v>
       </c>
       <c r="C200" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D200" s="2">
-        <v>45993.64005787037</v>
+        <v>45993.9084375</v>
       </c>
       <c r="E200" s="2" t="s">
         <v>10</v>
@@ -6288,7 +6286,7 @@
         <v>157</v>
       </c>
       <c r="G200" s="2">
-        <v>19</v>
+        <v>13.65</v>
       </c>
       <c r="H200" s="2" t="s">
         <v>158</v>
@@ -6296,10 +6294,10 @@
     </row>
     <row r="201" spans="1:8">
       <c r="A201" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B201" s="2">
-        <v>45992.64875</v>
+        <v>45992.6641087963</v>
       </c>
       <c r="C201" s="2" t="s">
         <v>9</v>
@@ -6309,23 +6307,25 @@
       <c r="F201" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="G201" s="2"/>
+      <c r="G201" s="2">
+        <v>13.65</v>
+      </c>
       <c r="H201" s="2" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="202" spans="1:8">
       <c r="A202" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="B202" s="2">
-        <v>45992.36230324074</v>
+        <v>45993.37694444445</v>
       </c>
       <c r="C202" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D202" s="2">
-        <v>45992.68001157408</v>
+        <v>45993.72078703704</v>
       </c>
       <c r="E202" s="2" t="s">
         <v>10</v>
@@ -6334,7 +6334,7 @@
         <v>157</v>
       </c>
       <c r="G202" s="2">
-        <v>21</v>
+        <v>13.65</v>
       </c>
       <c r="H202" s="2" t="s">
         <v>158</v>
@@ -6371,13 +6371,13 @@
         <v>174</v>
       </c>
       <c r="B204" s="2">
-        <v>45993.95416666667</v>
+        <v>45993.39311342593</v>
       </c>
       <c r="C204" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D204" s="2">
-        <v>45994.29306712963</v>
+        <v>45993.46118055555</v>
       </c>
       <c r="E204" s="2" t="s">
         <v>10</v>
@@ -6386,7 +6386,7 @@
         <v>175</v>
       </c>
       <c r="G204" s="2">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="H204" s="2" t="s">
         <v>176</v>
@@ -6397,13 +6397,13 @@
         <v>174</v>
       </c>
       <c r="B205" s="2">
-        <v>45992.9528587963</v>
+        <v>45992.53841435185</v>
       </c>
       <c r="C205" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D205" s="2">
-        <v>45993.29563657408</v>
+        <v>45992.95521990741</v>
       </c>
       <c r="E205" s="2" t="s">
         <v>10</v>
@@ -6412,7 +6412,7 @@
         <v>175</v>
       </c>
       <c r="G205" s="2">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="H205" s="2" t="s">
         <v>176</v>
@@ -6423,13 +6423,13 @@
         <v>177</v>
       </c>
       <c r="B206" s="2">
-        <v>45992.33770833333</v>
+        <v>45993.29008101852</v>
       </c>
       <c r="C206" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D206" s="2">
-        <v>45992.66642361111</v>
+        <v>45993.58872685185</v>
       </c>
       <c r="E206" s="2" t="s">
         <v>10</v>
@@ -6438,7 +6438,7 @@
         <v>175</v>
       </c>
       <c r="G206" s="2">
-        <v>15.25</v>
+        <v>16.5</v>
       </c>
       <c r="H206" s="2" t="s">
         <v>176</v>
@@ -6449,22 +6449,22 @@
         <v>178</v>
       </c>
       <c r="B207" s="2">
-        <v>45993.5</v>
+        <v>45993.62380787037</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D207" s="2">
-        <v>45993.5</v>
+        <v>45993.95444444445</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F207" s="2" t="s">
         <v>175</v>
       </c>
       <c r="G207" s="2">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="H207" s="2" t="s">
         <v>176</v>
@@ -6472,16 +6472,16 @@
     </row>
     <row r="208" spans="1:8">
       <c r="A208" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B208" s="2">
-        <v>45993.62380787037</v>
+        <v>45992.62354166667</v>
       </c>
       <c r="C208" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D208" s="2">
-        <v>45993.95444444445</v>
+        <v>45992.85416666666</v>
       </c>
       <c r="E208" s="2" t="s">
         <v>10</v>
@@ -6498,16 +6498,16 @@
     </row>
     <row r="209" spans="1:8">
       <c r="A209" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B209" s="2">
-        <v>45993.29008101852</v>
+        <v>45993.62984953704</v>
       </c>
       <c r="C209" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D209" s="2">
-        <v>45993.58872685185</v>
+        <v>45993.95290509259</v>
       </c>
       <c r="E209" s="2" t="s">
         <v>10</v>
@@ -6516,7 +6516,7 @@
         <v>175</v>
       </c>
       <c r="G209" s="2">
-        <v>16.5</v>
+        <v>17.25</v>
       </c>
       <c r="H209" s="2" t="s">
         <v>176</v>
@@ -6524,25 +6524,25 @@
     </row>
     <row r="210" spans="1:8">
       <c r="A210" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B210" s="2">
-        <v>45992.33333333334</v>
+        <v>45992.33770833333</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D210" s="2">
-        <v>45992.33333333334</v>
+        <v>45992.66642361111</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F210" s="2" t="s">
         <v>175</v>
       </c>
       <c r="G210" s="2">
-        <v>16</v>
+        <v>15.25</v>
       </c>
       <c r="H210" s="2" t="s">
         <v>176</v>
@@ -6556,13 +6556,13 @@
         <v>45993.33333333334</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D211" s="2">
         <v>45993.33333333334</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F211" s="2" t="s">
         <v>175</v>
@@ -6576,25 +6576,25 @@
     </row>
     <row r="212" spans="1:8">
       <c r="A212" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B212" s="2">
-        <v>45992.24747685185</v>
+        <v>45992.33333333334</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D212" s="2">
-        <v>45992.64570601852</v>
+        <v>45992.33333333334</v>
       </c>
       <c r="E212" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F212" s="2" t="s">
         <v>175</v>
       </c>
       <c r="G212" s="2">
-        <v>24.72</v>
+        <v>16</v>
       </c>
       <c r="H212" s="2" t="s">
         <v>176</v>
@@ -6602,19 +6602,19 @@
     </row>
     <row r="213" spans="1:8">
       <c r="A213" s="2" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B213" s="2">
-        <v>45992.53841435185</v>
+        <v>45993.5</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D213" s="2">
-        <v>45992.95521990741</v>
+        <v>45993.5</v>
       </c>
       <c r="E213" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F213" s="2" t="s">
         <v>175</v>
@@ -6628,16 +6628,16 @@
     </row>
     <row r="214" spans="1:8">
       <c r="A214" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B214" s="2">
-        <v>45993.39311342593</v>
+        <v>45993.95416666667</v>
       </c>
       <c r="C214" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D214" s="2">
-        <v>45993.46118055555</v>
+        <v>45994.29306712963</v>
       </c>
       <c r="E214" s="2" t="s">
         <v>10</v>
@@ -6646,7 +6646,7 @@
         <v>175</v>
       </c>
       <c r="G214" s="2">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="H214" s="2" t="s">
         <v>176</v>
@@ -6654,16 +6654,16 @@
     </row>
     <row r="215" spans="1:8">
       <c r="A215" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B215" s="2">
-        <v>45993.62984953704</v>
+        <v>45992.9528587963</v>
       </c>
       <c r="C215" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D215" s="2">
-        <v>45993.95290509259</v>
+        <v>45993.29563657408</v>
       </c>
       <c r="E215" s="2" t="s">
         <v>10</v>
@@ -6672,7 +6672,7 @@
         <v>175</v>
       </c>
       <c r="G215" s="2">
-        <v>17.25</v>
+        <v>18.5</v>
       </c>
       <c r="H215" s="2" t="s">
         <v>176</v>
@@ -6680,16 +6680,16 @@
     </row>
     <row r="216" spans="1:8">
       <c r="A216" s="2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B216" s="2">
-        <v>45992.62354166667</v>
+        <v>45992.24747685185</v>
       </c>
       <c r="C216" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D216" s="2">
-        <v>45992.85416666666</v>
+        <v>45992.64570601852</v>
       </c>
       <c r="E216" s="2" t="s">
         <v>10</v>
@@ -6698,7 +6698,7 @@
         <v>175</v>
       </c>
       <c r="G216" s="2">
-        <v>16.5</v>
+        <v>24.72</v>
       </c>
       <c r="H216" s="2" t="s">
         <v>176</v>
@@ -6709,13 +6709,13 @@
         <v>184</v>
       </c>
       <c r="B217" s="2">
-        <v>45993.47619212963</v>
+        <v>45992.39903935185</v>
       </c>
       <c r="C217" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D217" s="2">
-        <v>45993.66888888889</v>
+        <v>45992.78083333333</v>
       </c>
       <c r="E217" s="2" t="s">
         <v>10</v>
@@ -6732,16 +6732,16 @@
     </row>
     <row r="218" spans="1:8">
       <c r="A218" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B218" s="2">
-        <v>45992.39877314815</v>
+        <v>45993.33015046296</v>
       </c>
       <c r="C218" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D218" s="2">
-        <v>45992.78104166667</v>
+        <v>45993.49803240741</v>
       </c>
       <c r="E218" s="2" t="s">
         <v>10</v>
@@ -6750,7 +6750,7 @@
         <v>185</v>
       </c>
       <c r="G218" s="2">
-        <v>16.61</v>
+        <v>14.5</v>
       </c>
       <c r="H218" s="2" t="s">
         <v>186</v>
@@ -6758,16 +6758,16 @@
     </row>
     <row r="219" spans="1:8">
       <c r="A219" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B219" s="2">
-        <v>45993.36116898148</v>
+        <v>45992.39877314815</v>
       </c>
       <c r="C219" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D219" s="2">
-        <v>45993.64501157407</v>
+        <v>45992.78104166667</v>
       </c>
       <c r="E219" s="2" t="s">
         <v>10</v>
@@ -6776,7 +6776,7 @@
         <v>185</v>
       </c>
       <c r="G219" s="2">
-        <v>20</v>
+        <v>16.61</v>
       </c>
       <c r="H219" s="2" t="s">
         <v>186</v>
@@ -6784,16 +6784,16 @@
     </row>
     <row r="220" spans="1:8">
       <c r="A220" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B220" s="2">
-        <v>45993.40340277777</v>
+        <v>45992.30857638889</v>
       </c>
       <c r="C220" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D220" s="2">
-        <v>45993.67043981481</v>
+        <v>45992.63498842593</v>
       </c>
       <c r="E220" s="2" t="s">
         <v>10</v>
@@ -6802,7 +6802,7 @@
         <v>185</v>
       </c>
       <c r="G220" s="2">
-        <v>16.61</v>
+        <v>16</v>
       </c>
       <c r="H220" s="2" t="s">
         <v>186</v>
@@ -6810,16 +6810,16 @@
     </row>
     <row r="221" spans="1:8">
       <c r="A221" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B221" s="2">
-        <v>45992.39903935185</v>
+        <v>45993.30981481481</v>
       </c>
       <c r="C221" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D221" s="2">
-        <v>45992.78083333333</v>
+        <v>45993.67152777778</v>
       </c>
       <c r="E221" s="2" t="s">
         <v>10</v>
@@ -6828,7 +6828,7 @@
         <v>185</v>
       </c>
       <c r="G221" s="2">
-        <v>16.61</v>
+        <v>16</v>
       </c>
       <c r="H221" s="2" t="s">
         <v>186</v>
@@ -6836,16 +6836,16 @@
     </row>
     <row r="222" spans="1:8">
       <c r="A222" s="2" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="B222" s="2">
-        <v>45993.33015046296</v>
+        <v>45993.40340277777</v>
       </c>
       <c r="C222" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D222" s="2">
-        <v>45993.49803240741</v>
+        <v>45993.67043981481</v>
       </c>
       <c r="E222" s="2" t="s">
         <v>10</v>
@@ -6854,7 +6854,7 @@
         <v>185</v>
       </c>
       <c r="G222" s="2">
-        <v>14.5</v>
+        <v>16.61</v>
       </c>
       <c r="H222" s="2" t="s">
         <v>186</v>
@@ -6862,16 +6862,16 @@
     </row>
     <row r="223" spans="1:8">
       <c r="A223" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B223" s="2">
-        <v>45993.30981481481</v>
+        <v>45993.47619212963</v>
       </c>
       <c r="C223" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D223" s="2">
-        <v>45993.67152777778</v>
+        <v>45993.66888888889</v>
       </c>
       <c r="E223" s="2" t="s">
         <v>10</v>
@@ -6880,7 +6880,7 @@
         <v>185</v>
       </c>
       <c r="G223" s="2">
-        <v>16</v>
+        <v>16.61</v>
       </c>
       <c r="H223" s="2" t="s">
         <v>186</v>
@@ -6891,13 +6891,13 @@
         <v>190</v>
       </c>
       <c r="B224" s="2">
-        <v>45992.30857638889</v>
+        <v>45993.36116898148</v>
       </c>
       <c r="C224" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D224" s="2">
-        <v>45992.63498842593</v>
+        <v>45993.64501157407</v>
       </c>
       <c r="E224" s="2" t="s">
         <v>10</v>
@@ -6906,7 +6906,7 @@
         <v>185</v>
       </c>
       <c r="G224" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H224" s="2" t="s">
         <v>186</v>
@@ -6917,13 +6917,13 @@
         <v>191</v>
       </c>
       <c r="B225" s="2">
-        <v>45993.32358796296</v>
+        <v>45992.35121527778</v>
       </c>
       <c r="C225" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D225" s="2">
-        <v>45993.68211805556</v>
+        <v>45992.68732638889</v>
       </c>
       <c r="E225" s="2" t="s">
         <v>10</v>
@@ -6943,13 +6943,13 @@
         <v>191</v>
       </c>
       <c r="B226" s="2">
-        <v>45992.35121527778</v>
+        <v>45993.32358796296</v>
       </c>
       <c r="C226" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D226" s="2">
-        <v>45992.68732638889</v>
+        <v>45993.68211805556</v>
       </c>
       <c r="E226" s="2" t="s">
         <v>10</v>
@@ -6972,7 +6972,7 @@
         <v>45992.58616898148</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D227" s="2">
         <v>45992.6752662037</v>
@@ -6992,16 +6992,16 @@
     </row>
     <row r="228" spans="1:8">
       <c r="A228" s="2" t="s">
-        <v>101</v>
+        <v>197</v>
       </c>
       <c r="B228" s="2">
-        <v>45992.50498842593</v>
+        <v>45992.51815972223</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D228" s="2">
-        <v>45992.67591435185</v>
+        <v>45992.65887731482</v>
       </c>
       <c r="E228" s="2" t="s">
         <v>10</v>
@@ -7009,25 +7009,23 @@
       <c r="F228" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="G228" s="2">
-        <v>16</v>
-      </c>
+      <c r="G228" s="2"/>
       <c r="H228" s="2" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="229" spans="1:8">
       <c r="A229" s="2" t="s">
-        <v>197</v>
+        <v>98</v>
       </c>
       <c r="B229" s="2">
-        <v>45992.51815972223</v>
+        <v>45992.50498842593</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D229" s="2">
-        <v>45992.65887731482</v>
+        <v>45992.67591435185</v>
       </c>
       <c r="E229" s="2" t="s">
         <v>10</v>
@@ -7035,7 +7033,9 @@
       <c r="F229" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="G229" s="2"/>
+      <c r="G229" s="2">
+        <v>16</v>
+      </c>
       <c r="H229" s="2" t="s">
         <v>196</v>
       </c>
@@ -7097,13 +7097,13 @@
         <v>202</v>
       </c>
       <c r="B232" s="2">
-        <v>45992.33006944445</v>
+        <v>45992.32921296296</v>
       </c>
       <c r="C232" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D232" s="2">
-        <v>45992.4482175926</v>
+        <v>45992.74585648148</v>
       </c>
       <c r="E232" s="2" t="s">
         <v>10</v>
@@ -7112,7 +7112,7 @@
         <v>203</v>
       </c>
       <c r="G232" s="2">
-        <v>23.49</v>
+        <v>22</v>
       </c>
       <c r="H232" s="2" t="s">
         <v>204</v>
@@ -7123,13 +7123,13 @@
         <v>205</v>
       </c>
       <c r="B233" s="2">
-        <v>45992.34174768518</v>
+        <v>45993.34314814815</v>
       </c>
       <c r="C233" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D233" s="2">
-        <v>45992.67616898148</v>
+        <v>45993.66737268519</v>
       </c>
       <c r="E233" s="2" t="s">
         <v>10</v>
@@ -7138,7 +7138,7 @@
         <v>203</v>
       </c>
       <c r="G233" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H233" s="2" t="s">
         <v>204</v>
@@ -7146,7 +7146,7 @@
     </row>
     <row r="234" spans="1:8">
       <c r="A234" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B234" s="2">
         <v>45993.35118055555</v>
@@ -7172,16 +7172,16 @@
     </row>
     <row r="235" spans="1:8">
       <c r="A235" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B235" s="2">
-        <v>45992.34165509259</v>
+        <v>45992.33259259259</v>
       </c>
       <c r="C235" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D235" s="2">
-        <v>45992.66502314815</v>
+        <v>45992.62094907407</v>
       </c>
       <c r="E235" s="2" t="s">
         <v>10</v>
@@ -7190,7 +7190,7 @@
         <v>203</v>
       </c>
       <c r="G235" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H235" s="2" t="s">
         <v>204</v>
@@ -7198,16 +7198,16 @@
     </row>
     <row r="236" spans="1:8">
       <c r="A236" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B236" s="2">
-        <v>45993.33853009259</v>
+        <v>45992.34165509259</v>
       </c>
       <c r="C236" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D236" s="2">
-        <v>45993.67113425926</v>
+        <v>45992.66502314815</v>
       </c>
       <c r="E236" s="2" t="s">
         <v>10</v>
@@ -7227,13 +7227,13 @@
         <v>207</v>
       </c>
       <c r="B237" s="2">
-        <v>45992.33259259259</v>
+        <v>45993.33853009259</v>
       </c>
       <c r="C237" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D237" s="2">
-        <v>45992.62094907407</v>
+        <v>45993.67113425926</v>
       </c>
       <c r="E237" s="2" t="s">
         <v>10</v>
@@ -7242,7 +7242,7 @@
         <v>203</v>
       </c>
       <c r="G237" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H237" s="2" t="s">
         <v>204</v>
@@ -7250,16 +7250,16 @@
     </row>
     <row r="238" spans="1:8">
       <c r="A238" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B238" s="2">
-        <v>45992.32921296296</v>
+        <v>45992.34174768518</v>
       </c>
       <c r="C238" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D238" s="2">
-        <v>45992.74585648148</v>
+        <v>45992.67616898148</v>
       </c>
       <c r="E238" s="2" t="s">
         <v>10</v>
@@ -7276,16 +7276,16 @@
     </row>
     <row r="239" spans="1:8">
       <c r="A239" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B239" s="2">
-        <v>45993.34314814815</v>
+        <v>45992.33006944445</v>
       </c>
       <c r="C239" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D239" s="2">
-        <v>45993.66737268519</v>
+        <v>45992.4482175926</v>
       </c>
       <c r="E239" s="2" t="s">
         <v>10</v>
@@ -7294,7 +7294,7 @@
         <v>203</v>
       </c>
       <c r="G239" s="2">
-        <v>20</v>
+        <v>23.49</v>
       </c>
       <c r="H239" s="2" t="s">
         <v>204</v>
@@ -7302,208 +7302,210 @@
     </row>
     <row r="240" spans="1:8">
       <c r="A240" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B240" s="2">
+        <v>45992.29037037037</v>
+      </c>
+      <c r="C240" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D240" s="2">
+        <v>45992.55635416666</v>
+      </c>
+      <c r="E240" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F240" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="B240" s="2">
-        <v>45993.33415509259</v>
-      </c>
-      <c r="C240" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D240" s="2">
-        <v>45993.52702546296</v>
-      </c>
-      <c r="E240" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F240" s="2" t="s">
+      <c r="G240" s="2">
+        <v>20</v>
+      </c>
+      <c r="H240" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="G240" s="2">
-        <v>18</v>
-      </c>
-      <c r="H240" s="2" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="241" spans="1:8">
       <c r="A241" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B241" s="2">
+        <v>45992.5</v>
+      </c>
+      <c r="C241" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D241" s="2">
+        <v>45992.625</v>
+      </c>
+      <c r="E241" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F241" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="B241" s="2">
-        <v>45992.3484375</v>
-      </c>
-      <c r="C241" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D241" s="2">
-        <v>45992.49106481481</v>
-      </c>
-      <c r="E241" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F241" s="2" t="s">
+      <c r="G241" s="2">
+        <v>24</v>
+      </c>
+      <c r="H241" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="G241" s="2">
-        <v>18</v>
-      </c>
-      <c r="H241" s="2" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="242" spans="1:8">
       <c r="A242" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B242" s="2">
-        <v>45993.32947916666</v>
+        <v>45992.26368055555</v>
       </c>
       <c r="C242" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D242" s="2">
-        <v>45993.51585648148</v>
+        <v>45992.48032407407</v>
       </c>
       <c r="E242" s="2" t="s">
         <v>91</v>
       </c>
       <c r="F242" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G242" s="2">
+        <v>24</v>
+      </c>
+      <c r="H242" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="G242" s="2">
-        <v>17</v>
-      </c>
-      <c r="H242" s="2" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="243" spans="1:8">
       <c r="A243" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B243" s="2">
-        <v>45992.33333333334</v>
+        <v>45993.33415509259</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D243" s="2">
-        <v>45992.33333333334</v>
+        <v>45993.52702546296</v>
       </c>
       <c r="E243" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F243" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G243" s="2">
+        <v>18</v>
+      </c>
+      <c r="H243" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="G243" s="2">
-        <v>18.5</v>
-      </c>
-      <c r="H243" s="2" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="244" spans="1:8">
       <c r="A244" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B244" s="2">
-        <v>45993.33333333334</v>
+        <v>45992.3484375</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D244" s="2">
-        <v>45993.33333333334</v>
+        <v>45992.49106481481</v>
       </c>
       <c r="E244" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F244" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G244" s="2">
+        <v>18</v>
+      </c>
+      <c r="H244" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="G244" s="2">
-        <v>18.5</v>
-      </c>
-      <c r="H244" s="2" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="245" spans="1:8">
       <c r="A245" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B245" s="2">
-        <v>45993.54071759259</v>
+        <v>45993.33333333334</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D245" s="2">
-        <v>45993.69123842593</v>
+        <v>45993.33333333334</v>
       </c>
       <c r="E245" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F245" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G245" s="2">
+        <v>18.5</v>
+      </c>
+      <c r="H245" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="G245" s="2">
-        <v>17</v>
-      </c>
-      <c r="H245" s="2" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="246" spans="1:8">
       <c r="A246" s="2" t="s">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="B246" s="2">
-        <v>45992.29037037037</v>
+        <v>45992.33333333334</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D246" s="2">
-        <v>45992.55635416666</v>
+        <v>45992.33333333334</v>
       </c>
       <c r="E246" s="2" t="s">
-        <v>91</v>
+        <v>17</v>
       </c>
       <c r="F246" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G246" s="2">
+        <v>18.5</v>
+      </c>
+      <c r="H246" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="G246" s="2">
-        <v>20</v>
-      </c>
-      <c r="H246" s="2" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="247" spans="1:8">
       <c r="A247" s="2" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="B247" s="2">
-        <v>45992.33572916667</v>
+        <v>45992.29172453703</v>
       </c>
       <c r="C247" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D247" s="2">
-        <v>45992.49737268518</v>
+        <v>45992.5741087963</v>
       </c>
       <c r="E247" s="2" t="s">
         <v>91</v>
       </c>
       <c r="F247" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G247" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="H247" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="G247" s="2"/>
-      <c r="H247" s="2" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="248" spans="1:8">
@@ -7511,36 +7513,36 @@
         <v>214</v>
       </c>
       <c r="B248" s="2">
-        <v>45993.33489583333</v>
+        <v>45992.59509259259</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D248" s="2">
-        <v>45993.46734953704</v>
+        <v>45992.69358796296</v>
       </c>
       <c r="E248" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F248" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G248" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="H248" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="G248" s="2">
-        <v>15</v>
-      </c>
-      <c r="H248" s="2" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="249" spans="1:8">
       <c r="A249" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B249" s="2">
         <v>45993.54539351852</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D249" s="2">
         <v>45993.69030092593</v>
@@ -7549,13 +7551,13 @@
         <v>10</v>
       </c>
       <c r="F249" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G249" s="2">
         <v>20.5</v>
       </c>
       <c r="H249" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="250" spans="1:8">
@@ -7563,25 +7565,25 @@
         <v>215</v>
       </c>
       <c r="B250" s="2">
-        <v>45992.59509259259</v>
+        <v>45993.32947916666</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D250" s="2">
-        <v>45992.69358796296</v>
+        <v>45993.51585648148</v>
       </c>
       <c r="E250" s="2" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="F250" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G250" s="2">
+        <v>17</v>
+      </c>
+      <c r="H250" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="G250" s="2">
-        <v>20.5</v>
-      </c>
-      <c r="H250" s="2" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="251" spans="1:8">
@@ -7589,25 +7591,25 @@
         <v>215</v>
       </c>
       <c r="B251" s="2">
-        <v>45992.29172453703</v>
+        <v>45993.54071759259</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D251" s="2">
-        <v>45992.5741087963</v>
+        <v>45993.69123842593</v>
       </c>
       <c r="E251" s="2" t="s">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="F251" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G251" s="2">
+        <v>17</v>
+      </c>
+      <c r="H251" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="G251" s="2">
-        <v>20.5</v>
-      </c>
-      <c r="H251" s="2" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="252" spans="1:8">
@@ -7627,39 +7629,37 @@
         <v>10</v>
       </c>
       <c r="F252" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G252" s="2">
         <v>16</v>
       </c>
       <c r="H252" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="253" spans="1:8">
       <c r="A253" s="2" t="s">
-        <v>217</v>
+        <v>197</v>
       </c>
       <c r="B253" s="2">
-        <v>45992.5</v>
+        <v>45992.33572916667</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D253" s="2">
-        <v>45992.625</v>
+        <v>45992.49737268518</v>
       </c>
       <c r="E253" s="2" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="F253" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G253" s="2"/>
+      <c r="H253" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="G253" s="2">
-        <v>24</v>
-      </c>
-      <c r="H253" s="2" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="254" spans="1:8">
@@ -7679,16 +7679,16 @@
         <v>10</v>
       </c>
       <c r="F254" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G254" s="2"/>
       <c r="H254" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="255" spans="1:8">
       <c r="A255" s="2" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="B255" s="2">
         <v>45992.33586805555</v>
@@ -7703,18 +7703,18 @@
         <v>91</v>
       </c>
       <c r="F255" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G255" s="2">
         <v>16</v>
       </c>
       <c r="H255" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="256" spans="1:8">
       <c r="A256" s="2" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="B256" s="2">
         <v>45993.33440972222</v>
@@ -7729,13 +7729,13 @@
         <v>91</v>
       </c>
       <c r="F256" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G256" s="2">
         <v>16</v>
       </c>
       <c r="H256" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="257" spans="1:8">
@@ -7743,30 +7743,30 @@
         <v>217</v>
       </c>
       <c r="B257" s="2">
-        <v>45992.26368055555</v>
+        <v>45993.33489583333</v>
       </c>
       <c r="C257" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D257" s="2">
-        <v>45992.48032407407</v>
+        <v>45993.46734953704</v>
       </c>
       <c r="E257" s="2" t="s">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="F257" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G257" s="2">
+        <v>15</v>
+      </c>
+      <c r="H257" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="G257" s="2">
-        <v>24</v>
-      </c>
-      <c r="H257" s="2" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="258" spans="1:8">
       <c r="A258" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B258" s="2">
         <v>45993.33784722222</v>
@@ -7781,13 +7781,13 @@
         <v>91</v>
       </c>
       <c r="F258" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G258" s="2">
         <v>20.5</v>
       </c>
       <c r="H258" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="259" spans="1:8">
@@ -7850,7 +7850,7 @@
         <v>45992.55232638889</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D261" s="2">
         <v>45992.76518518518</v>
@@ -7873,16 +7873,16 @@
         <v>225</v>
       </c>
       <c r="B262" s="2">
-        <v>45992.27461805556</v>
+        <v>45993.55827546296</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D262" s="2">
-        <v>45992.53001157408</v>
+        <v>45993.71579861111</v>
       </c>
       <c r="E262" s="2" t="s">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="F262" s="2" t="s">
         <v>222</v>
@@ -7896,25 +7896,25 @@
     </row>
     <row r="263" spans="1:8">
       <c r="A263" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B263" s="2">
-        <v>45992.55216435185</v>
+        <v>45992.27319444445</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D263" s="2">
-        <v>45992.76539351852</v>
+        <v>45992.53025462963</v>
       </c>
       <c r="E263" s="2" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="F263" s="2" t="s">
         <v>222</v>
       </c>
       <c r="G263" s="2">
-        <v>23</v>
+        <v>17.5</v>
       </c>
       <c r="H263" s="2" t="s">
         <v>223</v>
@@ -7948,25 +7948,25 @@
     </row>
     <row r="265" spans="1:8">
       <c r="A265" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B265" s="2">
-        <v>45992.27319444445</v>
+        <v>45992.55216435185</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D265" s="2">
-        <v>45992.53025462963</v>
+        <v>45992.76539351852</v>
       </c>
       <c r="E265" s="2" t="s">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="F265" s="2" t="s">
         <v>222</v>
       </c>
       <c r="G265" s="2">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="H265" s="2" t="s">
         <v>223</v>
@@ -7974,25 +7974,25 @@
     </row>
     <row r="266" spans="1:8">
       <c r="A266" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B266" s="2">
-        <v>45993.58417824074</v>
+        <v>45992.27461805556</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D266" s="2">
-        <v>45993.77274305555</v>
+        <v>45992.53001157408</v>
       </c>
       <c r="E266" s="2" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="F266" s="2" t="s">
         <v>222</v>
       </c>
       <c r="G266" s="2">
-        <v>17.72</v>
+        <v>23</v>
       </c>
       <c r="H266" s="2" t="s">
         <v>223</v>
@@ -8000,16 +8000,16 @@
     </row>
     <row r="267" spans="1:8">
       <c r="A267" s="2" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="B267" s="2">
-        <v>45993.55827546296</v>
+        <v>45993.58417824074</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D267" s="2">
-        <v>45993.71579861111</v>
+        <v>45993.77274305555</v>
       </c>
       <c r="E267" s="2" t="s">
         <v>10</v>
@@ -8018,7 +8018,7 @@
         <v>222</v>
       </c>
       <c r="G267" s="2">
-        <v>23</v>
+        <v>17.72</v>
       </c>
       <c r="H267" s="2" t="s">
         <v>223</v>
@@ -8052,16 +8052,16 @@
     </row>
     <row r="269" spans="1:8">
       <c r="A269" s="2" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B269" s="2">
-        <v>45992.17318287037</v>
+        <v>45993.66258101852</v>
       </c>
       <c r="C269" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D269" s="2">
-        <v>45992.29707175926</v>
+        <v>45993.67274305555</v>
       </c>
       <c r="E269" s="2" t="s">
         <v>10</v>
@@ -8070,7 +8070,7 @@
         <v>227</v>
       </c>
       <c r="G269" s="2">
-        <v>15</v>
+        <v>20.57</v>
       </c>
       <c r="H269" s="2" t="s">
         <v>228</v>
@@ -8078,16 +8078,16 @@
     </row>
     <row r="270" spans="1:8">
       <c r="A270" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B270" s="2">
-        <v>45993.31112268518</v>
+        <v>45992.17318287037</v>
       </c>
       <c r="C270" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D270" s="2">
-        <v>45993.75378472222</v>
+        <v>45992.29707175926</v>
       </c>
       <c r="E270" s="2" t="s">
         <v>10</v>
@@ -8096,7 +8096,7 @@
         <v>227</v>
       </c>
       <c r="G270" s="2">
-        <v>19.5</v>
+        <v>15</v>
       </c>
       <c r="H270" s="2" t="s">
         <v>228</v>
@@ -8107,13 +8107,13 @@
         <v>230</v>
       </c>
       <c r="B271" s="2">
-        <v>45992.34172453704</v>
+        <v>45993.31112268518</v>
       </c>
       <c r="C271" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D271" s="2">
-        <v>45992.6603587963</v>
+        <v>45993.75378472222</v>
       </c>
       <c r="E271" s="2" t="s">
         <v>10</v>
@@ -8130,16 +8130,16 @@
     </row>
     <row r="272" spans="1:8">
       <c r="A272" s="2" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B272" s="2">
-        <v>45993.66258101852</v>
+        <v>45992.34172453704</v>
       </c>
       <c r="C272" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D272" s="2">
-        <v>45993.67274305555</v>
+        <v>45992.6603587963</v>
       </c>
       <c r="E272" s="2" t="s">
         <v>10</v>
@@ -8148,7 +8148,7 @@
         <v>227</v>
       </c>
       <c r="G272" s="2">
-        <v>20.57</v>
+        <v>19.5</v>
       </c>
       <c r="H272" s="2" t="s">
         <v>228</v>
@@ -8159,13 +8159,13 @@
         <v>231</v>
       </c>
       <c r="B273" s="2">
-        <v>45992.36092592592</v>
+        <v>45992.33524305555</v>
       </c>
       <c r="C273" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D273" s="2">
-        <v>45992.70349537037</v>
+        <v>45992.69309027777</v>
       </c>
       <c r="E273" s="2" t="s">
         <v>10</v>
@@ -8174,7 +8174,7 @@
         <v>232</v>
       </c>
       <c r="G273" s="2">
-        <v>23.27</v>
+        <v>20</v>
       </c>
       <c r="H273" s="2" t="s">
         <v>233</v>
@@ -8185,13 +8185,13 @@
         <v>234</v>
       </c>
       <c r="B274" s="2">
-        <v>45992.33524305555</v>
+        <v>45992.36092592592</v>
       </c>
       <c r="C274" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D274" s="2">
-        <v>45992.69309027777</v>
+        <v>45992.70349537037</v>
       </c>
       <c r="E274" s="2" t="s">
         <v>10</v>
@@ -8200,7 +8200,7 @@
         <v>232</v>
       </c>
       <c r="G274" s="2">
-        <v>20</v>
+        <v>23.27</v>
       </c>
       <c r="H274" s="2" t="s">
         <v>233</v>
@@ -8211,13 +8211,13 @@
         <v>235</v>
       </c>
       <c r="B275" s="2">
-        <v>45993.53115740741</v>
+        <v>45992.34743055556</v>
       </c>
       <c r="C275" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D275" s="2">
-        <v>45993.61241898148</v>
+        <v>45992.69462962963</v>
       </c>
       <c r="E275" s="2" t="s">
         <v>10</v>
@@ -8226,10 +8226,10 @@
         <v>236</v>
       </c>
       <c r="G275" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H275" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="276" spans="1:8">
@@ -8237,13 +8237,13 @@
         <v>237</v>
       </c>
       <c r="B276" s="2">
-        <v>45992.34743055556</v>
+        <v>45993.36427083334</v>
       </c>
       <c r="C276" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D276" s="2">
-        <v>45992.69462962963</v>
+        <v>45993.7037037037</v>
       </c>
       <c r="E276" s="2" t="s">
         <v>10</v>
@@ -8252,24 +8252,24 @@
         <v>236</v>
       </c>
       <c r="G276" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H276" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="277" spans="1:8">
       <c r="A277" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B277" s="2">
-        <v>45993.33876157407</v>
+        <v>45993.53115740741</v>
       </c>
       <c r="C277" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D277" s="2">
-        <v>45993.69791666666</v>
+        <v>45993.61241898148</v>
       </c>
       <c r="E277" s="2" t="s">
         <v>10</v>
@@ -8278,24 +8278,24 @@
         <v>236</v>
       </c>
       <c r="G277" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H277" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="278" spans="1:8">
       <c r="A278" s="2" t="s">
-        <v>97</v>
+        <v>238</v>
       </c>
       <c r="B278" s="2">
-        <v>45993.55390046296</v>
+        <v>45993.2841550926</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D278" s="2">
-        <v>45993.68125</v>
+        <v>45993.48572916666</v>
       </c>
       <c r="E278" s="2" t="s">
         <v>10</v>
@@ -8304,24 +8304,24 @@
         <v>236</v>
       </c>
       <c r="G278" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H278" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="279" spans="1:8">
       <c r="A279" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B279" s="2">
-        <v>45992.29229166666</v>
+        <v>45992.52555555556</v>
       </c>
       <c r="C279" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D279" s="2">
-        <v>45992.48096064815</v>
+        <v>45992.62041666666</v>
       </c>
       <c r="E279" s="2" t="s">
         <v>10</v>
@@ -8333,21 +8333,21 @@
         <v>18</v>
       </c>
       <c r="H279" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="280" spans="1:8">
       <c r="A280" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B280" s="2">
-        <v>45992.52555555556</v>
+        <v>45992.29229166666</v>
       </c>
       <c r="C280" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D280" s="2">
-        <v>45992.62041666666</v>
+        <v>45992.48096064815</v>
       </c>
       <c r="E280" s="2" t="s">
         <v>10</v>
@@ -8359,21 +8359,21 @@
         <v>18</v>
       </c>
       <c r="H280" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="281" spans="1:8">
       <c r="A281" s="2" t="s">
-        <v>235</v>
+        <v>111</v>
       </c>
       <c r="B281" s="2">
-        <v>45993.2841550926</v>
+        <v>45993.55390046296</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D281" s="2">
-        <v>45993.48572916666</v>
+        <v>45993.68125</v>
       </c>
       <c r="E281" s="2" t="s">
         <v>10</v>
@@ -8382,24 +8382,24 @@
         <v>236</v>
       </c>
       <c r="G281" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H281" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="282" spans="1:8">
       <c r="A282" s="2" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B282" s="2">
-        <v>45993.36427083334</v>
+        <v>45993.33876157407</v>
       </c>
       <c r="C282" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D282" s="2">
-        <v>45993.7037037037</v>
+        <v>45993.69791666666</v>
       </c>
       <c r="E282" s="2" t="s">
         <v>10</v>
@@ -8408,10 +8408,10 @@
         <v>236</v>
       </c>
       <c r="G282" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H282" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="283" spans="1:8">
